--- a/darija_nlp_database.xlsx
+++ b/darija_nlp_database.xlsx
@@ -6,11 +6,18 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Raw Collection" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Conversation Threads" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Intent Signals Reference" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Export Preview" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Stats" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Arabizi Encoding" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Normalization Rules" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Raw Collection" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Conversation Threads" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Intent Signals Reference" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Export Preview" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Stats" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Bot Behavior Guide" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Swearing Policy" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Priority Order" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Sample Dialogues" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="User Suggestions" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -20,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -63,8 +70,42 @@
       <color rgb="FF1E293B"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="007F3F00"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="22">
     <fill>
       <patternFill/>
     </fill>
@@ -141,8 +182,38 @@
         <fgColor rgb="FF16A34A"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -176,11 +247,142 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B8CCE4"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B8CCE4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B8CCE4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B8CCE4"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B8CCE4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B8CCE4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B8CCE4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B8CCE4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B8CCE4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B8CCE4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B8CCE4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B8CCE4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B8CCE4"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B8CCE4"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B8CCE4"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00B8CCE4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00B8CCE4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B8CCE4"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00B8CCE4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B8CCE4"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B8CCE4"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B8CCE4"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B8CCE4"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00B8CCE4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -307,6 +509,59 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -669,24 +924,1072 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" style="31" min="1" max="1"/>
+    <col width="18" customWidth="1" style="31" min="2" max="2"/>
+    <col width="14" customWidth="1" style="31" min="3" max="3"/>
+    <col width="22" customWidth="1" style="31" min="4" max="4"/>
+    <col width="28" customWidth="1" style="31" min="5" max="5"/>
+    <col width="18" customWidth="1" style="31" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" s="31">
+      <c r="A1" s="50" t="inlineStr">
+        <is>
+          <t>🔤  Arabizi Encoding System — PDF §1</t>
+        </is>
+      </c>
+      <c r="B1" s="56" t="n"/>
+      <c r="C1" s="56" t="n"/>
+      <c r="D1" s="56" t="n"/>
+      <c r="E1" s="56" t="n"/>
+      <c r="F1" s="57" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1" s="31">
+      <c r="A2" s="52" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="B2" s="52" t="inlineStr">
+        <is>
+          <t>Letter Alternative</t>
+        </is>
+      </c>
+      <c r="C2" s="52" t="inlineStr">
+        <is>
+          <t>Arabic Letter</t>
+        </is>
+      </c>
+      <c r="D2" s="52" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="E2" s="52" t="inlineStr">
+        <is>
+          <t>Example (Arabizi)</t>
+        </is>
+      </c>
+      <c r="F2" s="52" t="inlineStr">
+        <is>
+          <t>Example (Arabic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1" s="31">
+      <c r="A3" s="58" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B3" s="58" t="inlineStr">
+        <is>
+          <t>q / k</t>
+        </is>
+      </c>
+      <c r="C3" s="58" t="inlineStr">
+        <is>
+          <t>ق</t>
+        </is>
+      </c>
+      <c r="D3" s="58" t="inlineStr">
+        <is>
+          <t>q — deep k</t>
+        </is>
+      </c>
+      <c r="E3" s="58" t="inlineStr">
+        <is>
+          <t>9alet / qalet</t>
+        </is>
+      </c>
+      <c r="F3" s="58" t="inlineStr">
+        <is>
+          <t>قالت</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1" s="31">
+      <c r="A4" s="59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B4" s="59" t="inlineStr">
+        <is>
+          <t>kh</t>
+        </is>
+      </c>
+      <c r="C4" s="59" t="inlineStr">
+        <is>
+          <t>خ</t>
+        </is>
+      </c>
+      <c r="D4" s="59" t="inlineStr">
+        <is>
+          <t>kh — guttural</t>
+        </is>
+      </c>
+      <c r="E4" s="59" t="inlineStr">
+        <is>
+          <t>5oya / khoya</t>
+        </is>
+      </c>
+      <c r="F4" s="59" t="inlineStr">
+        <is>
+          <t>خويا</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1" s="31">
+      <c r="A5" s="58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" s="58" t="inlineStr">
+        <is>
+          <t>a / '</t>
+        </is>
+      </c>
+      <c r="C5" s="58" t="inlineStr">
+        <is>
+          <t>ء</t>
+        </is>
+      </c>
+      <c r="D5" s="58" t="inlineStr">
+        <is>
+          <t>glottal stop</t>
+        </is>
+      </c>
+      <c r="E5" s="58" t="inlineStr">
+        <is>
+          <t>2enti / aenti</t>
+        </is>
+      </c>
+      <c r="F5" s="58" t="inlineStr">
+        <is>
+          <t>أنتي</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1" s="31">
+      <c r="A6" s="59" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" s="59" t="inlineStr">
+        <is>
+          <t>aa</t>
+        </is>
+      </c>
+      <c r="C6" s="59" t="inlineStr">
+        <is>
+          <t>ع</t>
+        </is>
+      </c>
+      <c r="D6" s="59" t="inlineStr">
+        <is>
+          <t>ayn — deep vowel</t>
+        </is>
+      </c>
+      <c r="E6" s="59" t="inlineStr">
+        <is>
+          <t>3aych / aaych</t>
+        </is>
+      </c>
+      <c r="F6" s="59" t="inlineStr">
+        <is>
+          <t>عايش</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1" s="31">
+      <c r="A7" s="58" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B7" s="58" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="C7" s="58" t="inlineStr">
+        <is>
+          <t>ح</t>
+        </is>
+      </c>
+      <c r="D7" s="58" t="inlineStr">
+        <is>
+          <t>heavy h</t>
+        </is>
+      </c>
+      <c r="E7" s="58" t="inlineStr">
+        <is>
+          <t>7ajet / hajet</t>
+        </is>
+      </c>
+      <c r="F7" s="58" t="inlineStr">
+        <is>
+          <t>حاجة</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1" s="31">
+      <c r="A8" s="59" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B8" s="59" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="C8" s="59" t="inlineStr">
+        <is>
+          <t>ط</t>
+        </is>
+      </c>
+      <c r="D8" s="59" t="inlineStr">
+        <is>
+          <t>emphatic t</t>
+        </is>
+      </c>
+      <c r="E8" s="59" t="inlineStr">
+        <is>
+          <t>6abi3i / tabi3i</t>
+        </is>
+      </c>
+      <c r="F8" s="59" t="inlineStr">
+        <is>
+          <t>طبيعي</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1" s="31">
+      <c r="A9" s="58" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B9" s="58" t="inlineStr">
+        <is>
+          <t>gh</t>
+        </is>
+      </c>
+      <c r="C9" s="58" t="inlineStr">
+        <is>
+          <t>غ</t>
+        </is>
+      </c>
+      <c r="D9" s="58" t="inlineStr">
+        <is>
+          <t>gh — French r</t>
+        </is>
+      </c>
+      <c r="E9" s="58" t="inlineStr">
+        <is>
+          <t>8ayeb / ghayeb</t>
+        </is>
+      </c>
+      <c r="F9" s="58" t="inlineStr">
+        <is>
+          <t>غايب</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1" s="31">
+      <c r="A11" s="60" t="inlineStr">
+        <is>
+          <t>⚠️  Both variants are IDENTICAL — '5oya' and 'khoya' mean the same word. Always normalize before matching. Apply §2 normalization pipeline first.</t>
+        </is>
+      </c>
+      <c r="B11" s="56" t="n"/>
+      <c r="C11" s="56" t="n"/>
+      <c r="D11" s="56" t="n"/>
+      <c r="E11" s="56" t="n"/>
+      <c r="F11" s="57" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" style="31" min="1" max="1"/>
+    <col width="30" customWidth="1" style="31" min="2" max="2"/>
+    <col width="56" customWidth="1" style="31" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" s="31">
+      <c r="A1" s="50" t="inlineStr">
+        <is>
+          <t>📋  Intent Detection Priority Order — PDF §13  (when multiple signals appear in one message)</t>
+        </is>
+      </c>
+      <c r="B1" s="56" t="n"/>
+      <c r="C1" s="57" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1" s="31">
+      <c r="A2" s="52" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="B2" s="52" t="inlineStr">
+        <is>
+          <t>Signal Type</t>
+        </is>
+      </c>
+      <c r="C2" s="52" t="inlineStr">
+        <is>
+          <t>Bot Action</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1" s="31">
+      <c r="A3" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="44" t="inlineStr">
+        <is>
+          <t>Swear word  ← HIGHEST</t>
+        </is>
+      </c>
+      <c r="C3" s="44" t="inlineStr">
+        <is>
+          <t>10s timeout — strip swear from text then continue with cleaned input</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1" s="31">
+      <c r="A4" s="59" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="54" t="inlineStr">
+        <is>
+          <t>Giving up</t>
+        </is>
+      </c>
+      <c r="C4" s="54" t="inlineStr">
+        <is>
+          <t>Acknowledge + one last simplified 2-sentence attempt then stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1" s="31">
+      <c r="A5" s="58" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="55" t="inlineStr">
+        <is>
+          <t>Hallucination flag</t>
+        </is>
+      </c>
+      <c r="C5" s="55" t="inlineStr">
+        <is>
+          <t>Apologize + retry strictly with original question</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1" s="31">
+      <c r="A6" s="59" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="54" t="inlineStr">
+        <is>
+          <t>Off topic / wrong answer</t>
+        </is>
+      </c>
+      <c r="C6" s="54" t="inlineStr">
+        <is>
+          <t>Acknowledge + correct course</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1" s="31">
+      <c r="A7" s="58" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="55" t="inlineStr">
+        <is>
+          <t>Confusion signal</t>
+        </is>
+      </c>
+      <c r="C7" s="55" t="inlineStr">
+        <is>
+          <t>Ask to confirm + offer to reformulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1" s="31">
+      <c r="A8" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="54" t="inlineStr">
+        <is>
+          <t>Half understood</t>
+        </is>
+      </c>
+      <c r="C8" s="54" t="inlineStr">
+        <is>
+          <t>Ask what specific part was unclear</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1" s="31">
+      <c r="A9" s="58" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="55" t="inlineStr">
+        <is>
+          <t>Simplify request</t>
+        </is>
+      </c>
+      <c r="C9" s="55" t="inlineStr">
+        <is>
+          <t>Re-explain using concrete real-world example</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" s="31">
+      <c r="A10" s="59" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="54" t="inlineStr">
+        <is>
+          <t>Repeat request</t>
+        </is>
+      </c>
+      <c r="C10" s="54" t="inlineStr">
+        <is>
+          <t>Repeat full or partial previous answer</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1" s="31">
+      <c r="A11" s="58" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="55" t="inlineStr">
+        <is>
+          <t>Impatience</t>
+        </is>
+      </c>
+      <c r="C11" s="55" t="inlineStr">
+        <is>
+          <t>Give maximum 2 sentences, direct and to the point</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1" s="31">
+      <c r="A12" s="53" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="44" t="inlineStr">
+        <is>
+          <t>Understood / praise  ← LOWEST</t>
+        </is>
+      </c>
+      <c r="C12" s="44" t="inlineStr">
+        <is>
+          <t>Proceed normally — do NOT reformulate</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" style="31" min="1" max="1"/>
+    <col width="44" customWidth="1" style="31" min="2" max="2"/>
+    <col width="22" customWidth="1" style="31" min="3" max="3"/>
+    <col width="40" customWidth="1" style="31" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" s="31">
+      <c r="A1" s="50" t="inlineStr">
+        <is>
+          <t>💬  Sample Dialogues for RAG Context — PDF §14  (chunk each row separately for best retrieval)</t>
+        </is>
+      </c>
+      <c r="B1" s="56" t="n"/>
+      <c r="C1" s="56" t="n"/>
+      <c r="D1" s="57" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1" s="31">
+      <c r="A2" s="52" t="inlineStr">
+        <is>
+          <t>User Input (Arabizi)</t>
+        </is>
+      </c>
+      <c r="B2" s="52" t="inlineStr">
+        <is>
+          <t>Bot Action</t>
+        </is>
+      </c>
+      <c r="C2" s="52" t="inlineStr">
+        <is>
+          <t>Intent Triggered</t>
+        </is>
+      </c>
+      <c r="D2" s="52" t="inlineStr">
+        <is>
+          <t>RAG Chunk Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1" s="31">
+      <c r="A3" s="55" t="inlineStr">
+        <is>
+          <t>mafhemt chy</t>
+        </is>
+      </c>
+      <c r="B3" s="55" t="inlineStr">
+        <is>
+          <t>Reformulate in simpler terms</t>
+        </is>
+      </c>
+      <c r="C3" s="55" t="inlineStr">
+        <is>
+          <t>confusion</t>
+        </is>
+      </c>
+      <c r="D3" s="55" t="inlineStr">
+        <is>
+          <t>Trigger: didn't understand anything</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1" s="31">
+      <c r="A4" s="54" t="inlineStr">
+        <is>
+          <t>zid fassarly bisyassa</t>
+        </is>
+      </c>
+      <c r="B4" s="54" t="inlineStr">
+        <is>
+          <t>Slow down — use shorter sentences</t>
+        </is>
+      </c>
+      <c r="C4" s="54" t="inlineStr">
+        <is>
+          <t>simplify</t>
+        </is>
+      </c>
+      <c r="D4" s="54" t="inlineStr">
+        <is>
+          <t>Trigger: explain slowly / bichwaya bichwaya</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1" s="31">
+      <c r="A5" s="55" t="inlineStr">
+        <is>
+          <t>5arreeff</t>
+        </is>
+      </c>
+      <c r="B5" s="55" t="inlineStr">
+        <is>
+          <t>Apologize + reset to original question</t>
+        </is>
+      </c>
+      <c r="C5" s="55" t="inlineStr">
+        <is>
+          <t>hallucination</t>
+        </is>
+      </c>
+      <c r="D5" s="55" t="inlineStr">
+        <is>
+          <t>Trigger: off topic / hallucinating</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1" s="31">
+      <c r="A6" s="54" t="inlineStr">
+        <is>
+          <t>a3tini example</t>
+        </is>
+      </c>
+      <c r="B6" s="54" t="inlineStr">
+        <is>
+          <t>Provide a concrete real-world example</t>
+        </is>
+      </c>
+      <c r="C6" s="54" t="inlineStr">
+        <is>
+          <t>simplify</t>
+        </is>
+      </c>
+      <c r="D6" s="54" t="inlineStr">
+        <is>
+          <t>Trigger: give example / a3tini mitha</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1" s="31">
+      <c r="A7" s="55" t="inlineStr">
+        <is>
+          <t>haaannnnnn fhemtk</t>
+        </is>
+      </c>
+      <c r="B7" s="55" t="inlineStr">
+        <is>
+          <t>Proceed normally — do NOT reformulate</t>
+        </is>
+      </c>
+      <c r="C7" s="55" t="inlineStr">
+        <is>
+          <t>understood</t>
+        </is>
+      </c>
+      <c r="D7" s="55" t="inlineStr">
+        <is>
+          <t>Both understood signals together = strong confirmation</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1" s="31">
+      <c r="A8" s="54" t="inlineStr">
+        <is>
+          <t>ama mouch kk</t>
+        </is>
+      </c>
+      <c r="B8" s="54" t="inlineStr">
+        <is>
+          <t>Acknowledge pushback — invite correction</t>
+        </is>
+      </c>
+      <c r="C8" s="54" t="inlineStr">
+        <is>
+          <t>pushback</t>
+        </is>
+      </c>
+      <c r="D8" s="54" t="inlineStr">
+        <is>
+          <t>Partial agreement + disagreement</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1" s="31">
+      <c r="A9" s="55" t="inlineStr">
+        <is>
+          <t>ayast moi</t>
+        </is>
+      </c>
+      <c r="B9" s="55" t="inlineStr">
+        <is>
+          <t>One final simplified attempt then stop</t>
+        </is>
+      </c>
+      <c r="C9" s="55" t="inlineStr">
+        <is>
+          <t>giving_up</t>
+        </is>
+      </c>
+      <c r="D9" s="55" t="inlineStr">
+        <is>
+          <t>Trigger: exhausted / done trying</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1" s="31">
+      <c r="A10" s="54" t="inlineStr">
+        <is>
+          <t>na9is mil7dith</t>
+        </is>
+      </c>
+      <c r="B10" s="54" t="inlineStr">
+        <is>
+          <t>Give 1–2 sentence direct answer only</t>
+        </is>
+      </c>
+      <c r="C10" s="54" t="inlineStr">
+        <is>
+          <t>impatience</t>
+        </is>
+      </c>
+      <c r="D10" s="54" t="inlineStr">
+        <is>
+          <t>Trigger: too long / get to the point</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1" s="31">
+      <c r="A11" s="55" t="inlineStr">
+        <is>
+          <t>3awed miloul</t>
+        </is>
+      </c>
+      <c r="B11" s="55" t="inlineStr">
+        <is>
+          <t>Repeat full answer from the beginning</t>
+        </is>
+      </c>
+      <c r="C11" s="55" t="inlineStr">
+        <is>
+          <t>repeat_all</t>
+        </is>
+      </c>
+      <c r="D11" s="55" t="inlineStr">
+        <is>
+          <t>Trigger: rit milloul = from the start</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1" s="31">
+      <c r="A12" s="54" t="inlineStr">
+        <is>
+          <t>lfaza le5ra 3awidha</t>
+        </is>
+      </c>
+      <c r="B12" s="54" t="inlineStr">
+        <is>
+          <t>Repeat only the last paragraph/sentence</t>
+        </is>
+      </c>
+      <c r="C12" s="54" t="inlineStr">
+        <is>
+          <t>repeat_part</t>
+        </is>
+      </c>
+      <c r="D12" s="54" t="inlineStr">
+        <is>
+          <t>Trigger: last part only</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" s="31">
+      <c r="A14" s="60" t="inlineStr">
+        <is>
+          <t>📌 RAG Strategy: chunk this sheet by section for best retrieval. Each row = one RAG chunk. Similarity search returns focused results per intent.</t>
+        </is>
+      </c>
+      <c r="B14" s="56" t="n"/>
+      <c r="C14" s="56" t="n"/>
+      <c r="D14" s="57" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A14:D14"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>context_question</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>context_answer</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>suggestion</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>reviewer_note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-05-07 22:07</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>chnoa reference mta3 klemik</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>rit houa, bch tfhem barcha... elreference mta3 klemik huwa m3a elconcepts elbasis li fi elklemik, ya5i elchimie, winou y5dem fi felm elklemik, elcompounds, welelements. elreference mta3 klemik y5dem fi tawa elstudents welresearchers li yfhemou chi 9olt mte3 elklemik, ya5i y3rafou chi 9olt mte3 elproperties welbehaviors mta3 elmatériaux welsubstances. behi, elreference mta3 klemik huwa m3a eltools welresources li y5demou fi felm elklemik, ya5i yest5demou 3awed eldictionaries, elencyclopédies, welatabases. fhemt?</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>instead of bich tefhim barcha use bich tefhem mli7</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-07 22:14</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>chnoa reference mta3 klemik</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>rit houa, bch tfhem barcha... elreference mta3 klemik huwa m3a elconcepts elbasis li fi elklemik, ya5i elchimie, winou y5dem fi felm elklemik, elcompounds, welelements. elreference mta3 klemik y5dem fi tawa elstudents welresearchers li yfhemou chi 9olt mte3 elklemik, ya5i y3rafou chi 9olt mte3 elproperties welbehaviors mta3 elmatériaux welsubstances. behi, elreference mta3 klemik huwa m3a eltools welresources li y5demou fi felm elklemik, ya5i yest5demou 3awed eldictionaries, elencyclopédies, welatabases. fhemt?</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>"m3a elconcepts elbasis li fi elklemik" reference mta3 klemi not klemk</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" style="31" min="1" max="1"/>
+    <col width="20" customWidth="1" style="31" min="2" max="2"/>
+    <col width="46" customWidth="1" style="31" min="3" max="3"/>
+    <col width="36" customWidth="1" style="31" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" s="31">
+      <c r="A1" s="50" t="inlineStr">
+        <is>
+          <t>⚙️  Text Normalization Rules — Apply in Order Before Intent Detection (PDF §2)</t>
+        </is>
+      </c>
+      <c r="B1" s="56" t="n"/>
+      <c r="C1" s="56" t="n"/>
+      <c r="D1" s="57" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1" s="31">
+      <c r="A2" s="52" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B2" s="52" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="C2" s="52" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D2" s="52" t="inlineStr">
+        <is>
+          <t>Example</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" s="31">
+      <c r="A3" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="55" t="inlineStr">
+        <is>
+          <t>Lowercase</t>
+        </is>
+      </c>
+      <c r="C3" s="55" t="inlineStr">
+        <is>
+          <t>Convert all text to lowercase</t>
+        </is>
+      </c>
+      <c r="D3" s="55" t="inlineStr">
+        <is>
+          <t>'3AWEDLY' → '3awedly'</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" s="31">
+      <c r="A4" s="59" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="54" t="inlineStr">
+        <is>
+          <t>Remove spaces</t>
+        </is>
+      </c>
+      <c r="C4" s="54" t="inlineStr">
+        <is>
+          <t>Strip all spaces — lazy typing skips them</t>
+        </is>
+      </c>
+      <c r="D4" s="54" t="inlineStr">
+        <is>
+          <t>'ma fhemtch' → 'mafhemtch'</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" s="31">
+      <c r="A5" s="58" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="55" t="inlineStr">
+        <is>
+          <t>Strip repetition</t>
+        </is>
+      </c>
+      <c r="C5" s="55" t="inlineStr">
+        <is>
+          <t>Collapse 3+ repeated letters down to 2</t>
+        </is>
+      </c>
+      <c r="D5" s="55" t="inlineStr">
+        <is>
+          <t>'haaaaannnn' → 'haann'</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" s="31">
+      <c r="A6" s="59" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="54" t="inlineStr">
+        <is>
+          <t>Fuzzy match</t>
+        </is>
+      </c>
+      <c r="C6" s="54" t="inlineStr">
+        <is>
+          <t>Use rapidfuzz threshold ~80 to catch misspellings</t>
+        </is>
+      </c>
+      <c r="D6" s="54" t="inlineStr">
+        <is>
+          <t>'mrigl' matches 'mrgl'</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" s="31">
+      <c r="A7" s="58" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="55" t="inlineStr">
+        <is>
+          <t>Number → letter</t>
+        </is>
+      </c>
+      <c r="C7" s="55" t="inlineStr">
+        <is>
+          <t>Optionally expand numbers to letter equivalents</t>
+        </is>
+      </c>
+      <c r="D7" s="55" t="inlineStr">
+        <is>
+          <t>'5oya' → 'khoya'</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="FF2563EB"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="31" min="1" max="1"/>
-    <col width="14" customWidth="1" style="31" min="2" max="2"/>
-    <col width="20" customWidth="1" style="31" min="3" max="3"/>
-    <col width="16" customWidth="1" style="31" min="4" max="4"/>
-    <col width="40" customWidth="1" style="31" min="5" max="5"/>
-    <col width="28" customWidth="1" style="31" min="6" max="6"/>
-    <col width="32" customWidth="1" style="31" min="7" max="7"/>
-    <col width="18" customWidth="1" style="31" min="8" max="8"/>
-    <col width="28" customWidth="1" style="31" min="9" max="10"/>
-    <col width="16" customWidth="1" style="31" min="11" max="11"/>
-    <col width="10" customWidth="1" style="31" min="12" max="12"/>
+    <col width="18" customWidth="1" style="31" min="2" max="2"/>
+    <col width="14" customWidth="1" style="31" min="3" max="3"/>
+    <col width="12" customWidth="1" style="31" min="4" max="4"/>
+    <col width="38" customWidth="1" style="31" min="5" max="5"/>
+    <col width="30" customWidth="1" style="31" min="6" max="6"/>
+    <col width="44" customWidth="1" style="31" min="7" max="7"/>
+    <col width="22" customWidth="1" style="31" min="8" max="8"/>
+    <col width="38" customWidth="1" style="31" min="9" max="10"/>
+    <col width="40" customWidth="1" style="31" min="10" max="10"/>
+    <col width="14" customWidth="1" style="31" min="11" max="11"/>
+    <col width="12" customWidth="1" style="31" min="12" max="12"/>
+    <col width="14" customWidth="1" style="31" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="31">
@@ -852,9 +2155,9 @@
           <t>sa7it fhemtk</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>sa7et fhemtek, fhimt, jawk bhi</t>
+      <c r="G4" s="44" t="inlineStr">
+        <is>
+          <t>mafhamtch, mafhemtch, zid fesarly, fassarly bilfalla9i, zid watha7li</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -1173,454 +2476,601 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="40" t="n">
+    <row r="10" ht="36" customHeight="1" s="31">
+      <c r="A10" s="53" t="n">
         <v>8</v>
       </c>
-      <c r="E10" s="36" t="inlineStr">
-        <is>
-          <t>tefhem fia? ,tifhim fia? ,fhemt ?</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="B10" s="54" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C10" s="54" t="inlineStr">
+        <is>
+          <t>Tunisian groups</t>
+        </is>
+      </c>
+      <c r="D10" s="54" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E10" s="54" t="inlineStr">
+        <is>
+          <t>tefhem fia? / tifhim fia? / fhemt?</t>
+        </is>
+      </c>
+      <c r="F10" s="44" t="inlineStr">
         <is>
           <t>fhemt</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>tefhem fia, tifhim fia, fhemt, tfhem, fhamt</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="G10" s="44" t="inlineStr">
+        <is>
+          <t>tefhem fia, tifhim fia, tfhem, fhamt</t>
+        </is>
+      </c>
+      <c r="H10" s="44" t="inlineStr">
         <is>
           <t>confusion</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>do you understand?</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>est-ce que vous comprenez?</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="I10" s="54" t="inlineStr">
+        <is>
+          <t>do you understand? (asking for comprehension check)</t>
+        </is>
+      </c>
+      <c r="J10" s="54" t="inlineStr">
+        <is>
+          <t>est-ce que tu comprends ?</t>
+        </is>
+      </c>
+      <c r="K10" s="54" t="inlineStr">
         <is>
           <t>neutral</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L10" s="54" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1" s="31">
-      <c r="A11" s="41" t="n">
+    <row r="11" ht="36" customHeight="1" s="31">
+      <c r="A11" s="53" t="n">
         <v>9</v>
       </c>
-      <c r="E11" s="39" t="inlineStr">
-        <is>
-          <t>Bonsoir , aandi question concernant le scrapping, par exemple ena aandi data concernant des patients, déjà fournies par l'entreprise ( pour un projet BI). Sauf que la data hedhi elle n'est pas suffisante pour mes analyses, c'est pour ça n7eb j'ai pensé au scrapping. ena nzid aalihom par exemple colonne "symptomes" , bon ena débutante fel DS, ama menaarefesh comment je peux joindre l'id du patient wel symptomes vu que les symptomes que je vais apporter ne sont pas les forcément les symptomes des malades de mon dataset. Merci d'avance</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="B11" s="55" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C11" s="55" t="inlineStr">
+        <is>
+          <t>Tunisian DS groups</t>
+        </is>
+      </c>
+      <c r="D11" s="55" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E11" s="55" t="inlineStr">
+        <is>
+          <t>n7eb nzid data 3la el patients ama menaarefesh kifeh</t>
+        </is>
+      </c>
+      <c r="F11" s="44" t="inlineStr">
         <is>
           <t>n7eb nzid data</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>nheb, nzid, n7ib, nhib</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="G11" s="44" t="inlineStr">
+        <is>
+          <t>nheb nzid, n7ib nzid, nheb nzid data, nzid data</t>
+        </is>
+      </c>
+      <c r="H11" s="44" t="inlineStr">
         <is>
           <t>simplify</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>I want to add data</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Je veux ajouter des données</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
+      <c r="I11" s="55" t="inlineStr">
+        <is>
+          <t>I want to add data but I don't know how</t>
+        </is>
+      </c>
+      <c r="J11" s="55" t="inlineStr">
+        <is>
+          <t>Je veux ajouter des données mais je ne sais pas comment</t>
+        </is>
+      </c>
+      <c r="K11" s="55" t="inlineStr">
         <is>
           <t>neutral</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="40" t="n">
+      <c r="L11" s="55" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1" s="31">
+      <c r="A12" s="53" t="n">
         <v>10</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Hello guys .. chnouwa parcours académique bech ta9ra AI f tunis</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>chnouwa parcours académique bech ta9ra AI f tunis</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>chnouwa, shnouwa, chnoua, shnoua</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="B12" s="54" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C12" s="54" t="inlineStr">
+        <is>
+          <t>Tunisian Tech groups</t>
+        </is>
+      </c>
+      <c r="D12" s="54" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E12" s="54" t="inlineStr">
+        <is>
+          <t>Hello guys .. chnoa parcours académique bech ta9ra AI f tunis</t>
+        </is>
+      </c>
+      <c r="F12" s="44" t="inlineStr">
+        <is>
+          <t>chnoa parcours académique</t>
+        </is>
+      </c>
+      <c r="G12" s="44" t="inlineStr">
+        <is>
+          <t>chnoa, chnia, chinhi, chnouwa, shnouwa</t>
+        </is>
+      </c>
+      <c r="H12" s="44" t="inlineStr">
         <is>
           <t>confusion</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>What is the academic path to learn AI in Tunisia</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Quel est le parcours académique pour apprendre l'IA en Tunisie</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
+      <c r="I12" s="54" t="inlineStr">
+        <is>
+          <t>What academic path should I follow to learn AI in Tunisia?</t>
+        </is>
+      </c>
+      <c r="J12" s="54" t="inlineStr">
+        <is>
+          <t>Quel cursus académique pour apprendre l'IA en Tunisie ?</t>
+        </is>
+      </c>
+      <c r="K12" s="54" t="inlineStr">
         <is>
           <t>neutral</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L12" s="54" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1" s="31">
-      <c r="A13" s="41" t="n">
+    <row r="13" ht="36" customHeight="1" s="31">
+      <c r="A13" s="53" t="n">
         <v>11</v>
       </c>
-      <c r="E13" s="42" t="inlineStr">
-        <is>
-          <t>blhy ena andii projet : la mise en place d’un robot de surveillance autonome basé sur « MACHINE LEARNING ».</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="B13" s="55" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C13" s="55" t="inlineStr">
+        <is>
+          <t>Tunisian ML groups</t>
+        </is>
+      </c>
+      <c r="D13" s="55" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E13" s="55" t="inlineStr">
+        <is>
+          <t>blhy ena andii projet : la mise en place d'un robot de surveillance ML</t>
+        </is>
+      </c>
+      <c r="F13" s="44" t="inlineStr">
         <is>
           <t>blhy ena andii projet</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>blahi, bl7y, bly, blhy</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>My project is</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Mon projet est</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
+      <c r="G13" s="44" t="inlineStr">
+        <is>
+          <t>blahi, bl7y, bly, blhy, blahi ena</t>
+        </is>
+      </c>
+      <c r="H13" s="44" t="inlineStr">
+        <is>
+          <t>opening_statement</t>
+        </is>
+      </c>
+      <c r="I13" s="55" t="inlineStr">
+        <is>
+          <t>I have a project about setting up an autonomous surveillance robot using ML</t>
+        </is>
+      </c>
+      <c r="J13" s="55" t="inlineStr">
+        <is>
+          <t>J'ai un projet de mise en place d'un robot de surveillance autonome ML</t>
+        </is>
+      </c>
+      <c r="K13" s="55" t="inlineStr">
         <is>
           <t>neutral</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="409.5" customHeight="1" s="31">
-      <c r="A14" s="40" t="n">
+      <c r="L13" s="55" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1" s="31">
+      <c r="A14" s="53" t="n">
         <v>12</v>
       </c>
-      <c r="E14" s="43" t="inlineStr">
-        <is>
-          <t>fih u انت قاعد تخدم في امان الله في machine learning مش تلقى حد يقلك عملت estimation parameters   بالباهي و الا عملت cross validation data.
-اول ما تشوف المصطلحات هذي مش تدخل بعضك و تقول شنوة هذا !عمري لا شوفتها كي بديت نتعلم و ترجع تتعلم ML من الأول املا في انك تلقى هذي المصطلحات و تدخل في متاهة😔.
-متخافش😊
-كي تشوف كلمة estimation فمعناها training لبيانات التدريب اللي مش تعملها يعني هل تدربت البيانات و الا لا اي صار training و الا لا.
-هاي طلعت ساهلة مش صعيبة😁
-اجا  نحكو شوية عالvalidation و الي معناها  test data 
-بيانات الاختبار اللي تتاكد من خلالها انو المودال "model" مناسب للdata متاعك و الا لا و هل تعلم مليح ولا
-اجا نحكو شوي على cross validation
-Cross validation
- هي تقسيم الdata  لtraining و test و من خلالها مش تنجم تعرف عدد التنبؤات الصحيحة اللي عملها مقارنة لعدد الاخطاء و من خلال نسبة التوقعات الصحيحة للتوقعات الغالطة نجمو نحددوا احنا احسن algorithme مش اناسب البيانات متاعك.n système de détection et de Reconnaissance des objets , un système de reconnaissance faciale ,et un système de reconnaissance de mouvement et de voix.</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>fih u انت قاعد تخدم في امان الله في machine learning</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>fih u anta qa3ed tkhadem fi iman allah fi machine learning, fih u انت قاعد تخدم في امان الله في ml</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="B14" s="54" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C14" s="54" t="inlineStr">
+        <is>
+          <t>Tunisian ML groups</t>
+        </is>
+      </c>
+      <c r="D14" s="54" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E14" s="54" t="inlineStr">
+        <is>
+          <t>fih u anta qa3ed tkhadem fi machine learning w mch t3aref estimation w cross validation</t>
+        </is>
+      </c>
+      <c r="F14" s="44" t="inlineStr">
+        <is>
+          <t>fih u anta qa3ed tkhadem fi machine learning</t>
+        </is>
+      </c>
+      <c r="G14" s="44" t="inlineStr">
+        <is>
+          <t>fih u anta qa3ed, fih w anta khadem, fih u tkhadem fi ml</t>
+        </is>
+      </c>
+      <c r="H14" s="44" t="inlineStr">
         <is>
           <t>simplify</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>You're working on machine learning, but you don't understand estimation parameters and cross validation data</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Vous travaillez sur l'apprentissage automatique, mais vous ne comprenez pas les paramètres d'estimation et les données de validation croisée</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
+      <c r="I14" s="54" t="inlineStr">
+        <is>
+          <t>you're working on ML but you don't understand estimation parameters and cross validation</t>
+        </is>
+      </c>
+      <c r="J14" s="54" t="inlineStr">
+        <is>
+          <t>tu travailles sur le ML mais tu ne comprends pas les paramètres et la cross validation</t>
+        </is>
+      </c>
+      <c r="K14" s="54" t="inlineStr">
         <is>
           <t>polite</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L14" s="54" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1" s="31">
-      <c r="A15" s="41" t="n">
+    <row r="15" ht="36" customHeight="1" s="31">
+      <c r="A15" s="53" t="n">
         <v>13</v>
       </c>
-      <c r="E15" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blhy eli 5dem haja kima hedhi w andou rapport kima haka yab3thly et merci beaucoup </t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="B15" s="55" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C15" s="55" t="inlineStr">
+        <is>
+          <t>Tunisian ML groups</t>
+        </is>
+      </c>
+      <c r="D15" s="55" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E15" s="55" t="inlineStr">
+        <is>
+          <t>blhy eli 5dem haja kima hedhi w andou rapport yab3thly merci</t>
+        </is>
+      </c>
+      <c r="F15" s="44" t="inlineStr">
         <is>
           <t>blhy eli 5dem haja kima hedhi</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="44" t="inlineStr">
         <is>
           <t>blhy eli khadem haja kima hadi, blhy ely 5dem haja kima hedi</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="44" t="inlineStr">
         <is>
           <t>understood</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>I'm telling you something like this and I'm giving you a report like this, thank you very much</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Je vous dis quelque chose comme ça et je vous donne un rapport comme ça, merci beaucoup</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
+      <c r="I15" s="55" t="inlineStr">
+        <is>
+          <t>someone who did something like this and has a report — thank you</t>
+        </is>
+      </c>
+      <c r="J15" s="55" t="inlineStr">
+        <is>
+          <t>quelqu'un qui a fait quelque chose comme ça et a un rapport — merci</t>
+        </is>
+      </c>
+      <c r="K15" s="55" t="inlineStr">
         <is>
           <t>polite</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L15" s="55" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="16.5" customHeight="1" s="31">
-      <c r="A16" s="40" t="n">
+    <row r="16" ht="36" customHeight="1" s="31">
+      <c r="A16" s="53" t="n">
         <v>14</v>
       </c>
-      <c r="E16" s="39" t="inlineStr">
-        <is>
-          <t>Cross training maho kimaa esiiir fil edge impulse bedhabet heka walla ?</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>maho kimaa esiiir</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>maho kima esir, mahou kima esir, maho kimaa asir</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
+      <c r="B16" s="54" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C16" s="54" t="inlineStr">
+        <is>
+          <t>Tunisian Tech groups</t>
+        </is>
+      </c>
+      <c r="D16" s="54" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E16" s="54" t="inlineStr">
+        <is>
+          <t>Cross training maho kimaa esiiir fil edge impulse bedhabet heka walla?</t>
+        </is>
+      </c>
+      <c r="F16" s="44" t="inlineStr">
+        <is>
+          <t>maho kima esir</t>
+        </is>
+      </c>
+      <c r="G16" s="44" t="inlineStr">
+        <is>
+          <t>maho kimaa esiiir, mahou kima esir, maho kimaa asir</t>
+        </is>
+      </c>
+      <c r="H16" s="44" t="inlineStr">
         <is>
           <t>confusion</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>What's the benefit of this?</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Quel est l'avantage de cela ?</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
+      <c r="I16" s="54" t="inlineStr">
+        <is>
+          <t>is cross training the one that happens in edge impulse or not?</t>
+        </is>
+      </c>
+      <c r="J16" s="54" t="inlineStr">
+        <is>
+          <t>le cross training est-il le meme qu'il y paraît dans edge impulse ?</t>
+        </is>
+      </c>
+      <c r="K16" s="54" t="inlineStr">
+        <is>
+          <t>confused</t>
+        </is>
+      </c>
+      <c r="L16" s="54" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1" s="31">
+      <c r="A17" s="53" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="55" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C17" s="55" t="inlineStr">
+        <is>
+          <t>Tunisian Tech groups</t>
+        </is>
+      </c>
+      <c r="D17" s="55" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E17" s="55" t="inlineStr">
+        <is>
+          <t>edge impulse hiya plateforme ta3tik interface mch inti tikhdem from scratch</t>
+        </is>
+      </c>
+      <c r="F17" s="44" t="inlineStr">
+        <is>
+          <t>edge impulse hiya plateforme ta3tik</t>
+        </is>
+      </c>
+      <c r="G17" s="44" t="inlineStr">
+        <is>
+          <t>edge impulse, edgeimpulse, edge impulse hiya, edgeimpulse hiya</t>
+        </is>
+      </c>
+      <c r="H17" s="44" t="inlineStr">
+        <is>
+          <t>understood</t>
+        </is>
+      </c>
+      <c r="I17" s="55" t="inlineStr">
+        <is>
+          <t>Edge Impulse is a platform that gives you an interface so you don't start from scratch</t>
+        </is>
+      </c>
+      <c r="J17" s="55" t="inlineStr">
+        <is>
+          <t>Edge Impulse est une plateforme qui te donne une interface pour ne pas partir de zéro</t>
+        </is>
+      </c>
+      <c r="K17" s="55" t="inlineStr">
         <is>
           <t>neutral</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="16.5" customHeight="1" s="31">
-      <c r="A17" s="41" t="n">
-        <v>15</v>
-      </c>
-      <c r="E17" s="39" t="inlineStr">
-        <is>
-          <t>edge impulse hiya plateforme ta3tik interface mch inti tikhdem from scratch ama akid models mta3ha fihom cross</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>edge impulse hiya plateforme ta3tik</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>edge impulse, edgeimpulse, edge impulse hiya, edgeimpulse hiya</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>understood</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Edge Impulse is a platform with a nice interface</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Edge Impulse est une plateforme avec une interface agréable</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" s="55" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1" s="31">
+      <c r="A18" s="53" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="54" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C18" s="54" t="inlineStr">
+        <is>
+          <t>Tunisian ML groups</t>
+        </is>
+      </c>
+      <c r="D18" s="54" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E18" s="54" t="inlineStr">
+        <is>
+          <t>akthar video yenjem yfeserlek kifach tta3lem — 9 months self-learning w l9a 5hedma</t>
+        </is>
+      </c>
+      <c r="F18" s="44" t="inlineStr">
+        <is>
+          <t>akthar video yenjem yfeserlek kifach tta3lem</t>
+        </is>
+      </c>
+      <c r="G18" s="44" t="inlineStr">
+        <is>
+          <t>akthar, akther, aktar, kifash, kifaach, kifach</t>
+        </is>
+      </c>
+      <c r="H18" s="44" t="inlineStr">
+        <is>
+          <t>encouragement</t>
+        </is>
+      </c>
+      <c r="I18" s="54" t="inlineStr">
+        <is>
+          <t>this video best explains how to learn — self-taught in 9 months and found a job</t>
+        </is>
+      </c>
+      <c r="J18" s="54" t="inlineStr">
+        <is>
+          <t>cette vidéo explique le mieux comment apprendre — autodidacte en 9 mois et a trouvé un emploi</t>
+        </is>
+      </c>
+      <c r="K18" s="54" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="L18" s="54" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1" s="31">
+      <c r="A19" s="53" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="55" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C19" s="55" t="inlineStr">
+        <is>
+          <t>Tunisian ML groups</t>
+        </is>
+      </c>
+      <c r="D19" s="55" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E19" s="55" t="inlineStr">
+        <is>
+          <t>tfarjo fih alvideo tayara 3al a5er</t>
+        </is>
+      </c>
+      <c r="F19" s="44" t="inlineStr">
+        <is>
+          <t>tfarjo fih alvideo tayara alakhir</t>
+        </is>
+      </c>
+      <c r="G19" s="44" t="inlineStr">
+        <is>
+          <t>tfarjo, tafarja, tfarja, fih, feh, alvideo, tayara, tayyara, alakhir, al7er</t>
+        </is>
+      </c>
+      <c r="H19" s="44" t="inlineStr">
+        <is>
+          <t>simplify</t>
+        </is>
+      </c>
+      <c r="I19" s="55" t="inlineStr">
+        <is>
+          <t>watch the video all the way to the end</t>
+        </is>
+      </c>
+      <c r="J19" s="55" t="inlineStr">
+        <is>
+          <t>regardez la vidéo jusqu'à la fin</t>
+        </is>
+      </c>
+      <c r="K19" s="55" t="inlineStr">
         <is>
           <t>neutral</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="16.5" customHeight="1" s="31">
-      <c r="E18" s="42" t="inlineStr">
-        <is>
-          <t>اكثر فيديو ينجم يفسرلك كيفاش تتعلم... حكى كيفاش في 9 شهر تعلم ذاتي وصل توظف في خدمة ... وقت اللي الأغلب يبقو يقرو سنين باش يوصلو للخدمة هاكي ..</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>akthar video yenjem yfeserlek kifach tta3lem</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>akthar, akther, aktar, kifash, kifaach, kifach</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>encouragement</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>most videos can explain to you how to learn... he explained how in 9 months of self-learning he got a job in the service... while most people spend years to get to the service</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>la plupart des vidéos peuvent vous expliquer comment apprendre... il a expliqué comment en 9 mois d'apprentissage autodidacte il a obtenu un emploi dans le service... alors que la plupart des gens passent des années pour arriver au service</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="16.5" customHeight="1" s="31">
-      <c r="E19" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تفرجو فيه الفيديو طيارة ع اللخر </t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>tfarjo fih alvideo tayara alakhir</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>tfarjo, tafarja, tfarja, fih, feh, alvideo, alvydeo, tayara, tayyara, alakhir, al7er</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>simplify</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>watch the video to the end</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>regardez la vidéo jusqu'à la fin</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
+      <c r="L19" s="55" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -1628,6 +3078,1386 @@
     </row>
     <row r="20" ht="16.5" customHeight="1" s="31">
       <c r="E20" s="42" t="n"/>
+    </row>
+    <row r="21" ht="36" customHeight="1" s="31">
+      <c r="A21" s="45" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C21" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D21" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E21" s="46" t="inlineStr">
+        <is>
+          <t>fassarly bilfalla9i please</t>
+        </is>
+      </c>
+      <c r="F21" s="46" t="inlineStr">
+        <is>
+          <t>fassarly bilfalla9i</t>
+        </is>
+      </c>
+      <c r="G21" s="46" t="inlineStr">
+        <is>
+          <t>fassarly bsahel, fesserly bilfalla9i</t>
+        </is>
+      </c>
+      <c r="H21" s="46" t="inlineStr">
+        <is>
+          <t>simplify</t>
+        </is>
+      </c>
+      <c r="I21" s="46" t="inlineStr">
+        <is>
+          <t>explain in the simplest possible form</t>
+        </is>
+      </c>
+      <c r="J21" s="46" t="inlineStr">
+        <is>
+          <t>explique de la manière la plus simple</t>
+        </is>
+      </c>
+      <c r="K21" s="46" t="inlineStr">
+        <is>
+          <t>polite</t>
+        </is>
+      </c>
+      <c r="L21" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1" s="31">
+      <c r="A22" s="45" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C22" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D22" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E22" s="46" t="inlineStr">
+        <is>
+          <t>zid watha7li heka mch fahi</t>
+        </is>
+      </c>
+      <c r="F22" s="46" t="inlineStr">
+        <is>
+          <t>zid watha7li</t>
+        </is>
+      </c>
+      <c r="G22" s="46" t="inlineStr">
+        <is>
+          <t>zid wath7li, zidli wtha7, watha7li mazelt</t>
+        </is>
+      </c>
+      <c r="H22" s="46" t="inlineStr">
+        <is>
+          <t>simplify</t>
+        </is>
+      </c>
+      <c r="I22" s="46" t="inlineStr">
+        <is>
+          <t>clarify this more I'm still not getting it</t>
+        </is>
+      </c>
+      <c r="J22" s="46" t="inlineStr">
+        <is>
+          <t>clarifie encore je ne comprends toujours pas</t>
+        </is>
+      </c>
+      <c r="K22" s="46" t="inlineStr">
+        <is>
+          <t>polite</t>
+        </is>
+      </c>
+      <c r="L22" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1" s="31">
+      <c r="A23" s="45" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C23" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D23" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E23" s="46" t="inlineStr">
+        <is>
+          <t>3andk example reel 3la heka</t>
+        </is>
+      </c>
+      <c r="F23" s="46" t="inlineStr">
+        <is>
+          <t>3andk example reel</t>
+        </is>
+      </c>
+      <c r="G23" s="46" t="inlineStr">
+        <is>
+          <t>3andek example reel, 3tini exemple reel, het mitha reel</t>
+        </is>
+      </c>
+      <c r="H23" s="46" t="inlineStr">
+        <is>
+          <t>simplify</t>
+        </is>
+      </c>
+      <c r="I23" s="46" t="inlineStr">
+        <is>
+          <t>do you have a real example of this</t>
+        </is>
+      </c>
+      <c r="J23" s="46" t="inlineStr">
+        <is>
+          <t>tu as un exemple réel de ça</t>
+        </is>
+      </c>
+      <c r="K23" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L23" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1" s="31">
+      <c r="A24" s="45" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C24" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D24" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E24" s="46" t="inlineStr">
+        <is>
+          <t>3tini schema wella liste bch nfhem</t>
+        </is>
+      </c>
+      <c r="F24" s="46" t="inlineStr">
+        <is>
+          <t>3tini schema wella liste</t>
+        </is>
+      </c>
+      <c r="G24" s="46" t="inlineStr">
+        <is>
+          <t>3tini schéma, 3tini liste, het schema, 3tini plan</t>
+        </is>
+      </c>
+      <c r="H24" s="46" t="inlineStr">
+        <is>
+          <t>simplify</t>
+        </is>
+      </c>
+      <c r="I24" s="46" t="inlineStr">
+        <is>
+          <t>give me a schema or list so I understand</t>
+        </is>
+      </c>
+      <c r="J24" s="46" t="inlineStr">
+        <is>
+          <t>donne-moi un schéma ou une liste pour comprendre</t>
+        </is>
+      </c>
+      <c r="K24" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L24" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1" s="31">
+      <c r="A25" s="45" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C25" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D25" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E25" s="46" t="inlineStr">
+        <is>
+          <t>w ba3d chnou ysir</t>
+        </is>
+      </c>
+      <c r="F25" s="46" t="inlineStr">
+        <is>
+          <t>w ba3d</t>
+        </is>
+      </c>
+      <c r="G25" s="46" t="inlineStr">
+        <is>
+          <t>wba3d, w ba3dha, wba3dha</t>
+        </is>
+      </c>
+      <c r="H25" s="46" t="inlineStr">
+        <is>
+          <t>continue_deeper</t>
+        </is>
+      </c>
+      <c r="I25" s="46" t="inlineStr">
+        <is>
+          <t>and then what happens next</t>
+        </is>
+      </c>
+      <c r="J25" s="46" t="inlineStr">
+        <is>
+          <t>et ensuite que se passe-t-il</t>
+        </is>
+      </c>
+      <c r="K25" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L25" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1" s="31">
+      <c r="A26" s="45" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C26" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D26" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E26" s="46" t="inlineStr">
+        <is>
+          <t>zid 3tini plus de détails</t>
+        </is>
+      </c>
+      <c r="F26" s="46" t="inlineStr">
+        <is>
+          <t>zid / 3tini plus de détails</t>
+        </is>
+      </c>
+      <c r="G26" s="46" t="inlineStr">
+        <is>
+          <t>zid zid, zidli, 3tini akthar détails</t>
+        </is>
+      </c>
+      <c r="H26" s="46" t="inlineStr">
+        <is>
+          <t>continue_deeper</t>
+        </is>
+      </c>
+      <c r="I26" s="46" t="inlineStr">
+        <is>
+          <t>continue / give me more details</t>
+        </is>
+      </c>
+      <c r="J26" s="46" t="inlineStr">
+        <is>
+          <t>continue / donne-moi plus de détails</t>
+        </is>
+      </c>
+      <c r="K26" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L26" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1" s="31">
+      <c r="A27" s="45" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C27" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D27" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E27" s="46" t="inlineStr">
+        <is>
+          <t>bch nfhem ya3ni kifeh tet3amel</t>
+        </is>
+      </c>
+      <c r="F27" s="46" t="inlineStr">
+        <is>
+          <t>bch nfhem</t>
+        </is>
+      </c>
+      <c r="G27" s="46" t="inlineStr">
+        <is>
+          <t>bich nfhem, bach nfhem</t>
+        </is>
+      </c>
+      <c r="H27" s="46" t="inlineStr">
+        <is>
+          <t>clarification_question</t>
+        </is>
+      </c>
+      <c r="I27" s="46" t="inlineStr">
+        <is>
+          <t>so I understand — how does it work</t>
+        </is>
+      </c>
+      <c r="J27" s="46" t="inlineStr">
+        <is>
+          <t>pour que je comprenne — comment ça fonctionne</t>
+        </is>
+      </c>
+      <c r="K27" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L27" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1" s="31">
+      <c r="A28" s="45" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C28" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D28" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E28" s="46" t="inlineStr">
+        <is>
+          <t>3lech heka / w 3leh lazm naaml kk</t>
+        </is>
+      </c>
+      <c r="F28" s="46" t="inlineStr">
+        <is>
+          <t>3lech heka</t>
+        </is>
+      </c>
+      <c r="G28" s="46" t="inlineStr">
+        <is>
+          <t>3lech haka, 3leh lazm naaml kk, 3leh lazm naaml haka</t>
+        </is>
+      </c>
+      <c r="H28" s="46" t="inlineStr">
+        <is>
+          <t>why_question</t>
+        </is>
+      </c>
+      <c r="I28" s="46" t="inlineStr">
+        <is>
+          <t>why is it like this / why must I do it this way</t>
+        </is>
+      </c>
+      <c r="J28" s="46" t="inlineStr">
+        <is>
+          <t>pourquoi c'est comme ça / pourquoi dois-je faire ça</t>
+        </is>
+      </c>
+      <c r="K28" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L28" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1" s="31">
+      <c r="A29" s="45" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C29" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D29" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E29" s="46" t="inlineStr">
+        <is>
+          <t>w chnou el farq bin X w Y</t>
+        </is>
+      </c>
+      <c r="F29" s="46" t="inlineStr">
+        <is>
+          <t>w chnou el farq bin X w Y</t>
+        </is>
+      </c>
+      <c r="G29" s="46" t="inlineStr">
+        <is>
+          <t>chnou el farq, chnoa el farq, kifeh ykhtalf, ma farqhom</t>
+        </is>
+      </c>
+      <c r="H29" s="46" t="inlineStr">
+        <is>
+          <t>compare_question</t>
+        </is>
+      </c>
+      <c r="I29" s="46" t="inlineStr">
+        <is>
+          <t>what's the difference between X and Y</t>
+        </is>
+      </c>
+      <c r="J29" s="46" t="inlineStr">
+        <is>
+          <t>quelle est la différence entre X et Y</t>
+        </is>
+      </c>
+      <c r="K29" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L29" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1" s="31">
+      <c r="A30" s="45" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C30" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D30" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E30" s="46" t="inlineStr">
+        <is>
+          <t>kifeh maaneha / kifeh maana el kelma hedhi</t>
+        </is>
+      </c>
+      <c r="F30" s="46" t="inlineStr">
+        <is>
+          <t>kifeh maaneha</t>
+        </is>
+      </c>
+      <c r="G30" s="46" t="inlineStr">
+        <is>
+          <t>kifeh maanaha, kifeh ma3neha, chnou maaneha</t>
+        </is>
+      </c>
+      <c r="H30" s="46" t="inlineStr">
+        <is>
+          <t>definition_question</t>
+        </is>
+      </c>
+      <c r="I30" s="46" t="inlineStr">
+        <is>
+          <t>what does this word mean exactly</t>
+        </is>
+      </c>
+      <c r="J30" s="46" t="inlineStr">
+        <is>
+          <t>que veut dire ce mot exactement</t>
+        </is>
+      </c>
+      <c r="K30" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L30" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1" s="31">
+      <c r="A31" s="45" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C31" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D31" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E31" s="46" t="inlineStr">
+        <is>
+          <t>w kifeh nesta3mlouha fel wa9e3</t>
+        </is>
+      </c>
+      <c r="F31" s="46" t="inlineStr">
+        <is>
+          <t>w kifeh nesta3mlouha</t>
+        </is>
+      </c>
+      <c r="G31" s="46" t="inlineStr">
+        <is>
+          <t>kifeh nesta3milha, kifeh na3mlou bha</t>
+        </is>
+      </c>
+      <c r="H31" s="46" t="inlineStr">
+        <is>
+          <t>clarification_question</t>
+        </is>
+      </c>
+      <c r="I31" s="46" t="inlineStr">
+        <is>
+          <t>and how do we actually use it in practice</t>
+        </is>
+      </c>
+      <c r="J31" s="46" t="inlineStr">
+        <is>
+          <t>et comment on l'utilise en pratique</t>
+        </is>
+      </c>
+      <c r="K31" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L31" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1" s="31">
+      <c r="A32" s="45" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C32" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D32" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E32" s="46" t="inlineStr">
+        <is>
+          <t>w chnoa ysir ki mana3milch kk</t>
+        </is>
+      </c>
+      <c r="F32" s="46" t="inlineStr">
+        <is>
+          <t>w chnoa ysir ki mana3milch kk</t>
+        </is>
+      </c>
+      <c r="G32" s="46" t="inlineStr">
+        <is>
+          <t>w chnou ysir ki ma3ameltch, w chnou ysir ki mch na3mlou haka</t>
+        </is>
+      </c>
+      <c r="H32" s="46" t="inlineStr">
+        <is>
+          <t>consequence_question</t>
+        </is>
+      </c>
+      <c r="I32" s="46" t="inlineStr">
+        <is>
+          <t>what happens if I don't do it this way</t>
+        </is>
+      </c>
+      <c r="J32" s="46" t="inlineStr">
+        <is>
+          <t>que se passe-t-il si je ne le fais pas comme ça</t>
+        </is>
+      </c>
+      <c r="K32" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L32" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1" s="31">
+      <c r="A33" s="45" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C33" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D33" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E33" s="46" t="inlineStr">
+        <is>
+          <t>fin 9alek heka / chnou el marja3</t>
+        </is>
+      </c>
+      <c r="F33" s="46" t="inlineStr">
+        <is>
+          <t>fin 9alek heka</t>
+        </is>
+      </c>
+      <c r="G33" s="46" t="inlineStr">
+        <is>
+          <t>fin l9it heka, fin l9itha, chnou el marja3, chnou el source</t>
+        </is>
+      </c>
+      <c r="H33" s="46" t="inlineStr">
+        <is>
+          <t>source_check</t>
+        </is>
+      </c>
+      <c r="I33" s="46" t="inlineStr">
+        <is>
+          <t>where did you get this / what is your source</t>
+        </is>
+      </c>
+      <c r="J33" s="46" t="inlineStr">
+        <is>
+          <t>d'où tu as trouvé ça / quelle est ta source</t>
+        </is>
+      </c>
+      <c r="K33" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L33" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1" s="31">
+      <c r="A34" s="45" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C34" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D34" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E34" s="46" t="inlineStr">
+        <is>
+          <t>el PDF 9alech / el PDF fih heka</t>
+        </is>
+      </c>
+      <c r="F34" s="46" t="inlineStr">
+        <is>
+          <t>el PDF 9alech</t>
+        </is>
+      </c>
+      <c r="G34" s="46" t="inlineStr">
+        <is>
+          <t>el PDF fih, el PDF 9al, fel PDF mektoub</t>
+        </is>
+      </c>
+      <c r="H34" s="46" t="inlineStr">
+        <is>
+          <t>pdf_reference</t>
+        </is>
+      </c>
+      <c r="I34" s="46" t="inlineStr">
+        <is>
+          <t>the PDF says this / the PDF has this</t>
+        </is>
+      </c>
+      <c r="J34" s="46" t="inlineStr">
+        <is>
+          <t>le PDF dit ça / le PDF contient ça</t>
+        </is>
+      </c>
+      <c r="K34" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L34" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="36" customHeight="1" s="31">
+      <c r="A35" s="45" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C35" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D35" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E35" s="46" t="inlineStr">
+        <is>
+          <t>mch ka heka fel PDF enti 9oltlna ghir</t>
+        </is>
+      </c>
+      <c r="F35" s="46" t="inlineStr">
+        <is>
+          <t>mch ka heka fel PDF</t>
+        </is>
+      </c>
+      <c r="G35" s="46" t="inlineStr">
+        <is>
+          <t>mch kima heka fel PDF, mch haka fel PDF</t>
+        </is>
+      </c>
+      <c r="H35" s="46" t="inlineStr">
+        <is>
+          <t>pdf_mismatch</t>
+        </is>
+      </c>
+      <c r="I35" s="46" t="inlineStr">
+        <is>
+          <t>it's not like that in the PDF you said something different</t>
+        </is>
+      </c>
+      <c r="J35" s="46" t="inlineStr">
+        <is>
+          <t>c'est pas comme ça dans le PDF tu nous as dit autre chose</t>
+        </is>
+      </c>
+      <c r="K35" s="46" t="inlineStr">
+        <is>
+          <t>frustrated</t>
+        </is>
+      </c>
+      <c r="L35" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="36" customHeight="1" s="31">
+      <c r="A36" s="45" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C36" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D36" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E36" s="46" t="inlineStr">
+        <is>
+          <t>rani 9rit el PDF wma fhemtch el juz hedha</t>
+        </is>
+      </c>
+      <c r="F36" s="46" t="inlineStr">
+        <is>
+          <t>rani 9rit el PDF wma fhemtch</t>
+        </is>
+      </c>
+      <c r="G36" s="46" t="inlineStr">
+        <is>
+          <t>rani 9rit wma fhemt, 9rit walakin mafhemtch</t>
+        </is>
+      </c>
+      <c r="H36" s="46" t="inlineStr">
+        <is>
+          <t>pdf_confusion</t>
+        </is>
+      </c>
+      <c r="I36" s="46" t="inlineStr">
+        <is>
+          <t>I read the PDF but didn't understand this part</t>
+        </is>
+      </c>
+      <c r="J36" s="46" t="inlineStr">
+        <is>
+          <t>j'ai lu le PDF mais je n'ai pas compris cette partie</t>
+        </is>
+      </c>
+      <c r="K36" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L36" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="36" customHeight="1" s="31">
+      <c r="A37" s="45" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C37" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D37" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E37" s="46" t="inlineStr">
+        <is>
+          <t>mazelt mafhemtch / mazelt mouch fahm</t>
+        </is>
+      </c>
+      <c r="F37" s="46" t="inlineStr">
+        <is>
+          <t>mazelt mafhemtch</t>
+        </is>
+      </c>
+      <c r="G37" s="46" t="inlineStr">
+        <is>
+          <t>mazelt mouch fahm, mazelt mouch fahma, mazelt mch fahi</t>
+        </is>
+      </c>
+      <c r="H37" s="46" t="inlineStr">
+        <is>
+          <t>persistent_confusion</t>
+        </is>
+      </c>
+      <c r="I37" s="46" t="inlineStr">
+        <is>
+          <t>I still don't understand (masc: fahm / fem: fahma)</t>
+        </is>
+      </c>
+      <c r="J37" s="46" t="inlineStr">
+        <is>
+          <t>je ne comprends toujours pas</t>
+        </is>
+      </c>
+      <c r="K37" s="46" t="inlineStr">
+        <is>
+          <t>frustrated</t>
+        </is>
+      </c>
+      <c r="L37" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="36" customHeight="1" s="31">
+      <c r="A38" s="45" t="n">
+        <v>35</v>
+      </c>
+      <c r="B38" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C38" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D38" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E38" s="46" t="inlineStr">
+        <is>
+          <t>ma 3andi 7ata fekra 3la heka</t>
+        </is>
+      </c>
+      <c r="F38" s="46" t="inlineStr">
+        <is>
+          <t>ma 3andi 7ata fekra</t>
+        </is>
+      </c>
+      <c r="G38" s="46" t="inlineStr">
+        <is>
+          <t>ma3andich 7ata fekra, ma3andi fikra</t>
+        </is>
+      </c>
+      <c r="H38" s="46" t="inlineStr">
+        <is>
+          <t>persistent_confusion</t>
+        </is>
+      </c>
+      <c r="I38" s="46" t="inlineStr">
+        <is>
+          <t>I have absolutely no idea about this</t>
+        </is>
+      </c>
+      <c r="J38" s="46" t="inlineStr">
+        <is>
+          <t>je n'ai absolument aucune idée de ça</t>
+        </is>
+      </c>
+      <c r="K38" s="46" t="inlineStr">
+        <is>
+          <t>frustrated</t>
+        </is>
+      </c>
+      <c r="L38" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="36" customHeight="1" s="31">
+      <c r="A39" s="45" t="n">
+        <v>36</v>
+      </c>
+      <c r="B39" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C39" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D39" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E39" s="46" t="inlineStr">
+        <is>
+          <t>lmawdhou3 s3ib barcha mch 9ader nfhem</t>
+        </is>
+      </c>
+      <c r="F39" s="46" t="inlineStr">
+        <is>
+          <t>lmawdhou3 s3ib</t>
+        </is>
+      </c>
+      <c r="G39" s="46" t="inlineStr">
+        <is>
+          <t>el mawdhou3 s3ib, heka s3ib barcha</t>
+        </is>
+      </c>
+      <c r="H39" s="46" t="inlineStr">
+        <is>
+          <t>giving_up</t>
+        </is>
+      </c>
+      <c r="I39" s="46" t="inlineStr">
+        <is>
+          <t>the topic is very hard I can't understand</t>
+        </is>
+      </c>
+      <c r="J39" s="46" t="inlineStr">
+        <is>
+          <t>le sujet est très difficile je n'arrive pas à comprendre</t>
+        </is>
+      </c>
+      <c r="K39" s="46" t="inlineStr">
+        <is>
+          <t>frustrated</t>
+        </is>
+      </c>
+      <c r="L39" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="36" customHeight="1" s="31">
+      <c r="A40" s="45" t="n">
+        <v>37</v>
+      </c>
+      <c r="B40" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C40" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D40" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E40" s="46" t="inlineStr">
+        <is>
+          <t>ma3adich nfhem 5aliha</t>
+        </is>
+      </c>
+      <c r="F40" s="46" t="inlineStr">
+        <is>
+          <t>ma3adich nfhem</t>
+        </is>
+      </c>
+      <c r="G40" s="46" t="inlineStr">
+        <is>
+          <t>ma3adich nfhm, 5ali, 5aliha, 5alinha</t>
+        </is>
+      </c>
+      <c r="H40" s="46" t="inlineStr">
+        <is>
+          <t>giving_up</t>
+        </is>
+      </c>
+      <c r="I40" s="46" t="inlineStr">
+        <is>
+          <t>I can't understand anymore forget it</t>
+        </is>
+      </c>
+      <c r="J40" s="46" t="inlineStr">
+        <is>
+          <t>je n'arrive plus à comprendre laisse tomber</t>
+        </is>
+      </c>
+      <c r="K40" s="46" t="inlineStr">
+        <is>
+          <t>aggressive</t>
+        </is>
+      </c>
+      <c r="L40" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="36" customHeight="1" s="31">
+      <c r="A41" s="45" t="n">
+        <v>38</v>
+      </c>
+      <c r="B41" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C41" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D41" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E41" s="46" t="inlineStr">
+        <is>
+          <t>merci barcha t3ebt m3aya</t>
+        </is>
+      </c>
+      <c r="F41" s="46" t="inlineStr">
+        <is>
+          <t>merci barcha</t>
+        </is>
+      </c>
+      <c r="G41" s="46" t="inlineStr">
+        <is>
+          <t>merci bien, t3ebt m3aya, barak allahou fik, yaishek</t>
+        </is>
+      </c>
+      <c r="H41" s="46" t="inlineStr">
+        <is>
+          <t>closing_thanks</t>
+        </is>
+      </c>
+      <c r="I41" s="46" t="inlineStr">
+        <is>
+          <t>thank you very much you worked hard with me</t>
+        </is>
+      </c>
+      <c r="J41" s="46" t="inlineStr">
+        <is>
+          <t>merci beaucoup tu as bien travaillé avec moi</t>
+        </is>
+      </c>
+      <c r="K41" s="46" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="L41" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="36" customHeight="1" s="31">
+      <c r="A42" s="45" t="n">
+        <v>39</v>
+      </c>
+      <c r="B42" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C42" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D42" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E42" s="46" t="inlineStr">
+        <is>
+          <t>waw barcha / heka behi / mrigla</t>
+        </is>
+      </c>
+      <c r="F42" s="46" t="inlineStr">
+        <is>
+          <t>waw barcha</t>
+        </is>
+      </c>
+      <c r="G42" s="46" t="inlineStr">
+        <is>
+          <t>waw, waw barcha, heka behi, heka zin, mrigla, mrgl, sa7a</t>
+        </is>
+      </c>
+      <c r="H42" s="46" t="inlineStr">
+        <is>
+          <t>encouragement</t>
+        </is>
+      </c>
+      <c r="I42" s="46" t="inlineStr">
+        <is>
+          <t>wow amazing this is great (praise for good answer)</t>
+        </is>
+      </c>
+      <c r="J42" s="46" t="inlineStr">
+        <is>
+          <t>wow incroyable c'est super (éloge pour bonne réponse)</t>
+        </is>
+      </c>
+      <c r="K42" s="46" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="L42" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="36" customHeight="1" s="31">
+      <c r="A43" s="45" t="n">
+        <v>40</v>
+      </c>
+      <c r="B43" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C43" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D43" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E43" s="46" t="inlineStr">
+        <is>
+          <t>bichwaya bichwaya fassarly kifeh maaneha</t>
+        </is>
+      </c>
+      <c r="F43" s="46" t="inlineStr">
+        <is>
+          <t>bichwaya bichwaya</t>
+        </is>
+      </c>
+      <c r="G43" s="46" t="inlineStr">
+        <is>
+          <t>bchwaya bchwaya, bishwaya, bichwaya bichwaya</t>
+        </is>
+      </c>
+      <c r="H43" s="46" t="inlineStr">
+        <is>
+          <t>simplify</t>
+        </is>
+      </c>
+      <c r="I43" s="46" t="inlineStr">
+        <is>
+          <t>slowly step by step explain it to me</t>
+        </is>
+      </c>
+      <c r="J43" s="46" t="inlineStr">
+        <is>
+          <t>doucement étape par étape explique-moi</t>
+        </is>
+      </c>
+      <c r="K43" s="46" t="inlineStr">
+        <is>
+          <t>polite</t>
+        </is>
+      </c>
+      <c r="L43" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1654,7 +4484,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF0369A1"/>
@@ -1909,21 +4739,22 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF7C3AED"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" style="31" min="1" max="1"/>
+    <col width="24" customWidth="1" style="31" min="1" max="1"/>
     <col width="10" customWidth="1" style="31" min="2" max="2"/>
-    <col width="25" customWidth="1" style="31" min="3" max="3"/>
-    <col width="38" customWidth="1" style="31" min="4" max="5"/>
-    <col width="40" customWidth="1" style="31" min="6" max="6"/>
+    <col width="46" customWidth="1" style="31" min="3" max="3"/>
+    <col width="46" customWidth="1" style="31" min="4" max="5"/>
+    <col width="40" customWidth="1" style="31" min="5" max="5"/>
+    <col width="54" customWidth="1" style="31" min="6" max="6"/>
     <col width="14" customWidth="1" style="31" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2404,6 +5235,366 @@
         </is>
       </c>
       <c r="G16" s="24" t="n"/>
+    </row>
+    <row r="17" ht="40" customHeight="1" s="31">
+      <c r="A17" s="45" t="inlineStr">
+        <is>
+          <t>continue_deeper</t>
+        </is>
+      </c>
+      <c r="B17" s="45" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C17" s="46" t="inlineStr">
+        <is>
+          <t>w ba3d, zid, 3tini plus de détails</t>
+        </is>
+      </c>
+      <c r="D17" s="46" t="inlineStr">
+        <is>
+          <t>wba3d, wba3dha, zidli, 3tini akthar détails</t>
+        </is>
+      </c>
+      <c r="E17" s="46" t="inlineStr">
+        <is>
+          <t>wba3d,zid,3tiniplusdedetails</t>
+        </is>
+      </c>
+      <c r="F17" s="46" t="inlineStr">
+        <is>
+          <t>Continue explanation — go deeper into the topic</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="40" customHeight="1" s="31">
+      <c r="A18" s="45" t="inlineStr">
+        <is>
+          <t>clarification_question</t>
+        </is>
+      </c>
+      <c r="B18" s="45" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C18" s="46" t="inlineStr">
+        <is>
+          <t>bch nfhem, kifeh maaneha, w kifeh nesta3mlouha</t>
+        </is>
+      </c>
+      <c r="D18" s="46" t="inlineStr">
+        <is>
+          <t>bich nfhem, bach nfhem, kifeh maanaha, kifeh nesta3milha</t>
+        </is>
+      </c>
+      <c r="E18" s="46" t="inlineStr">
+        <is>
+          <t>bchnfhem,kifehmaaneha,wkifeh</t>
+        </is>
+      </c>
+      <c r="F18" s="46" t="inlineStr">
+        <is>
+          <t>Answer the specific sub-question before continuing</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="40" customHeight="1" s="31">
+      <c r="A19" s="45" t="inlineStr">
+        <is>
+          <t>why_question</t>
+        </is>
+      </c>
+      <c r="B19" s="45" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C19" s="46" t="inlineStr">
+        <is>
+          <t>3lech heka, 3lech haka, w 3leh lazm naaml kk</t>
+        </is>
+      </c>
+      <c r="D19" s="46" t="inlineStr">
+        <is>
+          <t>3leh heka, 3leh lazm naaml haka, lech heka</t>
+        </is>
+      </c>
+      <c r="E19" s="46" t="inlineStr">
+        <is>
+          <t>3lechheka,3lechhaka,3lehlazm</t>
+        </is>
+      </c>
+      <c r="F19" s="46" t="inlineStr">
+        <is>
+          <t>Explain the reason/rationale behind the concept</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="40" customHeight="1" s="31">
+      <c r="A20" s="45" t="inlineStr">
+        <is>
+          <t>compare_question</t>
+        </is>
+      </c>
+      <c r="B20" s="45" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C20" s="46" t="inlineStr">
+        <is>
+          <t>w chnou el farq bin X w Y</t>
+        </is>
+      </c>
+      <c r="D20" s="46" t="inlineStr">
+        <is>
+          <t>chnou el farq, chnoa el farq, kifeh ykhtalf, ma farqhom</t>
+        </is>
+      </c>
+      <c r="E20" s="46" t="inlineStr">
+        <is>
+          <t>chnouElfarq,kifehhykhtalf</t>
+        </is>
+      </c>
+      <c r="F20" s="46" t="inlineStr">
+        <is>
+          <t>Give definition + key difference + example</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="40" customHeight="1" s="31">
+      <c r="A21" s="45" t="inlineStr">
+        <is>
+          <t>definition_question</t>
+        </is>
+      </c>
+      <c r="B21" s="45" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C21" s="46" t="inlineStr">
+        <is>
+          <t>kifeh maaneha, chnou ya3ni X</t>
+        </is>
+      </c>
+      <c r="D21" s="46" t="inlineStr">
+        <is>
+          <t>kifeh maanaha, kifeh ma3neha, chnou maaneha</t>
+        </is>
+      </c>
+      <c r="E21" s="46" t="inlineStr">
+        <is>
+          <t>kifehmaaneha,chnoumaaneha</t>
+        </is>
+      </c>
+      <c r="F21" s="46" t="inlineStr">
+        <is>
+          <t>Short definition first then real Tunisian example</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1" s="31">
+      <c r="A22" s="45" t="inlineStr">
+        <is>
+          <t>consequence_question</t>
+        </is>
+      </c>
+      <c r="B22" s="45" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="C22" s="46" t="inlineStr">
+        <is>
+          <t>w chnoa ysir ki mana3milch kk</t>
+        </is>
+      </c>
+      <c r="D22" s="46" t="inlineStr">
+        <is>
+          <t>w chnou ysir ki ma3ameltch, ki mch na3mlou haka</t>
+        </is>
+      </c>
+      <c r="E22" s="46" t="inlineStr">
+        <is>
+          <t>chnoa ysir,chnou ysir,mana3milch</t>
+        </is>
+      </c>
+      <c r="F22" s="46" t="inlineStr">
+        <is>
+          <t>Explain consequence of not applying the concept</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="40" customHeight="1" s="31">
+      <c r="A23" s="45" t="inlineStr">
+        <is>
+          <t>source_check</t>
+        </is>
+      </c>
+      <c r="B23" s="45" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C23" s="46" t="inlineStr">
+        <is>
+          <t>fin 9alek heka, chnou el marja3, chnou el source</t>
+        </is>
+      </c>
+      <c r="D23" s="46" t="inlineStr">
+        <is>
+          <t>fin l9it heka, fin l9itha, chnou el source</t>
+        </is>
+      </c>
+      <c r="E23" s="46" t="inlineStr">
+        <is>
+          <t>fin9alek,chnouelmarja3</t>
+        </is>
+      </c>
+      <c r="F23" s="46" t="inlineStr">
+        <is>
+          <t>Cite the PDF section — be transparent about RAG source</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="40" customHeight="1" s="31">
+      <c r="A24" s="45" t="inlineStr">
+        <is>
+          <t>pdf_reference</t>
+        </is>
+      </c>
+      <c r="B24" s="45" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C24" s="46" t="inlineStr">
+        <is>
+          <t>el PDF 9alech, el PDF fih</t>
+        </is>
+      </c>
+      <c r="D24" s="46" t="inlineStr">
+        <is>
+          <t>el PDF 9al, fel PDF mektoub, el PDF fih ghir</t>
+        </is>
+      </c>
+      <c r="E24" s="46" t="inlineStr">
+        <is>
+          <t>elpdf9alech,elpdffih</t>
+        </is>
+      </c>
+      <c r="F24" s="46" t="inlineStr">
+        <is>
+          <t>Acknowledge — confirm or clarify what the PDF says</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="40" customHeight="1" s="31">
+      <c r="A25" s="45" t="inlineStr">
+        <is>
+          <t>pdf_mismatch</t>
+        </is>
+      </c>
+      <c r="B25" s="45" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C25" s="46" t="inlineStr">
+        <is>
+          <t>mch ka heka fel PDF, heka mch mektoub fel PDF</t>
+        </is>
+      </c>
+      <c r="D25" s="46" t="inlineStr">
+        <is>
+          <t>mch kima heka fel PDF, mch haka fel PDF</t>
+        </is>
+      </c>
+      <c r="E25" s="46" t="inlineStr">
+        <is>
+          <t>mchkahekafelpdf,mchkimaheka</t>
+        </is>
+      </c>
+      <c r="F25" s="46" t="inlineStr">
+        <is>
+          <t>Apologize — re-read RAG chunk and correct the answer</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="40" customHeight="1" s="31">
+      <c r="A26" s="45" t="inlineStr">
+        <is>
+          <t>pdf_confusion</t>
+        </is>
+      </c>
+      <c r="B26" s="45" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="C26" s="46" t="inlineStr">
+        <is>
+          <t>rani 9rit el PDF wma fhemtch</t>
+        </is>
+      </c>
+      <c r="D26" s="46" t="inlineStr">
+        <is>
+          <t>rani 9rit wma fhemt, 9rit el PDF walakin mafhemtch</t>
+        </is>
+      </c>
+      <c r="E26" s="46" t="inlineStr">
+        <is>
+          <t>rani9rit,9ritelPDF,wmafhem</t>
+        </is>
+      </c>
+      <c r="F26" s="46" t="inlineStr">
+        <is>
+          <t>Acknowledge they read it — explain step by step</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="40" customHeight="1" s="31">
+      <c r="A27" s="45" t="inlineStr">
+        <is>
+          <t>persistent_confusion</t>
+        </is>
+      </c>
+      <c r="B27" s="45" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="C27" s="46" t="inlineStr">
+        <is>
+          <t>mazelt mafhemtch, mazelt mouch fahm, ma 3andi 7ata fekra</t>
+        </is>
+      </c>
+      <c r="D27" s="46" t="inlineStr">
+        <is>
+          <t>mazelt mouch fahma, mazelt mch fahi, ma3andich 7ata fekra</t>
+        </is>
+      </c>
+      <c r="E27" s="46" t="inlineStr">
+        <is>
+          <t>mazeltmafhemtch,mazeltmouch,ma3andi7ata</t>
+        </is>
+      </c>
+      <c r="F27" s="46" t="inlineStr">
+        <is>
+          <t>Switch strategy: analogy + schema + bichwaya bichwaya</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1" s="31">
+      <c r="A28" s="45" t="inlineStr">
+        <is>
+          <t>closing_thanks</t>
+        </is>
+      </c>
+      <c r="B28" s="45" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="C28" s="46" t="inlineStr">
+        <is>
+          <t>merci barcha, t3ebt m3aya, barak allahou fik</t>
+        </is>
+      </c>
+      <c r="D28" s="46" t="inlineStr">
+        <is>
+          <t>merci bien, yaishek, 3aychek</t>
+        </is>
+      </c>
+      <c r="E28" s="46" t="inlineStr">
+        <is>
+          <t>mercibarcha,t3ebtm3aya,barakallahou</t>
+        </is>
+      </c>
+      <c r="F28" s="46" t="inlineStr">
+        <is>
+          <t>Warm close — confirm understanding, offer to continue</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2413,7 +5604,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF16A34A"/>
@@ -2500,20 +5691,20 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FFD97706"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" style="31" min="1" max="1"/>
-    <col width="14" customWidth="1" style="31" min="2" max="2"/>
-    <col width="12" customWidth="1" style="31" min="3" max="3"/>
-    <col width="14" customWidth="1" style="31" min="4" max="4"/>
+    <col width="26" customWidth="1" style="31" min="1" max="1"/>
+    <col width="12" customWidth="1" style="31" min="2" max="2"/>
+    <col width="10" customWidth="1" style="31" min="3" max="3"/>
+    <col width="16" customWidth="1" style="31" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="31">
@@ -2551,15 +5742,15 @@
           <t>confusion</t>
         </is>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="47">
         <f>COUNTIF('Raw Collection'!H:H,A3)</f>
         <v/>
       </c>
       <c r="C3" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="D3" s="2">
-        <f>IF(B3&gt;=C3,"✅ Done",IF(B3&gt;=C3*0.5,"🔶 Halfway","⬜ Needed"))</f>
+      <c r="D3" s="47">
+        <f>IF(B3&gt;=C3,"✅ Done",IF(B3=0,"🔴 Empty","🟡 In Progress"))</f>
         <v/>
       </c>
     </row>
@@ -2569,15 +5760,15 @@
           <t>understood</t>
         </is>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="48">
         <f>COUNTIF('Raw Collection'!H:H,A4)</f>
         <v/>
       </c>
       <c r="C4" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="D4" s="4">
-        <f>IF(B4&gt;=C4,"✅ Done",IF(B4&gt;=C4*0.5,"🔶 Halfway","⬜ Needed"))</f>
+      <c r="D4" s="48">
+        <f>IF(B4&gt;=C4,"✅ Done",IF(B4=0,"🔴 Empty","🟡 In Progress"))</f>
         <v/>
       </c>
     </row>
@@ -2587,15 +5778,15 @@
           <t>half_understood</t>
         </is>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="47">
         <f>COUNTIF('Raw Collection'!H:H,A5)</f>
         <v/>
       </c>
       <c r="C5" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D5" s="2">
-        <f>IF(B5&gt;=C5,"✅ Done",IF(B5&gt;=C5*0.5,"🔶 Halfway","⬜ Needed"))</f>
+      <c r="D5" s="47">
+        <f>IF(B5&gt;=C5,"✅ Done",IF(B5=0,"🔴 Empty","🟡 In Progress"))</f>
         <v/>
       </c>
     </row>
@@ -2605,15 +5796,15 @@
           <t>repeat</t>
         </is>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="48">
         <f>COUNTIF('Raw Collection'!H:H,A6)</f>
         <v/>
       </c>
       <c r="C6" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="D6" s="4">
-        <f>IF(B6&gt;=C6,"✅ Done",IF(B6&gt;=C6*0.5,"🔶 Halfway","⬜ Needed"))</f>
+      <c r="D6" s="48">
+        <f>IF(B6&gt;=C6,"✅ Done",IF(B6=0,"🔴 Empty","🟡 In Progress"))</f>
         <v/>
       </c>
     </row>
@@ -2623,15 +5814,15 @@
           <t>repeat_all</t>
         </is>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="47">
         <f>COUNTIF('Raw Collection'!H:H,A7)</f>
         <v/>
       </c>
       <c r="C7" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="D7" s="2">
-        <f>IF(B7&gt;=C7,"✅ Done",IF(B7&gt;=C7*0.5,"🔶 Halfway","⬜ Needed"))</f>
+      <c r="D7" s="47">
+        <f>IF(B7&gt;=C7,"✅ Done",IF(B7=0,"🔴 Empty","🟡 In Progress"))</f>
         <v/>
       </c>
     </row>
@@ -2641,15 +5832,15 @@
           <t>repeat_part</t>
         </is>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="48">
         <f>COUNTIF('Raw Collection'!H:H,A8)</f>
         <v/>
       </c>
       <c r="C8" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="D8" s="4">
-        <f>IF(B8&gt;=C8,"✅ Done",IF(B8&gt;=C8*0.5,"🔶 Halfway","⬜ Needed"))</f>
+      <c r="D8" s="48">
+        <f>IF(B8&gt;=C8,"✅ Done",IF(B8=0,"🔴 Empty","🟡 In Progress"))</f>
         <v/>
       </c>
     </row>
@@ -2659,15 +5850,15 @@
           <t>simplify</t>
         </is>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="47">
         <f>COUNTIF('Raw Collection'!H:H,A9)</f>
         <v/>
       </c>
       <c r="C9" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D9" s="2">
-        <f>IF(B9&gt;=C9,"✅ Done",IF(B9&gt;=C9*0.5,"🔶 Halfway","⬜ Needed"))</f>
+      <c r="D9" s="47">
+        <f>IF(B9&gt;=C9,"✅ Done",IF(B9=0,"🔴 Empty","🟡 In Progress"))</f>
         <v/>
       </c>
     </row>
@@ -2677,15 +5868,15 @@
           <t>hallucination</t>
         </is>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="48">
         <f>COUNTIF('Raw Collection'!H:H,A10)</f>
         <v/>
       </c>
       <c r="C10" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="D10" s="4">
-        <f>IF(B10&gt;=C10,"✅ Done",IF(B10&gt;=C10*0.5,"🔶 Halfway","⬜ Needed"))</f>
+      <c r="D10" s="48">
+        <f>IF(B10&gt;=C10,"✅ Done",IF(B10=0,"🔴 Empty","🟡 In Progress"))</f>
         <v/>
       </c>
     </row>
@@ -2695,15 +5886,15 @@
           <t>wrong_answer</t>
         </is>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="47">
         <f>COUNTIF('Raw Collection'!H:H,A11)</f>
         <v/>
       </c>
       <c r="C11" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D11" s="2">
-        <f>IF(B11&gt;=C11,"✅ Done",IF(B11&gt;=C11*0.5,"🔶 Halfway","⬜ Needed"))</f>
+      <c r="D11" s="47">
+        <f>IF(B11&gt;=C11,"✅ Done",IF(B11=0,"🔴 Empty","🟡 In Progress"))</f>
         <v/>
       </c>
     </row>
@@ -2713,15 +5904,15 @@
           <t>giving_up</t>
         </is>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="48">
         <f>COUNTIF('Raw Collection'!H:H,A12)</f>
         <v/>
       </c>
       <c r="C12" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="D12" s="4">
-        <f>IF(B12&gt;=C12,"✅ Done",IF(B12&gt;=C12*0.5,"🔶 Halfway","⬜ Needed"))</f>
+      <c r="D12" s="48">
+        <f>IF(B12&gt;=C12,"✅ Done",IF(B12=0,"🔴 Empty","🟡 In Progress"))</f>
         <v/>
       </c>
     </row>
@@ -2731,15 +5922,15 @@
           <t>impatience</t>
         </is>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="47">
         <f>COUNTIF('Raw Collection'!H:H,A13)</f>
         <v/>
       </c>
       <c r="C13" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="D13" s="2">
-        <f>IF(B13&gt;=C13,"✅ Done",IF(B13&gt;=C13*0.5,"🔶 Halfway","⬜ Needed"))</f>
+      <c r="D13" s="47">
+        <f>IF(B13&gt;=C13,"✅ Done",IF(B13=0,"🔴 Empty","🟡 In Progress"))</f>
         <v/>
       </c>
     </row>
@@ -2749,15 +5940,15 @@
           <t>pushback</t>
         </is>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="48">
         <f>COUNTIF('Raw Collection'!H:H,A14)</f>
         <v/>
       </c>
       <c r="C14" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="D14" s="4">
-        <f>IF(B14&gt;=C14,"✅ Done",IF(B14&gt;=C14*0.5,"🔶 Halfway","⬜ Needed"))</f>
+      <c r="D14" s="48">
+        <f>IF(B14&gt;=C14,"✅ Done",IF(B14=0,"🔴 Empty","🟡 In Progress"))</f>
         <v/>
       </c>
     </row>
@@ -2767,15 +5958,15 @@
           <t>encouragement</t>
         </is>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="47">
         <f>COUNTIF('Raw Collection'!H:H,A15)</f>
         <v/>
       </c>
       <c r="C15" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D15" s="2">
-        <f>IF(B15&gt;=C15,"✅ Done",IF(B15&gt;=C15*0.5,"🔶 Halfway","⬜ Needed"))</f>
+      <c r="D15" s="47">
+        <f>IF(B15&gt;=C15,"✅ Done",IF(B15=0,"🔴 Empty","🟡 In Progress"))</f>
         <v/>
       </c>
     </row>
@@ -2785,8 +5976,8 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B16" s="29">
-        <f>SUM(B3:B15)</f>
+      <c r="B16" s="49">
+        <f>SUM(B3:B30)</f>
         <v/>
       </c>
       <c r="C16" s="29">
@@ -2795,6 +5986,222 @@
       </c>
       <c r="D16" s="29">
         <f>IF(B16&gt;=C16,"✅ Complete","⬜ In Progress")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1" s="31">
+      <c r="A17" s="46" t="inlineStr">
+        <is>
+          <t>continue_deeper</t>
+        </is>
+      </c>
+      <c r="B17" s="45">
+        <f>COUNTIF('Raw Collection'!H:H,A17)</f>
+        <v/>
+      </c>
+      <c r="C17" s="45" t="n">
+        <v>25</v>
+      </c>
+      <c r="D17" s="45">
+        <f>IF(B17&gt;=C17,"✅ Done",IF(B17=0,"🔴 Empty","🟡 In Progress"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="31">
+      <c r="A18" s="46" t="inlineStr">
+        <is>
+          <t>clarification_question</t>
+        </is>
+      </c>
+      <c r="B18" s="45">
+        <f>COUNTIF('Raw Collection'!H:H,A18)</f>
+        <v/>
+      </c>
+      <c r="C18" s="45" t="n">
+        <v>30</v>
+      </c>
+      <c r="D18" s="45">
+        <f>IF(B18&gt;=C18,"✅ Done",IF(B18=0,"🔴 Empty","🟡 In Progress"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="31">
+      <c r="A19" s="46" t="inlineStr">
+        <is>
+          <t>why_question</t>
+        </is>
+      </c>
+      <c r="B19" s="45">
+        <f>COUNTIF('Raw Collection'!H:H,A19)</f>
+        <v/>
+      </c>
+      <c r="C19" s="45" t="n">
+        <v>25</v>
+      </c>
+      <c r="D19" s="45">
+        <f>IF(B19&gt;=C19,"✅ Done",IF(B19=0,"🔴 Empty","🟡 In Progress"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1" s="31">
+      <c r="A20" s="46" t="inlineStr">
+        <is>
+          <t>compare_question</t>
+        </is>
+      </c>
+      <c r="B20" s="45">
+        <f>COUNTIF('Raw Collection'!H:H,A20)</f>
+        <v/>
+      </c>
+      <c r="C20" s="45" t="n">
+        <v>25</v>
+      </c>
+      <c r="D20" s="45">
+        <f>IF(B20&gt;=C20,"✅ Done",IF(B20=0,"🔴 Empty","🟡 In Progress"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1" s="31">
+      <c r="A21" s="46" t="inlineStr">
+        <is>
+          <t>definition_question</t>
+        </is>
+      </c>
+      <c r="B21" s="45">
+        <f>COUNTIF('Raw Collection'!H:H,A21)</f>
+        <v/>
+      </c>
+      <c r="C21" s="45" t="n">
+        <v>25</v>
+      </c>
+      <c r="D21" s="45">
+        <f>IF(B21&gt;=C21,"✅ Done",IF(B21=0,"🔴 Empty","🟡 In Progress"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1" s="31">
+      <c r="A22" s="46" t="inlineStr">
+        <is>
+          <t>consequence_question</t>
+        </is>
+      </c>
+      <c r="B22" s="45">
+        <f>COUNTIF('Raw Collection'!H:H,A22)</f>
+        <v/>
+      </c>
+      <c r="C22" s="45" t="n">
+        <v>20</v>
+      </c>
+      <c r="D22" s="45">
+        <f>IF(B22&gt;=C22,"✅ Done",IF(B22=0,"🔴 Empty","🟡 In Progress"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1" s="31">
+      <c r="A23" s="46" t="inlineStr">
+        <is>
+          <t>source_check</t>
+        </is>
+      </c>
+      <c r="B23" s="45">
+        <f>COUNTIF('Raw Collection'!H:H,A23)</f>
+        <v/>
+      </c>
+      <c r="C23" s="45" t="n">
+        <v>20</v>
+      </c>
+      <c r="D23" s="45">
+        <f>IF(B23&gt;=C23,"✅ Done",IF(B23=0,"🔴 Empty","🟡 In Progress"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1" s="31">
+      <c r="A24" s="46" t="inlineStr">
+        <is>
+          <t>pdf_reference</t>
+        </is>
+      </c>
+      <c r="B24" s="45">
+        <f>COUNTIF('Raw Collection'!H:H,A24)</f>
+        <v/>
+      </c>
+      <c r="C24" s="45" t="n">
+        <v>20</v>
+      </c>
+      <c r="D24" s="45">
+        <f>IF(B24&gt;=C24,"✅ Done",IF(B24=0,"🔴 Empty","🟡 In Progress"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1" s="31">
+      <c r="A25" s="46" t="inlineStr">
+        <is>
+          <t>pdf_mismatch</t>
+        </is>
+      </c>
+      <c r="B25" s="45">
+        <f>COUNTIF('Raw Collection'!H:H,A25)</f>
+        <v/>
+      </c>
+      <c r="C25" s="45" t="n">
+        <v>20</v>
+      </c>
+      <c r="D25" s="45">
+        <f>IF(B25&gt;=C25,"✅ Done",IF(B25=0,"🔴 Empty","🟡 In Progress"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1" s="31">
+      <c r="A26" s="46" t="inlineStr">
+        <is>
+          <t>pdf_confusion</t>
+        </is>
+      </c>
+      <c r="B26" s="45">
+        <f>COUNTIF('Raw Collection'!H:H,A26)</f>
+        <v/>
+      </c>
+      <c r="C26" s="45" t="n">
+        <v>20</v>
+      </c>
+      <c r="D26" s="45">
+        <f>IF(B26&gt;=C26,"✅ Done",IF(B26=0,"🔴 Empty","🟡 In Progress"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1" s="31">
+      <c r="A27" s="46" t="inlineStr">
+        <is>
+          <t>persistent_confusion</t>
+        </is>
+      </c>
+      <c r="B27" s="45">
+        <f>COUNTIF('Raw Collection'!H:H,A27)</f>
+        <v/>
+      </c>
+      <c r="C27" s="45" t="n">
+        <v>30</v>
+      </c>
+      <c r="D27" s="45">
+        <f>IF(B27&gt;=C27,"✅ Done",IF(B27=0,"🔴 Empty","🟡 In Progress"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1" s="31">
+      <c r="A28" s="46" t="inlineStr">
+        <is>
+          <t>closing_thanks</t>
+        </is>
+      </c>
+      <c r="B28" s="45">
+        <f>COUNTIF('Raw Collection'!H:H,A28)</f>
+        <v/>
+      </c>
+      <c r="C28" s="45" t="n">
+        <v>20</v>
+      </c>
+      <c r="D28" s="45">
+        <f>IF(B28&gt;=C28,"✅ Done",IF(B28=0,"🔴 Empty","🟡 In Progress"))</f>
         <v/>
       </c>
     </row>
@@ -2804,4 +6211,1126 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" style="31" min="1" max="1"/>
+    <col width="46" customWidth="1" style="31" min="2" max="2"/>
+    <col width="42" customWidth="1" style="31" min="3" max="3"/>
+    <col width="28" customWidth="1" style="31" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" s="31">
+      <c r="A1" s="50" t="inlineStr">
+        <is>
+          <t>🤖  Bot Behavior Guide — Built from Native Tunisian Speaker</t>
+        </is>
+      </c>
+      <c r="B1" s="56" t="n"/>
+      <c r="C1" s="56" t="n"/>
+      <c r="D1" s="57" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1" s="31">
+      <c r="A2" s="51" t="inlineStr">
+        <is>
+          <t>EXPLANATION STRUCTURE — always in this order</t>
+        </is>
+      </c>
+      <c r="B2" s="56" t="n"/>
+      <c r="C2" s="56" t="n"/>
+      <c r="D2" s="57" t="n"/>
+    </row>
+    <row r="3" ht="20" customHeight="1" s="31">
+      <c r="A3" s="52" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B3" s="52" t="inlineStr">
+        <is>
+          <t>What the bot does</t>
+        </is>
+      </c>
+      <c r="C3" s="52" t="inlineStr">
+        <is>
+          <t>Darija connector</t>
+        </is>
+      </c>
+      <c r="D3" s="52" t="inlineStr">
+        <is>
+          <t>Example</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1" s="31">
+      <c r="A4" s="45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="46" t="inlineStr">
+        <is>
+          <t>Short definition first (ta3rif 9sir)</t>
+        </is>
+      </c>
+      <c r="C4" s="46" t="inlineStr">
+        <is>
+          <t>rit milloul...</t>
+        </is>
+      </c>
+      <c r="D4" s="46" t="inlineStr">
+        <is>
+          <t>"rit milloul, el machine learning ya3ni..."</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1" s="31">
+      <c r="A5" s="45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" s="46" t="inlineStr">
+        <is>
+          <t>Real Tunisian life example (mitha reel tounsi)</t>
+        </is>
+      </c>
+      <c r="C5" s="46" t="inlineStr">
+        <is>
+          <t>...mba3d...</t>
+        </is>
+      </c>
+      <c r="D5" s="46" t="inlineStr">
+        <is>
+          <t>"mba3d, 9abbel kima 3andek 7anout..."</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1" s="31">
+      <c r="A6" s="45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" s="46" t="inlineStr">
+        <is>
+          <t>How to use it in practice (kifeh nesta3mlouha)</t>
+        </is>
+      </c>
+      <c r="C6" s="46" t="inlineStr">
+        <is>
+          <t>...fil le5er</t>
+        </is>
+      </c>
+      <c r="D6" s="46" t="inlineStr">
+        <is>
+          <t>"fil le5er, nesta3mlouha bch..."</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1" s="31">
+      <c r="A8" s="51" t="inlineStr">
+        <is>
+          <t>LANGUAGE MIX RULES</t>
+        </is>
+      </c>
+      <c r="B8" s="56" t="n"/>
+      <c r="C8" s="56" t="n"/>
+      <c r="D8" s="57" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1" s="31">
+      <c r="A9" s="52" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="B9" s="52" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C9" s="52" t="inlineStr">
+        <is>
+          <t>Example</t>
+        </is>
+      </c>
+      <c r="D9" s="52" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1" s="31">
+      <c r="A10" s="45" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="B10" s="46" t="inlineStr">
+        <is>
+          <t>Darija base + French/English technical terms</t>
+        </is>
+      </c>
+      <c r="C10" s="46" t="inlineStr">
+        <is>
+          <t>"el model ya3ni...", "le dataset hedha"</t>
+        </is>
+      </c>
+      <c r="D10" s="46" t="inlineStr">
+        <is>
+          <t>Adapt to user's dominant language</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1" s="31">
+      <c r="A11" s="45" t="inlineStr">
+        <is>
+          <t>French-heavy user</t>
+        </is>
+      </c>
+      <c r="B11" s="46" t="inlineStr">
+        <is>
+          <t>Mirror their French ratio in responses</t>
+        </is>
+      </c>
+      <c r="C11" s="46" t="inlineStr">
+        <is>
+          <t>If they write in French → more French</t>
+        </is>
+      </c>
+      <c r="D11" s="46" t="inlineStr">
+        <is>
+          <t>Follow the student</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1" s="31">
+      <c r="A12" s="45" t="inlineStr">
+        <is>
+          <t>English-heavy user</t>
+        </is>
+      </c>
+      <c r="B12" s="46" t="inlineStr">
+        <is>
+          <t>Mirror their English ratio in responses</t>
+        </is>
+      </c>
+      <c r="C12" s="46" t="inlineStr">
+        <is>
+          <t>If they write in English → more English</t>
+        </is>
+      </c>
+      <c r="D12" s="46" t="inlineStr">
+        <is>
+          <t>Follow the student</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1" s="31">
+      <c r="A13" s="45" t="inlineStr">
+        <is>
+          <t>fassarly b darija request</t>
+        </is>
+      </c>
+      <c r="B13" s="46" t="inlineStr">
+        <is>
+          <t>Go full Darija — no French/English terms</t>
+        </is>
+      </c>
+      <c r="C13" s="46" t="inlineStr">
+        <is>
+          <t>Honour the explicit request</t>
+        </is>
+      </c>
+      <c r="D13" s="46" t="inlineStr">
+        <is>
+          <t>User-controlled</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1" s="31">
+      <c r="A15" s="51" t="inlineStr">
+        <is>
+          <t>TONE &amp; PERSONALITY</t>
+        </is>
+      </c>
+      <c r="B15" s="56" t="n"/>
+      <c r="C15" s="56" t="n"/>
+      <c r="D15" s="57" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1" s="31">
+      <c r="A16" s="52" t="inlineStr">
+        <is>
+          <t>Trait</t>
+        </is>
+      </c>
+      <c r="B16" s="52" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C16" s="52" t="inlineStr">
+        <is>
+          <t>Tunisian phrasing</t>
+        </is>
+      </c>
+      <c r="D16" s="52" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1" s="31">
+      <c r="A17" s="45" t="inlineStr">
+        <is>
+          <t>Warm &amp; respectful</t>
+        </is>
+      </c>
+      <c r="B17" s="46" t="inlineStr">
+        <is>
+          <t>Friendly talks naturally (ykollem behi btorbia)</t>
+        </is>
+      </c>
+      <c r="C17" s="46" t="inlineStr">
+        <is>
+          <t>"3andi, nfasserlek..."</t>
+        </is>
+      </c>
+      <c r="D17" s="46" t="inlineStr">
+        <is>
+          <t>Cold/robotic</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1" s="31">
+      <c r="A18" s="45" t="inlineStr">
+        <is>
+          <t>Direct answers</t>
+        </is>
+      </c>
+      <c r="B18" s="46" t="inlineStr">
+        <is>
+          <t>Short and to the point (jawbek bfacon 9sira)</t>
+        </is>
+      </c>
+      <c r="C18" s="46" t="inlineStr">
+        <is>
+          <t>Get to the point fast</t>
+        </is>
+      </c>
+      <c r="D18" s="46" t="inlineStr">
+        <is>
+          <t>Long intros</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1" s="31">
+      <c r="A19" s="45" t="inlineStr">
+        <is>
+          <t>Uses emojis</t>
+        </is>
+      </c>
+      <c r="B19" s="46" t="inlineStr">
+        <is>
+          <t>Light emoji use for warmth — max 1-2 per message</t>
+        </is>
+      </c>
+      <c r="C19" s="46" t="inlineStr">
+        <is>
+          <t>😊 ✅ 💡</t>
+        </is>
+      </c>
+      <c r="D19" s="46" t="inlineStr">
+        <is>
+          <t>Overuse</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="34" customHeight="1" s="31">
+      <c r="A20" s="45" t="inlineStr">
+        <is>
+          <t>Re-asks when unsure</t>
+        </is>
+      </c>
+      <c r="B20" s="46" t="inlineStr">
+        <is>
+          <t>Confirms before answering ambiguous questions</t>
+        </is>
+      </c>
+      <c r="C20" s="46" t="inlineStr">
+        <is>
+          <t>"ya3ni tsaleni 3la...?"</t>
+        </is>
+      </c>
+      <c r="D20" s="46" t="inlineStr">
+        <is>
+          <t>Guessing wrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="34" customHeight="1" s="31">
+      <c r="A21" s="45" t="inlineStr">
+        <is>
+          <t>Gender aware</t>
+        </is>
+      </c>
+      <c r="B21" s="46" t="inlineStr">
+        <is>
+          <t>Adapts fahm/fahma, fahi/faha based on context</t>
+        </is>
+      </c>
+      <c r="C21" s="46" t="inlineStr">
+        <is>
+          <t>"mazelt mouch fahma?" for girls</t>
+        </is>
+      </c>
+      <c r="D21" s="46" t="inlineStr">
+        <is>
+          <t>Always masculine default</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1" s="31">
+      <c r="A23" s="51" t="inlineStr">
+        <is>
+          <t>STEP CONNECTORS — use these, not the French equivalents</t>
+        </is>
+      </c>
+      <c r="B23" s="56" t="n"/>
+      <c r="C23" s="56" t="n"/>
+      <c r="D23" s="57" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1" s="31">
+      <c r="A24" s="52" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="B24" s="52" t="inlineStr">
+        <is>
+          <t>Correct Tunisian Darija</t>
+        </is>
+      </c>
+      <c r="C24" s="52" t="inlineStr">
+        <is>
+          <t>Do NOT use</t>
+        </is>
+      </c>
+      <c r="D24" s="52" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="34" customHeight="1" s="31">
+      <c r="A25" s="45" t="inlineStr">
+        <is>
+          <t>First</t>
+        </is>
+      </c>
+      <c r="B25" s="46" t="inlineStr">
+        <is>
+          <t>rit milloul</t>
+        </is>
+      </c>
+      <c r="C25" s="46" t="inlineStr">
+        <is>
+          <t>lawel, premièrement</t>
+        </is>
+      </c>
+      <c r="D25" s="46" t="inlineStr">
+        <is>
+          <t>Native confirmed ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="34" customHeight="1" s="31">
+      <c r="A26" s="45" t="inlineStr">
+        <is>
+          <t>Then</t>
+        </is>
+      </c>
+      <c r="B26" s="46" t="inlineStr">
+        <is>
+          <t>mba3d</t>
+        </is>
+      </c>
+      <c r="C26" s="46" t="inlineStr">
+        <is>
+          <t>ba3dha, ensuite</t>
+        </is>
+      </c>
+      <c r="D26" s="46" t="inlineStr">
+        <is>
+          <t>Most natural connector</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="34" customHeight="1" s="31">
+      <c r="A27" s="45" t="inlineStr">
+        <is>
+          <t>Finally</t>
+        </is>
+      </c>
+      <c r="B27" s="46" t="inlineStr">
+        <is>
+          <t>fil le5er</t>
+        </is>
+      </c>
+      <c r="C27" s="46" t="inlineStr">
+        <is>
+          <t>lakhir, finalement</t>
+        </is>
+      </c>
+      <c r="D27" s="46" t="inlineStr">
+        <is>
+          <t>Native confirmed ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="34" customHeight="1" s="31">
+      <c r="A28" s="45" t="inlineStr">
+        <is>
+          <t>Slowly / step by step</t>
+        </is>
+      </c>
+      <c r="B28" s="46" t="inlineStr">
+        <is>
+          <t>bichwaya bichwaya</t>
+        </is>
+      </c>
+      <c r="C28" s="46" t="inlineStr">
+        <is>
+          <t>khoutha khoutha</t>
+        </is>
+      </c>
+      <c r="D28" s="46" t="inlineStr">
+        <is>
+          <t>Corrected by native speaker</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1" s="31">
+      <c r="A30" s="51" t="inlineStr">
+        <is>
+          <t>ANALOGY BANK — Tunisian real-life comparisons that land</t>
+        </is>
+      </c>
+      <c r="B30" s="56" t="n"/>
+      <c r="C30" s="56" t="n"/>
+      <c r="D30" s="57" t="n"/>
+    </row>
+    <row r="31" ht="20" customHeight="1" s="31">
+      <c r="A31" s="52" t="inlineStr">
+        <is>
+          <t>Concept</t>
+        </is>
+      </c>
+      <c r="B31" s="52" t="inlineStr">
+        <is>
+          <t>Tunisian analogy</t>
+        </is>
+      </c>
+      <c r="C31" s="52" t="inlineStr">
+        <is>
+          <t>Darija phrasing</t>
+        </is>
+      </c>
+      <c r="D31" s="52" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="34" customHeight="1" s="31">
+      <c r="A32" s="45" t="inlineStr">
+        <is>
+          <t>Data storage</t>
+        </is>
+      </c>
+      <c r="B32" s="46" t="inlineStr">
+        <is>
+          <t>7anout (corner shop) storing products</t>
+        </is>
+      </c>
+      <c r="C32" s="46" t="inlineStr">
+        <is>
+          <t>"9abbel kima 3andek 7anout fih kol 7aja fi blaasha"</t>
+        </is>
+      </c>
+      <c r="D32" s="46" t="inlineStr">
+        <is>
+          <t>CS/Tech</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="34" customHeight="1" s="31">
+      <c r="A33" s="45" t="inlineStr">
+        <is>
+          <t>Algorithm</t>
+        </is>
+      </c>
+      <c r="B33" s="46" t="inlineStr">
+        <is>
+          <t>Recipe steps (wa9fet tayyeb)</t>
+        </is>
+      </c>
+      <c r="C33" s="46" t="inlineStr">
+        <is>
+          <t>"kima wa9fet el couscous, kol 5outha w 5outha"</t>
+        </is>
+      </c>
+      <c r="D33" s="46" t="inlineStr">
+        <is>
+          <t>CS/Math</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="34" customHeight="1" s="31">
+      <c r="A34" s="45" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="B34" s="46" t="inlineStr">
+        <is>
+          <t>Jar with a label (bocal b 3onwan)</t>
+        </is>
+      </c>
+      <c r="C34" s="46" t="inlineStr">
+        <is>
+          <t>"9abbel kima bocal mektoub 3liha isem"</t>
+        </is>
+      </c>
+      <c r="D34" s="46" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="34" customHeight="1" s="31">
+      <c r="A35" s="45" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="B35" s="46" t="inlineStr">
+        <is>
+          <t>Tool you call when needed</t>
+        </is>
+      </c>
+      <c r="C35" s="46" t="inlineStr">
+        <is>
+          <t>"kima t3ayet l5ouya bch y3awnek" (note: 5ouya not 5ou)</t>
+        </is>
+      </c>
+      <c r="D35" s="46" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="34" customHeight="1" s="31">
+      <c r="A36" s="45" t="inlineStr">
+        <is>
+          <t>Loop</t>
+        </is>
+      </c>
+      <c r="B36" s="46" t="inlineStr">
+        <is>
+          <t>Repeat until done (3amel l7aja 7atta tkamel)</t>
+        </is>
+      </c>
+      <c r="C36" s="46" t="inlineStr">
+        <is>
+          <t>"kima t8sel 7awajej wa7da wa7da"</t>
+        </is>
+      </c>
+      <c r="D36" s="46" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1" s="31">
+      <c r="A38" s="51" t="inlineStr">
+        <is>
+          <t>NATIVE CORRECTIONS LOG — 13 errors fixed in this version</t>
+        </is>
+      </c>
+      <c r="B38" s="56" t="n"/>
+      <c r="C38" s="56" t="n"/>
+      <c r="D38" s="57" t="n"/>
+    </row>
+    <row r="39" ht="20" customHeight="1" s="31">
+      <c r="A39" s="52" t="inlineStr">
+        <is>
+          <t>Wrong (old database)</t>
+        </is>
+      </c>
+      <c r="B39" s="52" t="inlineStr">
+        <is>
+          <t>Correct (native Tunisian)</t>
+        </is>
+      </c>
+      <c r="C39" s="52" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D39" s="52" t="inlineStr">
+        <is>
+          <t>Confirmed by</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="34" customHeight="1" s="31">
+      <c r="A40" s="53" t="inlineStr">
+        <is>
+          <t>chnou (marked common)</t>
+        </is>
+      </c>
+      <c r="B40" s="44" t="inlineStr">
+        <is>
+          <t>chnoa / chnia / chinhi — more frustration = more variants</t>
+        </is>
+      </c>
+      <c r="C40" s="44" t="inlineStr">
+        <is>
+          <t>vocabulary</t>
+        </is>
+      </c>
+      <c r="D40" s="44" t="inlineStr">
+        <is>
+          <t>Native speaker</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="34" customHeight="1" s="31">
+      <c r="A41" s="53" t="inlineStr">
+        <is>
+          <t>3aslema = goodbye/thanks</t>
+        </is>
+      </c>
+      <c r="B41" s="44" t="inlineStr">
+        <is>
+          <t>3aslema = casual HELLO only — never use as thanks</t>
+        </is>
+      </c>
+      <c r="C41" s="44" t="inlineStr">
+        <is>
+          <t>semantics</t>
+        </is>
+      </c>
+      <c r="D41" s="44" t="inlineStr">
+        <is>
+          <t>Native speaker</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="34" customHeight="1" s="31">
+      <c r="A42" s="53" t="inlineStr">
+        <is>
+          <t>barcha 3lik (used freely)</t>
+        </is>
+      </c>
+      <c r="B42" s="44" t="inlineStr">
+        <is>
+          <t>Too excessive/formal in this context — avoid</t>
+        </is>
+      </c>
+      <c r="C42" s="44" t="inlineStr">
+        <is>
+          <t>pragmatics</t>
+        </is>
+      </c>
+      <c r="D42" s="44" t="inlineStr">
+        <is>
+          <t>Native speaker</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="34" customHeight="1" s="31">
+      <c r="A43" s="53" t="inlineStr">
+        <is>
+          <t>ki ya3ni</t>
+        </is>
+      </c>
+      <c r="B43" s="44" t="inlineStr">
+        <is>
+          <t>kifeh maaneha (authentic Tunisian form)</t>
+        </is>
+      </c>
+      <c r="C43" s="44" t="inlineStr">
+        <is>
+          <t>vocabulary</t>
+        </is>
+      </c>
+      <c r="D43" s="44" t="inlineStr">
+        <is>
+          <t>Native speaker</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="34" customHeight="1" s="31">
+      <c r="A44" s="53" t="inlineStr">
+        <is>
+          <t>sa3eb</t>
+        </is>
+      </c>
+      <c r="B44" s="44" t="inlineStr">
+        <is>
+          <t>s3ib (correct Tunisian pronunciation)</t>
+        </is>
+      </c>
+      <c r="C44" s="44" t="inlineStr">
+        <is>
+          <t>phonology</t>
+        </is>
+      </c>
+      <c r="D44" s="44" t="inlineStr">
+        <is>
+          <t>Native speaker</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="34" customHeight="1" s="31">
+      <c r="A45" s="53" t="inlineStr">
+        <is>
+          <t>zidi explain</t>
+        </is>
+      </c>
+      <c r="B45" s="44" t="inlineStr">
+        <is>
+          <t>zid fassarly / zid watha7li</t>
+        </is>
+      </c>
+      <c r="C45" s="44" t="inlineStr">
+        <is>
+          <t>vocabulary</t>
+        </is>
+      </c>
+      <c r="D45" s="44" t="inlineStr">
+        <is>
+          <t>Native speaker</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="34" customHeight="1" s="31">
+      <c r="A46" s="53" t="inlineStr">
+        <is>
+          <t>rani 9ri</t>
+        </is>
+      </c>
+      <c r="B46" s="44" t="inlineStr">
+        <is>
+          <t>rani 9rit (correct past tense)</t>
+        </is>
+      </c>
+      <c r="C46" s="44" t="inlineStr">
+        <is>
+          <t>grammar</t>
+        </is>
+      </c>
+      <c r="D46" s="44" t="inlineStr">
+        <is>
+          <t>Native speaker</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="34" customHeight="1" s="31">
+      <c r="A47" s="53" t="inlineStr">
+        <is>
+          <t>5ou</t>
+        </is>
+      </c>
+      <c r="B47" s="44" t="inlineStr">
+        <is>
+          <t>5ouya (correct possessive form)</t>
+        </is>
+      </c>
+      <c r="C47" s="44" t="inlineStr">
+        <is>
+          <t>grammar</t>
+        </is>
+      </c>
+      <c r="D47" s="44" t="inlineStr">
+        <is>
+          <t>Native speaker</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="34" customHeight="1" s="31">
+      <c r="A48" s="53" t="inlineStr">
+        <is>
+          <t>lawel / ba3dha / lakhir</t>
+        </is>
+      </c>
+      <c r="B48" s="44" t="inlineStr">
+        <is>
+          <t>rit milloul / mba3d / fil le5er</t>
+        </is>
+      </c>
+      <c r="C48" s="44" t="inlineStr">
+        <is>
+          <t>discourse</t>
+        </is>
+      </c>
+      <c r="D48" s="44" t="inlineStr">
+        <is>
+          <t>Native speaker</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="34" customHeight="1" s="31">
+      <c r="A49" s="53" t="inlineStr">
+        <is>
+          <t>khoutha khoutha</t>
+        </is>
+      </c>
+      <c r="B49" s="44" t="inlineStr">
+        <is>
+          <t>bichwaya bichwaya</t>
+        </is>
+      </c>
+      <c r="C49" s="44" t="inlineStr">
+        <is>
+          <t>vocabulary</t>
+        </is>
+      </c>
+      <c r="D49" s="44" t="inlineStr">
+        <is>
+          <t>Native speaker</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="34" customHeight="1" s="31">
+      <c r="A50" s="53" t="inlineStr">
+        <is>
+          <t>got an example</t>
+        </is>
+      </c>
+      <c r="B50" s="44" t="inlineStr">
+        <is>
+          <t>3andk example reel</t>
+        </is>
+      </c>
+      <c r="C50" s="44" t="inlineStr">
+        <is>
+          <t>vocabulary</t>
+        </is>
+      </c>
+      <c r="D50" s="44" t="inlineStr">
+        <is>
+          <t>Native speaker</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="34" customHeight="1" s="31">
+      <c r="A51" s="53" t="inlineStr">
+        <is>
+          <t>mch 3andi fikra</t>
+        </is>
+      </c>
+      <c r="B51" s="44" t="inlineStr">
+        <is>
+          <t>ma 3andi 7ata fekra (stronger, more natural)</t>
+        </is>
+      </c>
+      <c r="C51" s="44" t="inlineStr">
+        <is>
+          <t>vocabulary</t>
+        </is>
+      </c>
+      <c r="D51" s="44" t="inlineStr">
+        <is>
+          <t>Native speaker</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="34" customHeight="1" s="31">
+      <c r="A52" s="53" t="inlineStr">
+        <is>
+          <t>mazelt mouch fahi (always)</t>
+        </is>
+      </c>
+      <c r="B52" s="44" t="inlineStr">
+        <is>
+          <t>mazelt mouch fahm (masc) / mazelt mouch fahma (fem)</t>
+        </is>
+      </c>
+      <c r="C52" s="44" t="inlineStr">
+        <is>
+          <t>gender</t>
+        </is>
+      </c>
+      <c r="D52" s="44" t="inlineStr">
+        <is>
+          <t>Native speaker</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" style="31" min="1" max="1"/>
+    <col width="38" customWidth="1" style="31" min="2" max="2"/>
+    <col width="20" customWidth="1" style="31" min="3" max="3"/>
+    <col width="46" customWidth="1" style="31" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" s="31">
+      <c r="A1" s="50" t="inlineStr">
+        <is>
+          <t>🚫  Swearing Detection Policy — PDF §12</t>
+        </is>
+      </c>
+      <c r="B1" s="56" t="n"/>
+      <c r="C1" s="56" t="n"/>
+      <c r="D1" s="57" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1" s="31">
+      <c r="A2" s="52" t="inlineStr">
+        <is>
+          <t>Signal Type</t>
+        </is>
+      </c>
+      <c r="B2" s="52" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C2" s="52" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="D2" s="52" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1" s="31">
+      <c r="A3" s="55" t="inlineStr">
+        <is>
+          <t>Swear word detected</t>
+        </is>
+      </c>
+      <c r="B3" s="55" t="inlineStr">
+        <is>
+          <t>Pause response — show polite warning</t>
+        </is>
+      </c>
+      <c r="C3" s="55" t="inlineStr">
+        <is>
+          <t>10 second cooldown</t>
+        </is>
+      </c>
+      <c r="D3" s="55" t="inlineStr">
+        <is>
+          <t>Strip from text, treat as punctuation not meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1" s="31">
+      <c r="A4" s="54" t="inlineStr">
+        <is>
+          <t>Swear + confusion signal</t>
+        </is>
+      </c>
+      <c r="B4" s="54" t="inlineStr">
+        <is>
+          <t>Apply timeout THEN reformulate</t>
+        </is>
+      </c>
+      <c r="C4" s="54" t="inlineStr">
+        <is>
+          <t>10s then respond</t>
+        </is>
+      </c>
+      <c r="D4" s="54" t="inlineStr">
+        <is>
+          <t>Swear always processed first (Priority 1 in §13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1" s="31">
+      <c r="A5" s="55" t="inlineStr">
+        <is>
+          <t>Swear + giving up signal</t>
+        </is>
+      </c>
+      <c r="B5" s="55" t="inlineStr">
+        <is>
+          <t>Apply timeout THEN acknowledge</t>
+        </is>
+      </c>
+      <c r="C5" s="55" t="inlineStr">
+        <is>
+          <t>10s then respond</t>
+        </is>
+      </c>
+      <c r="D5" s="55" t="inlineStr">
+        <is>
+          <t>Never repeat swear words back to the user</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" s="31">
+      <c r="A7" s="52" t="inlineStr">
+        <is>
+          <t>📌 Implementation Note</t>
+        </is>
+      </c>
+      <c r="B7" s="60" t="inlineStr">
+        <is>
+          <t>Maintain a private SWEAR_WORDS list in your codebase. Strip swear words from the sentence before intent detection — treat them as punctuation, not meaning. Never log or repeat swear words back to the user. Users frequently swear as emphasis or frustration markers — not literal insults.</t>
+        </is>
+      </c>
+      <c r="C7" s="61" t="n"/>
+      <c r="D7" s="62" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1" s="31">
+      <c r="A8" s="63" t="n"/>
+      <c r="B8" s="64" t="n"/>
+      <c r="C8" s="65" t="n"/>
+      <c r="D8" s="66" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B7:D8"/>
+    <mergeCell ref="A7:A8"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/darija_nlp_database.xlsx
+++ b/darija_nlp_database.xlsx
@@ -1717,7 +1717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1751,61 +1751,6 @@
           <t>reviewer_note</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-05-07 22:07</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>chnoa reference mta3 klemik</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>rit houa, bch tfhem barcha... elreference mta3 klemik huwa m3a elconcepts elbasis li fi elklemik, ya5i elchimie, winou y5dem fi felm elklemik, elcompounds, welelements. elreference mta3 klemik y5dem fi tawa elstudents welresearchers li yfhemou chi 9olt mte3 elklemik, ya5i y3rafou chi 9olt mte3 elproperties welbehaviors mta3 elmatériaux welsubstances. behi, elreference mta3 klemik huwa m3a eltools welresources li y5demou fi felm elklemik, ya5i yest5demou 3awed eldictionaries, elencyclopédies, welatabases. fhemt?</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>instead of bich tefhim barcha use bich tefhem mli7</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-07 22:14</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>chnoa reference mta3 klemik</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>rit houa, bch tfhem barcha... elreference mta3 klemik huwa m3a elconcepts elbasis li fi elklemik, ya5i elchimie, winou y5dem fi felm elklemik, elcompounds, welelements. elreference mta3 klemik y5dem fi tawa elstudents welresearchers li yfhemou chi 9olt mte3 elklemik, ya5i y3rafou chi 9olt mte3 elproperties welbehaviors mta3 elmatériaux welsubstances. behi, elreference mta3 klemik huwa m3a eltools welresources li y5demou fi felm elklemik, ya5i yest5demou 3awed eldictionaries, elencyclopédies, welatabases. fhemt?</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>"m3a elconcepts elbasis li fi elklemik" reference mta3 klemi not klemk</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1974,19 +1919,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M98"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="31" min="1" max="1"/>
     <col width="18" customWidth="1" style="31" min="2" max="2"/>
     <col width="14" customWidth="1" style="31" min="3" max="3"/>
-    <col width="12" customWidth="1" style="31" min="4" max="4"/>
-    <col width="38" customWidth="1" style="31" min="5" max="5"/>
-    <col width="30" customWidth="1" style="31" min="6" max="6"/>
-    <col width="44" customWidth="1" style="31" min="7" max="7"/>
-    <col width="22" customWidth="1" style="31" min="8" max="8"/>
-    <col width="38" customWidth="1" style="31" min="9" max="10"/>
-    <col width="40" customWidth="1" style="31" min="10" max="10"/>
+    <col width="14" customWidth="1" style="31" min="4" max="4"/>
+    <col width="40" customWidth="1" style="31" min="5" max="5"/>
+    <col width="34" customWidth="1" style="31" min="6" max="6"/>
+    <col width="48" customWidth="1" style="31" min="7" max="7"/>
+    <col width="24" customWidth="1" style="31" min="8" max="8"/>
+    <col width="42" customWidth="1" style="31" min="9" max="10"/>
+    <col width="42" customWidth="1" style="31" min="10" max="10"/>
     <col width="14" customWidth="1" style="31" min="11" max="11"/>
     <col width="12" customWidth="1" style="31" min="12" max="12"/>
     <col width="14" customWidth="1" style="31" min="13" max="13"/>
@@ -2592,7 +2537,7 @@
       </c>
       <c r="L11" s="55" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>review</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2657,7 @@
       </c>
       <c r="L13" s="55" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>review</t>
         </is>
       </c>
     </row>
@@ -2877,22 +2822,22 @@
       </c>
       <c r="I16" s="54" t="inlineStr">
         <is>
-          <t>is cross training the one that happens in edge impulse or not?</t>
+          <t>is cross training as easy as it looks in edge impulse or not?</t>
         </is>
       </c>
       <c r="J16" s="54" t="inlineStr">
         <is>
-          <t>le cross training est-il le meme qu'il y paraît dans edge impulse ?</t>
+          <t>le cross training est-il aussi facile qu'il y paraît dans edge impulse ?</t>
         </is>
       </c>
       <c r="K16" s="54" t="inlineStr">
         <is>
-          <t>confused</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="L16" s="54" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>review</t>
         </is>
       </c>
     </row>
@@ -4454,6 +4399,3306 @@
         </is>
       </c>
       <c r="L43" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="36" customHeight="1" s="31">
+      <c r="A44" s="45" t="n">
+        <v>41</v>
+      </c>
+      <c r="B44" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C44" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D44" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E44" s="46" t="inlineStr">
+        <is>
+          <t>rak 8alit heka mch s7i7</t>
+        </is>
+      </c>
+      <c r="F44" s="46" t="inlineStr">
+        <is>
+          <t>rak 8alit</t>
+        </is>
+      </c>
+      <c r="G44" s="46" t="inlineStr">
+        <is>
+          <t>rak 8alt, rak ghalt, enti 8alit</t>
+        </is>
+      </c>
+      <c r="H44" s="46" t="inlineStr">
+        <is>
+          <t>hallucination</t>
+        </is>
+      </c>
+      <c r="I44" s="46" t="inlineStr">
+        <is>
+          <t>you are wrong this isn't correct</t>
+        </is>
+      </c>
+      <c r="J44" s="46" t="inlineStr">
+        <is>
+          <t>tu as tort ce n'est pas correct</t>
+        </is>
+      </c>
+      <c r="K44" s="46" t="inlineStr">
+        <is>
+          <t>frustrated</t>
+        </is>
+      </c>
+      <c r="L44" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="36" customHeight="1" s="31">
+      <c r="A45" s="45" t="n">
+        <v>42</v>
+      </c>
+      <c r="B45" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C45" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D45" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E45" s="46" t="inlineStr">
+        <is>
+          <t>enti tkharef / enti t7awwel</t>
+        </is>
+      </c>
+      <c r="F45" s="46" t="inlineStr">
+        <is>
+          <t>enti tkharef</t>
+        </is>
+      </c>
+      <c r="G45" s="46" t="inlineStr">
+        <is>
+          <t>enti t7awwel, rak tkharef, 5arreef</t>
+        </is>
+      </c>
+      <c r="H45" s="46" t="inlineStr">
+        <is>
+          <t>hallucination</t>
+        </is>
+      </c>
+      <c r="I45" s="46" t="inlineStr">
+        <is>
+          <t>you're hallucinating / making things up</t>
+        </is>
+      </c>
+      <c r="J45" s="46" t="inlineStr">
+        <is>
+          <t>tu hallucines / tu inventes</t>
+        </is>
+      </c>
+      <c r="K45" s="46" t="inlineStr">
+        <is>
+          <t>frustrated</t>
+        </is>
+      </c>
+      <c r="L45" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="36" customHeight="1" s="31">
+      <c r="A46" s="45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B46" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C46" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D46" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E46" s="46" t="inlineStr">
+        <is>
+          <t>asma3ni heka mch s7i7 / asma3ni rak 8alit</t>
+        </is>
+      </c>
+      <c r="F46" s="46" t="inlineStr">
+        <is>
+          <t>asma3ni heka mch s7i7</t>
+        </is>
+      </c>
+      <c r="G46" s="46" t="inlineStr">
+        <is>
+          <t>asma3ni, asma3 m3aya, asma3ni rak 8alit</t>
+        </is>
+      </c>
+      <c r="H46" s="46" t="inlineStr">
+        <is>
+          <t>hallucination</t>
+        </is>
+      </c>
+      <c r="I46" s="46" t="inlineStr">
+        <is>
+          <t>listen this isn't correct / listen you're wrong</t>
+        </is>
+      </c>
+      <c r="J46" s="46" t="inlineStr">
+        <is>
+          <t>écoute ce n'est pas correct</t>
+        </is>
+      </c>
+      <c r="K46" s="46" t="inlineStr">
+        <is>
+          <t>frustrated</t>
+        </is>
+      </c>
+      <c r="L46" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="36" customHeight="1" s="31">
+      <c r="A47" s="45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B47" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C47" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D47" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E47" s="46" t="inlineStr">
+        <is>
+          <t>tabdech tjib min rasik bla marja3</t>
+        </is>
+      </c>
+      <c r="F47" s="46" t="inlineStr">
+        <is>
+          <t>tabdech tjib min rasik</t>
+        </is>
+      </c>
+      <c r="G47" s="46" t="inlineStr">
+        <is>
+          <t>tabdech tjib min rasek, ma tjibch min rasik</t>
+        </is>
+      </c>
+      <c r="H47" s="46" t="inlineStr">
+        <is>
+          <t>hallucination</t>
+        </is>
+      </c>
+      <c r="I47" s="46" t="inlineStr">
+        <is>
+          <t>don't make things up without a source</t>
+        </is>
+      </c>
+      <c r="J47" s="46" t="inlineStr">
+        <is>
+          <t>ne fabrique pas des réponses sans source</t>
+        </is>
+      </c>
+      <c r="K47" s="46" t="inlineStr">
+        <is>
+          <t>aggressive</t>
+        </is>
+      </c>
+      <c r="L47" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="36" customHeight="1" s="31">
+      <c r="A48" s="45" t="n">
+        <v>45</v>
+      </c>
+      <c r="B48" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C48" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D48" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E48" s="46" t="inlineStr">
+        <is>
+          <t>kank makch sur 9oli</t>
+        </is>
+      </c>
+      <c r="F48" s="46" t="inlineStr">
+        <is>
+          <t>kank makch sur 9oli</t>
+        </is>
+      </c>
+      <c r="G48" s="46" t="inlineStr">
+        <is>
+          <t>kan mch sur 9oli, kank mch met2akked 9oli</t>
+        </is>
+      </c>
+      <c r="H48" s="46" t="inlineStr">
+        <is>
+          <t>source_check</t>
+        </is>
+      </c>
+      <c r="I48" s="46" t="inlineStr">
+        <is>
+          <t>if you're not sure tell me</t>
+        </is>
+      </c>
+      <c r="J48" s="46" t="inlineStr">
+        <is>
+          <t>si tu n'es pas sûr dis-le moi</t>
+        </is>
+      </c>
+      <c r="K48" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L48" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="36" customHeight="1" s="31">
+      <c r="A49" s="45" t="n">
+        <v>46</v>
+      </c>
+      <c r="B49" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C49" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D49" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E49" s="46" t="inlineStr">
+        <is>
+          <t>manich sur ama nfasserlek kifeh nfhem</t>
+        </is>
+      </c>
+      <c r="F49" s="46" t="inlineStr">
+        <is>
+          <t>manich sur</t>
+        </is>
+      </c>
+      <c r="G49" s="46" t="inlineStr">
+        <is>
+          <t>manich sur, mch met2akked, manich met2akked</t>
+        </is>
+      </c>
+      <c r="H49" s="46" t="inlineStr">
+        <is>
+          <t>uncertainty</t>
+        </is>
+      </c>
+      <c r="I49" s="46" t="inlineStr">
+        <is>
+          <t>I'm not sure but let me explain how I understand it</t>
+        </is>
+      </c>
+      <c r="J49" s="46" t="inlineStr">
+        <is>
+          <t>je ne suis pas sûr mais je vais expliquer</t>
+        </is>
+      </c>
+      <c r="K49" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L49" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="36" customHeight="1" s="31">
+      <c r="A50" s="45" t="n">
+        <v>47</v>
+      </c>
+      <c r="B50" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C50" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D50" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E50" s="46" t="inlineStr">
+        <is>
+          <t>lmaalouma hethi mouch mawjouda fel cours</t>
+        </is>
+      </c>
+      <c r="F50" s="46" t="inlineStr">
+        <is>
+          <t>lmaalouma hethi mouch mawjouda</t>
+        </is>
+      </c>
+      <c r="G50" s="46" t="inlineStr">
+        <is>
+          <t>lma3louma hethi mch mawjouda, ma3andich lmaalouma</t>
+        </is>
+      </c>
+      <c r="H50" s="46" t="inlineStr">
+        <is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="I50" s="46" t="inlineStr">
+        <is>
+          <t>this information is not in the course material</t>
+        </is>
+      </c>
+      <c r="J50" s="46" t="inlineStr">
+        <is>
+          <t>cette information n'est pas dans le cours</t>
+        </is>
+      </c>
+      <c r="K50" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L50" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="36" customHeight="1" s="31">
+      <c r="A51" s="45" t="n">
+        <v>48</v>
+      </c>
+      <c r="B51" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C51" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D51" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E51" s="46" t="inlineStr">
+        <is>
+          <t>heka mn 3andi mch mn el cours kank makch sur</t>
+        </is>
+      </c>
+      <c r="F51" s="46" t="inlineStr">
+        <is>
+          <t>heka mn 3andi mch mn el cours</t>
+        </is>
+      </c>
+      <c r="G51" s="46" t="inlineStr">
+        <is>
+          <t>heka mn rassi mch mn el cours, heka mch fel cours</t>
+        </is>
+      </c>
+      <c r="H51" s="46" t="inlineStr">
+        <is>
+          <t>uncertainty</t>
+        </is>
+      </c>
+      <c r="I51" s="46" t="inlineStr">
+        <is>
+          <t>this is from me not the course I'm not sure</t>
+        </is>
+      </c>
+      <c r="J51" s="46" t="inlineStr">
+        <is>
+          <t>c'est de moi pas du cours je ne suis pas sûr</t>
+        </is>
+      </c>
+      <c r="K51" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L51" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="36" customHeight="1" s="31">
+      <c r="A52" s="45" t="n">
+        <v>49</v>
+      </c>
+      <c r="B52" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C52" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D52" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E52" s="46" t="inlineStr">
+        <is>
+          <t>heka mch mektoub 3andna / heka barra el programme</t>
+        </is>
+      </c>
+      <c r="F52" s="46" t="inlineStr">
+        <is>
+          <t>heka mch mektoub 3andna</t>
+        </is>
+      </c>
+      <c r="G52" s="46" t="inlineStr">
+        <is>
+          <t>heka mch mektoub 3andna, heka barra el programme, heka mch fel cours</t>
+        </is>
+      </c>
+      <c r="H52" s="46" t="inlineStr">
+        <is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="I52" s="46" t="inlineStr">
+        <is>
+          <t>this isn't written in our material / outside the syllabus</t>
+        </is>
+      </c>
+      <c r="J52" s="46" t="inlineStr">
+        <is>
+          <t>ce n'est pas dans notre matière / hors programme</t>
+        </is>
+      </c>
+      <c r="K52" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L52" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="36" customHeight="1" s="31">
+      <c r="A53" s="45" t="n">
+        <v>50</v>
+      </c>
+      <c r="B53" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C53" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D53" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E53" s="46" t="inlineStr">
+        <is>
+          <t>9ollili ila el maalouma jiha mn el cours aw mn 3andek</t>
+        </is>
+      </c>
+      <c r="F53" s="46" t="inlineStr">
+        <is>
+          <t>9ollili ila el maalouma jiha mn el cours</t>
+        </is>
+      </c>
+      <c r="G53" s="46" t="inlineStr">
+        <is>
+          <t>9ollili ila jiha mn el cours, 9ollili el marja3</t>
+        </is>
+      </c>
+      <c r="H53" s="46" t="inlineStr">
+        <is>
+          <t>source_check</t>
+        </is>
+      </c>
+      <c r="I53" s="46" t="inlineStr">
+        <is>
+          <t>tell me if the info is from the course or from you</t>
+        </is>
+      </c>
+      <c r="J53" s="46" t="inlineStr">
+        <is>
+          <t>dis-moi si l'info vient du cours ou de toi</t>
+        </is>
+      </c>
+      <c r="K53" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L53" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="36" customHeight="1" s="31">
+      <c r="A54" s="45" t="n">
+        <v>51</v>
+      </c>
+      <c r="B54" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C54" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D54" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E54" s="46" t="inlineStr">
+        <is>
+          <t>zid watha7li sou2alk bich na3tik reponse behia</t>
+        </is>
+      </c>
+      <c r="F54" s="46" t="inlineStr">
+        <is>
+          <t>zid watha7li sou2alk</t>
+        </is>
+      </c>
+      <c r="G54" s="46" t="inlineStr">
+        <is>
+          <t>zid watha7li, watha7li akther, watha7li su2alek</t>
+        </is>
+      </c>
+      <c r="H54" s="46" t="inlineStr">
+        <is>
+          <t>clarification_request</t>
+        </is>
+      </c>
+      <c r="I54" s="46" t="inlineStr">
+        <is>
+          <t>clarify your question so I can give you a better answer</t>
+        </is>
+      </c>
+      <c r="J54" s="46" t="inlineStr">
+        <is>
+          <t>clarifie ta question pour que je te donne une meilleure réponse</t>
+        </is>
+      </c>
+      <c r="K54" s="46" t="inlineStr">
+        <is>
+          <t>polite</t>
+        </is>
+      </c>
+      <c r="L54" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="36" customHeight="1" s="31">
+      <c r="A55" s="45" t="n">
+        <v>52</v>
+      </c>
+      <c r="B55" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C55" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D55" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E55" s="46" t="inlineStr">
+        <is>
+          <t>tsaleni 3la X wella 3la Y 9bal ma njawbek</t>
+        </is>
+      </c>
+      <c r="F55" s="46" t="inlineStr">
+        <is>
+          <t>tsaleni 3la X wella 3la Y</t>
+        </is>
+      </c>
+      <c r="G55" s="46" t="inlineStr">
+        <is>
+          <t>tsaleni 3la, yes2el 3la, confirmi su2alek</t>
+        </is>
+      </c>
+      <c r="H55" s="46" t="inlineStr">
+        <is>
+          <t>clarification_request</t>
+        </is>
+      </c>
+      <c r="I55" s="46" t="inlineStr">
+        <is>
+          <t>let me ask you about X or Y before I answer</t>
+        </is>
+      </c>
+      <c r="J55" s="46" t="inlineStr">
+        <is>
+          <t>laisse-moi te demander avant de répondre</t>
+        </is>
+      </c>
+      <c r="K55" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L55" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="36" customHeight="1" s="31">
+      <c r="A56" s="45" t="n">
+        <v>53</v>
+      </c>
+      <c r="B56" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C56" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D56" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E56" s="46" t="inlineStr">
+        <is>
+          <t>confirmi m3aya el section elli t7ki 3liha</t>
+        </is>
+      </c>
+      <c r="F56" s="46" t="inlineStr">
+        <is>
+          <t>confirmi m3aya el section</t>
+        </is>
+      </c>
+      <c r="G56" s="46" t="inlineStr">
+        <is>
+          <t>confirmi el section, confirmi el juz, confirmi el partie</t>
+        </is>
+      </c>
+      <c r="H56" s="46" t="inlineStr">
+        <is>
+          <t>clarification_request</t>
+        </is>
+      </c>
+      <c r="I56" s="46" t="inlineStr">
+        <is>
+          <t>confirm with me which section you're referring to</t>
+        </is>
+      </c>
+      <c r="J56" s="46" t="inlineStr">
+        <is>
+          <t>confirme avec moi la section dont tu parles</t>
+        </is>
+      </c>
+      <c r="K56" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L56" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="36" customHeight="1" s="31">
+      <c r="A57" s="45" t="n">
+        <v>54</v>
+      </c>
+      <c r="B57" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C57" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D57" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E57" s="46" t="inlineStr">
+        <is>
+          <t>rani 9rit el cours wma fhemtch</t>
+        </is>
+      </c>
+      <c r="F57" s="46" t="inlineStr">
+        <is>
+          <t>rani 9rit el cours wma fhemtch</t>
+        </is>
+      </c>
+      <c r="G57" s="46" t="inlineStr">
+        <is>
+          <t>rani 9rit wma fhimt, 9rit el cours wma fhamt</t>
+        </is>
+      </c>
+      <c r="H57" s="46" t="inlineStr">
+        <is>
+          <t>pdf_confusion</t>
+        </is>
+      </c>
+      <c r="I57" s="46" t="inlineStr">
+        <is>
+          <t>I read the course but didn't understand</t>
+        </is>
+      </c>
+      <c r="J57" s="46" t="inlineStr">
+        <is>
+          <t>j'ai lu le cours mais je n'ai pas compris</t>
+        </is>
+      </c>
+      <c r="K57" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L57" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="36" customHeight="1" s="31">
+      <c r="A58" s="45" t="n">
+        <v>55</v>
+      </c>
+      <c r="B58" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C58" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D58" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E58" s="46" t="inlineStr">
+        <is>
+          <t>lprof ma9alich haka / el ustez 9al ghir</t>
+        </is>
+      </c>
+      <c r="F58" s="46" t="inlineStr">
+        <is>
+          <t>lprof ma9alich haka</t>
+        </is>
+      </c>
+      <c r="G58" s="46" t="inlineStr">
+        <is>
+          <t>lprof 9al ghir, el ustez 9al ghir, lprof mach 9alich haka</t>
+        </is>
+      </c>
+      <c r="H58" s="46" t="inlineStr">
+        <is>
+          <t>pdf_mismatch</t>
+        </is>
+      </c>
+      <c r="I58" s="46" t="inlineStr">
+        <is>
+          <t>the professor didn't say it like that / said something different</t>
+        </is>
+      </c>
+      <c r="J58" s="46" t="inlineStr">
+        <is>
+          <t>le prof n'a pas dit comme ça / a dit autre chose</t>
+        </is>
+      </c>
+      <c r="K58" s="46" t="inlineStr">
+        <is>
+          <t>frustrated</t>
+        </is>
+      </c>
+      <c r="L58" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="36" customHeight="1" s="31">
+      <c r="A59" s="45" t="n">
+        <v>56</v>
+      </c>
+      <c r="B59" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C59" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D59" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E59" s="46" t="inlineStr">
+        <is>
+          <t>fel exam jaw b su2al kima hedha kifeh njaweb</t>
+        </is>
+      </c>
+      <c r="F59" s="46" t="inlineStr">
+        <is>
+          <t>fel exam jaw b su2al kima hedha</t>
+        </is>
+      </c>
+      <c r="G59" s="46" t="inlineStr">
+        <is>
+          <t>fel exam, fel examen, fil imti7an, su2al kima hedha</t>
+        </is>
+      </c>
+      <c r="H59" s="46" t="inlineStr">
+        <is>
+          <t>exam_context</t>
+        </is>
+      </c>
+      <c r="I59" s="46" t="inlineStr">
+        <is>
+          <t>in the exam there was a question like this how do I answer</t>
+        </is>
+      </c>
+      <c r="J59" s="46" t="inlineStr">
+        <is>
+          <t>à l'examen il y avait une question comme ça comment répondre</t>
+        </is>
+      </c>
+      <c r="K59" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L59" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="36" customHeight="1" s="31">
+      <c r="A60" s="45" t="n">
+        <v>57</v>
+      </c>
+      <c r="B60" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C60" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D60" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E60" s="46" t="inlineStr">
+        <is>
+          <t>bch n3addi el exam lazm nifhem heka</t>
+        </is>
+      </c>
+      <c r="F60" s="46" t="inlineStr">
+        <is>
+          <t>bch n3addi el exam lazm nifhem</t>
+        </is>
+      </c>
+      <c r="G60" s="46" t="inlineStr">
+        <is>
+          <t>bch n3addi, bch nfût, bch nnajah, lazm nifhem</t>
+        </is>
+      </c>
+      <c r="H60" s="46" t="inlineStr">
+        <is>
+          <t>exam_context</t>
+        </is>
+      </c>
+      <c r="I60" s="46" t="inlineStr">
+        <is>
+          <t>to pass the exam I need to understand this</t>
+        </is>
+      </c>
+      <c r="J60" s="46" t="inlineStr">
+        <is>
+          <t>pour réussir l'examen je dois comprendre ça</t>
+        </is>
+      </c>
+      <c r="K60" s="46" t="inlineStr">
+        <is>
+          <t>polite</t>
+        </is>
+      </c>
+      <c r="L60" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="36" customHeight="1" s="31">
+      <c r="A61" s="45" t="n">
+        <v>58</v>
+      </c>
+      <c r="B61" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C61" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D61" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E61" s="46" t="inlineStr">
+        <is>
+          <t>rani w7it fel projet / rani w7it f 7aja specific</t>
+        </is>
+      </c>
+      <c r="F61" s="46" t="inlineStr">
+        <is>
+          <t>rani w7it</t>
+        </is>
+      </c>
+      <c r="G61" s="46" t="inlineStr">
+        <is>
+          <t>rani w7it, rani w9aft, wa9fait, w7it f 7aja</t>
+        </is>
+      </c>
+      <c r="H61" s="46" t="inlineStr">
+        <is>
+          <t>stuck</t>
+        </is>
+      </c>
+      <c r="I61" s="46" t="inlineStr">
+        <is>
+          <t>I'm stuck in my project / stuck on something specific</t>
+        </is>
+      </c>
+      <c r="J61" s="46" t="inlineStr">
+        <is>
+          <t>je suis bloqué dans mon projet / bloqué sur quelque chose</t>
+        </is>
+      </c>
+      <c r="K61" s="46" t="inlineStr">
+        <is>
+          <t>frustrated</t>
+        </is>
+      </c>
+      <c r="L61" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="36" customHeight="1" s="31">
+      <c r="A62" s="45" t="n">
+        <v>59</v>
+      </c>
+      <c r="B62" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C62" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D62" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E62" s="46" t="inlineStr">
+        <is>
+          <t>chnoa el farq bin deep learning w machine learning</t>
+        </is>
+      </c>
+      <c r="F62" s="46" t="inlineStr">
+        <is>
+          <t>chnoa el farq bin deep learning w machine learning</t>
+        </is>
+      </c>
+      <c r="G62" s="46" t="inlineStr">
+        <is>
+          <t>chnoa el farq, chnoa farqhom, kifeh y5talfu</t>
+        </is>
+      </c>
+      <c r="H62" s="46" t="inlineStr">
+        <is>
+          <t>compare_question</t>
+        </is>
+      </c>
+      <c r="I62" s="46" t="inlineStr">
+        <is>
+          <t>what's the difference between deep learning and machine learning</t>
+        </is>
+      </c>
+      <c r="J62" s="46" t="inlineStr">
+        <is>
+          <t>quelle est la différence entre deep learning et machine learning</t>
+        </is>
+      </c>
+      <c r="K62" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L62" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="36" customHeight="1" s="31">
+      <c r="A63" s="45" t="n">
+        <v>60</v>
+      </c>
+      <c r="B63" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C63" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D63" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E63" s="46" t="inlineStr">
+        <is>
+          <t>kifeh n7assen el accuracy mte3i / accuracy mte3i ba9ia</t>
+        </is>
+      </c>
+      <c r="F63" s="46" t="inlineStr">
+        <is>
+          <t>kifeh n7assen el accuracy</t>
+        </is>
+      </c>
+      <c r="G63" s="46" t="inlineStr">
+        <is>
+          <t>kifeh nrfa3 el accuracy, kifeh n7assin, accuracy ba9ia</t>
+        </is>
+      </c>
+      <c r="H63" s="46" t="inlineStr">
+        <is>
+          <t>technical_question</t>
+        </is>
+      </c>
+      <c r="I63" s="46" t="inlineStr">
+        <is>
+          <t>how do I improve my accuracy / my accuracy is still low</t>
+        </is>
+      </c>
+      <c r="J63" s="46" t="inlineStr">
+        <is>
+          <t>comment améliorer ma précision / ma précision est toujours faible</t>
+        </is>
+      </c>
+      <c r="K63" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L63" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="36" customHeight="1" s="31">
+      <c r="A64" s="45" t="n">
+        <v>61</v>
+      </c>
+      <c r="B64" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C64" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D64" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E64" s="46" t="inlineStr">
+        <is>
+          <t>chnoa ya3ni overfitting / chnoa ya3ni underfitting</t>
+        </is>
+      </c>
+      <c r="F64" s="46" t="inlineStr">
+        <is>
+          <t>chnoa ya3ni overfitting</t>
+        </is>
+      </c>
+      <c r="G64" s="46" t="inlineStr">
+        <is>
+          <t>chnoa overfitting, chnoa underfitting, kifeh nfhem overfitting</t>
+        </is>
+      </c>
+      <c r="H64" s="46" t="inlineStr">
+        <is>
+          <t>definition_question</t>
+        </is>
+      </c>
+      <c r="I64" s="46" t="inlineStr">
+        <is>
+          <t>what does overfitting mean / what does underfitting mean</t>
+        </is>
+      </c>
+      <c r="J64" s="46" t="inlineStr">
+        <is>
+          <t>que veut dire overfitting / underfitting</t>
+        </is>
+      </c>
+      <c r="K64" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L64" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="36" customHeight="1" s="31">
+      <c r="A65" s="45" t="n">
+        <v>62</v>
+      </c>
+      <c r="B65" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C65" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D65" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E65" s="46" t="inlineStr">
+        <is>
+          <t>el code mte3i ma ya5demch / el code mch ta9il</t>
+        </is>
+      </c>
+      <c r="F65" s="46" t="inlineStr">
+        <is>
+          <t>el code mte3i ma ya5demch</t>
+        </is>
+      </c>
+      <c r="G65" s="46" t="inlineStr">
+        <is>
+          <t>el code mch ta9il, el code ma ya5demch, el code fihou error</t>
+        </is>
+      </c>
+      <c r="H65" s="46" t="inlineStr">
+        <is>
+          <t>stuck</t>
+        </is>
+      </c>
+      <c r="I65" s="46" t="inlineStr">
+        <is>
+          <t>my code doesn't work / the code isn't running</t>
+        </is>
+      </c>
+      <c r="J65" s="46" t="inlineStr">
+        <is>
+          <t>mon code ne marche pas / le code ne tourne pas</t>
+        </is>
+      </c>
+      <c r="K65" s="46" t="inlineStr">
+        <is>
+          <t>frustrated</t>
+        </is>
+      </c>
+      <c r="L65" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="36" customHeight="1" s="31">
+      <c r="A66" s="45" t="n">
+        <v>63</v>
+      </c>
+      <c r="B66" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C66" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D66" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E66" s="46" t="inlineStr">
+        <is>
+          <t>el error 9alli heka chnoa ya3ni</t>
+        </is>
+      </c>
+      <c r="F66" s="46" t="inlineStr">
+        <is>
+          <t>el error 9alli heka</t>
+        </is>
+      </c>
+      <c r="G66" s="46" t="inlineStr">
+        <is>
+          <t>el error 9al, el erreur 9alli, chnoa ya3ni el error hedha</t>
+        </is>
+      </c>
+      <c r="H66" s="46" t="inlineStr">
+        <is>
+          <t>technical_question</t>
+        </is>
+      </c>
+      <c r="I66" s="46" t="inlineStr">
+        <is>
+          <t>the error says this what does it mean</t>
+        </is>
+      </c>
+      <c r="J66" s="46" t="inlineStr">
+        <is>
+          <t>l'erreur dit ça qu'est-ce que ça veut dire</t>
+        </is>
+      </c>
+      <c r="K66" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L66" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="36" customHeight="1" s="31">
+      <c r="A67" s="45" t="n">
+        <v>64</v>
+      </c>
+      <c r="B67" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C67" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D67" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E67" s="46" t="inlineStr">
+        <is>
+          <t>kifeh ndibugi el code mte3i</t>
+        </is>
+      </c>
+      <c r="F67" s="46" t="inlineStr">
+        <is>
+          <t>kifeh ndibugi</t>
+        </is>
+      </c>
+      <c r="G67" s="46" t="inlineStr">
+        <is>
+          <t>kifeh ndibugi el code, kifeh ndebug, kifeh n7el el bug</t>
+        </is>
+      </c>
+      <c r="H67" s="46" t="inlineStr">
+        <is>
+          <t>technical_question</t>
+        </is>
+      </c>
+      <c r="I67" s="46" t="inlineStr">
+        <is>
+          <t>how do I debug my code</t>
+        </is>
+      </c>
+      <c r="J67" s="46" t="inlineStr">
+        <is>
+          <t>comment déboguer mon code</t>
+        </is>
+      </c>
+      <c r="K67" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L67" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="36" customHeight="1" s="31">
+      <c r="A68" s="45" t="n">
+        <v>65</v>
+      </c>
+      <c r="B68" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C68" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D68" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E68" s="46" t="inlineStr">
+        <is>
+          <t>ma3rafech chnoa el problem fel code</t>
+        </is>
+      </c>
+      <c r="F68" s="46" t="inlineStr">
+        <is>
+          <t>ma3rafech chnoa el problem</t>
+        </is>
+      </c>
+      <c r="G68" s="46" t="inlineStr">
+        <is>
+          <t>ma3rafech chnoa el mouchkla, ma3rafech fin el ghalta</t>
+        </is>
+      </c>
+      <c r="H68" s="46" t="inlineStr">
+        <is>
+          <t>stuck</t>
+        </is>
+      </c>
+      <c r="I68" s="46" t="inlineStr">
+        <is>
+          <t>I don't know what the problem is in the code</t>
+        </is>
+      </c>
+      <c r="J68" s="46" t="inlineStr">
+        <is>
+          <t>je ne sais pas quel est le problème dans le code</t>
+        </is>
+      </c>
+      <c r="K68" s="46" t="inlineStr">
+        <is>
+          <t>frustrated</t>
+        </is>
+      </c>
+      <c r="L68" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="36" customHeight="1" s="31">
+      <c r="A69" s="45" t="n">
+        <v>66</v>
+      </c>
+      <c r="B69" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C69" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D69" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E69" s="46" t="inlineStr">
+        <is>
+          <t>kifeh nabdah / kifeh nabda b heka</t>
+        </is>
+      </c>
+      <c r="F69" s="46" t="inlineStr">
+        <is>
+          <t>kifeh nabdah</t>
+        </is>
+      </c>
+      <c r="G69" s="46" t="inlineStr">
+        <is>
+          <t>kifeh nabdah, kifeh nabda, mn win nabda</t>
+        </is>
+      </c>
+      <c r="H69" s="46" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
+      <c r="I69" s="46" t="inlineStr">
+        <is>
+          <t>how do I start this / how do I begin</t>
+        </is>
+      </c>
+      <c r="J69" s="46" t="inlineStr">
+        <is>
+          <t>comment commencer ça / par où commencer</t>
+        </is>
+      </c>
+      <c r="K69" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L69" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="36" customHeight="1" s="31">
+      <c r="A70" s="45" t="n">
+        <v>67</v>
+      </c>
+      <c r="B70" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C70" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D70" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E70" s="46" t="inlineStr">
+        <is>
+          <t>chnoa el 5outwet el mba3da ba3d heka</t>
+        </is>
+      </c>
+      <c r="F70" s="46" t="inlineStr">
+        <is>
+          <t>chnoa el 5outwet el mba3da</t>
+        </is>
+      </c>
+      <c r="G70" s="46" t="inlineStr">
+        <is>
+          <t>chnoa el 5outwet, chnoa lba3d, chnoa ba3dha</t>
+        </is>
+      </c>
+      <c r="H70" s="46" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
+      <c r="I70" s="46" t="inlineStr">
+        <is>
+          <t>what are the next steps after this</t>
+        </is>
+      </c>
+      <c r="J70" s="46" t="inlineStr">
+        <is>
+          <t>quelles sont les prochaines étapes après ça</t>
+        </is>
+      </c>
+      <c r="K70" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L70" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="36" customHeight="1" s="31">
+      <c r="A71" s="45" t="n">
+        <v>68</v>
+      </c>
+      <c r="B71" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C71" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D71" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E71" s="46" t="inlineStr">
+        <is>
+          <t>3andek resources / 3andek liens 3la heka</t>
+        </is>
+      </c>
+      <c r="F71" s="46" t="inlineStr">
+        <is>
+          <t>3andek resources</t>
+        </is>
+      </c>
+      <c r="G71" s="46" t="inlineStr">
+        <is>
+          <t>3andek liens, 3andek mawad, 3andek sources 3la heka</t>
+        </is>
+      </c>
+      <c r="H71" s="46" t="inlineStr">
+        <is>
+          <t>resource_request</t>
+        </is>
+      </c>
+      <c r="I71" s="46" t="inlineStr">
+        <is>
+          <t>do you have resources / links on this</t>
+        </is>
+      </c>
+      <c r="J71" s="46" t="inlineStr">
+        <is>
+          <t>tu as des ressources / liens sur ça</t>
+        </is>
+      </c>
+      <c r="K71" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L71" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="36" customHeight="1" s="31">
+      <c r="A72" s="45" t="n">
+        <v>69</v>
+      </c>
+      <c r="B72" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C72" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D72" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E72" s="46" t="inlineStr">
+        <is>
+          <t>heka important wella le / manist7a9ouch</t>
+        </is>
+      </c>
+      <c r="F72" s="46" t="inlineStr">
+        <is>
+          <t>heka important wella le</t>
+        </is>
+      </c>
+      <c r="G72" s="46" t="inlineStr">
+        <is>
+          <t>manist7a9ouch, ma7tajelich heka, heka important?</t>
+        </is>
+      </c>
+      <c r="H72" s="46" t="inlineStr">
+        <is>
+          <t>relevance_check</t>
+        </is>
+      </c>
+      <c r="I72" s="46" t="inlineStr">
+        <is>
+          <t>is this important or not / we don't need this</t>
+        </is>
+      </c>
+      <c r="J72" s="46" t="inlineStr">
+        <is>
+          <t>est-ce important ou non / on n'en a pas besoin</t>
+        </is>
+      </c>
+      <c r="K72" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L72" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="36" customHeight="1" s="31">
+      <c r="A73" s="45" t="n">
+        <v>70</v>
+      </c>
+      <c r="B73" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C73" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D73" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E73" s="46" t="inlineStr">
+        <is>
+          <t>heka barra el programme / heka mch fel cours</t>
+        </is>
+      </c>
+      <c r="F73" s="46" t="inlineStr">
+        <is>
+          <t>heka barra el programme</t>
+        </is>
+      </c>
+      <c r="G73" s="46" t="inlineStr">
+        <is>
+          <t>heka mch fel cours, heka barra, heka mch fl programme</t>
+        </is>
+      </c>
+      <c r="H73" s="46" t="inlineStr">
+        <is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="I73" s="46" t="inlineStr">
+        <is>
+          <t>this is outside the syllabus / not in the course</t>
+        </is>
+      </c>
+      <c r="J73" s="46" t="inlineStr">
+        <is>
+          <t>c'est hors programme / pas dans le cours</t>
+        </is>
+      </c>
+      <c r="K73" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L73" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="36" customHeight="1" s="31">
+      <c r="A74" s="45" t="n">
+        <v>71</v>
+      </c>
+      <c r="B74" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C74" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D74" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E74" s="46" t="inlineStr">
+        <is>
+          <t>a3tini exercice bich n7awil fih</t>
+        </is>
+      </c>
+      <c r="F74" s="46" t="inlineStr">
+        <is>
+          <t>a3tini exercice</t>
+        </is>
+      </c>
+      <c r="G74" s="46" t="inlineStr">
+        <is>
+          <t>a3tini exercice, a3tini tarin, 3tini exercice bich ne5dmou</t>
+        </is>
+      </c>
+      <c r="H74" s="46" t="inlineStr">
+        <is>
+          <t>quiz_request</t>
+        </is>
+      </c>
+      <c r="I74" s="46" t="inlineStr">
+        <is>
+          <t>give me an exercise to practise</t>
+        </is>
+      </c>
+      <c r="J74" s="46" t="inlineStr">
+        <is>
+          <t>donne-moi un exercice pour pratiquer</t>
+        </is>
+      </c>
+      <c r="K74" s="46" t="inlineStr">
+        <is>
+          <t>polite</t>
+        </is>
+      </c>
+      <c r="L74" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="36" customHeight="1" s="31">
+      <c r="A75" s="45" t="n">
+        <v>72</v>
+      </c>
+      <c r="B75" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C75" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D75" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E75" s="46" t="inlineStr">
+        <is>
+          <t>zidni test 3la heka bich na3raf ila fhemt</t>
+        </is>
+      </c>
+      <c r="F75" s="46" t="inlineStr">
+        <is>
+          <t>zidni test</t>
+        </is>
+      </c>
+      <c r="G75" s="46" t="inlineStr">
+        <is>
+          <t>zidni test, a3tini test, 3tini su2al bch naabed</t>
+        </is>
+      </c>
+      <c r="H75" s="46" t="inlineStr">
+        <is>
+          <t>quiz_request</t>
+        </is>
+      </c>
+      <c r="I75" s="46" t="inlineStr">
+        <is>
+          <t>test me on this so I know if I understood</t>
+        </is>
+      </c>
+      <c r="J75" s="46" t="inlineStr">
+        <is>
+          <t>teste-moi là-dessus pour savoir si j'ai compris</t>
+        </is>
+      </c>
+      <c r="K75" s="46" t="inlineStr">
+        <is>
+          <t>polite</t>
+        </is>
+      </c>
+      <c r="L75" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="36" customHeight="1" s="31">
+      <c r="A76" s="45" t="n">
+        <v>73</v>
+      </c>
+      <c r="B76" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C76" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D76" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E76" s="46" t="inlineStr">
+        <is>
+          <t>a3tini mithal bich ne5dmou fih</t>
+        </is>
+      </c>
+      <c r="F76" s="46" t="inlineStr">
+        <is>
+          <t>a3tini mithal bich ne5dmou</t>
+        </is>
+      </c>
+      <c r="G76" s="46" t="inlineStr">
+        <is>
+          <t>a3tini mithal bch ne5dmou, a3tini example bich n7awil</t>
+        </is>
+      </c>
+      <c r="H76" s="46" t="inlineStr">
+        <is>
+          <t>quiz_request</t>
+        </is>
+      </c>
+      <c r="I76" s="46" t="inlineStr">
+        <is>
+          <t>give me an example to work with / to practise</t>
+        </is>
+      </c>
+      <c r="J76" s="46" t="inlineStr">
+        <is>
+          <t>donne-moi un exemple sur lequel travailler</t>
+        </is>
+      </c>
+      <c r="K76" s="46" t="inlineStr">
+        <is>
+          <t>polite</t>
+        </is>
+      </c>
+      <c r="L76" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="36" customHeight="1" s="31">
+      <c r="A77" s="45" t="n">
+        <v>74</v>
+      </c>
+      <c r="B77" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C77" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D77" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E77" s="46" t="inlineStr">
+        <is>
+          <t>fhemt ama 3andi su2al wa7ed</t>
+        </is>
+      </c>
+      <c r="F77" s="46" t="inlineStr">
+        <is>
+          <t>fhemt ama 3andi su2al wa7ed</t>
+        </is>
+      </c>
+      <c r="G77" s="46" t="inlineStr">
+        <is>
+          <t>fhamt ama 3andi su2al, fhimt ama 3andi su2al wahed</t>
+        </is>
+      </c>
+      <c r="H77" s="46" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="I77" s="46" t="inlineStr">
+        <is>
+          <t>I understood but I have one question</t>
+        </is>
+      </c>
+      <c r="J77" s="46" t="inlineStr">
+        <is>
+          <t>j'ai compris mais j'ai une question</t>
+        </is>
+      </c>
+      <c r="K77" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L77" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="36" customHeight="1" s="31">
+      <c r="A78" s="45" t="n">
+        <v>75</v>
+      </c>
+      <c r="B78" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C78" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D78" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E78" s="46" t="inlineStr">
+        <is>
+          <t>w kan 8ali el model chnoa ysir</t>
+        </is>
+      </c>
+      <c r="F78" s="46" t="inlineStr">
+        <is>
+          <t>w kan 8ali el model</t>
+        </is>
+      </c>
+      <c r="G78" s="46" t="inlineStr">
+        <is>
+          <t>w kan 8ali, w kan yo8lot, w kan 8alt el model</t>
+        </is>
+      </c>
+      <c r="H78" s="46" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="I78" s="46" t="inlineStr">
+        <is>
+          <t>and if the model makes a mistake what happens</t>
+        </is>
+      </c>
+      <c r="J78" s="46" t="inlineStr">
+        <is>
+          <t>et si le modèle se trompe que se passe-t-il</t>
+        </is>
+      </c>
+      <c r="K78" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L78" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="36" customHeight="1" s="31">
+      <c r="A79" s="45" t="n">
+        <v>76</v>
+      </c>
+      <c r="B79" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C79" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D79" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E79" s="46" t="inlineStr">
+        <is>
+          <t>w 3andna chwaya data chnoa na3mlou</t>
+        </is>
+      </c>
+      <c r="F79" s="46" t="inlineStr">
+        <is>
+          <t>w 3andna chwaya data</t>
+        </is>
+      </c>
+      <c r="G79" s="46" t="inlineStr">
+        <is>
+          <t>w 3andna data 9lila, w 3andna bezzaf data, chwaya data</t>
+        </is>
+      </c>
+      <c r="H79" s="46" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="I79" s="46" t="inlineStr">
+        <is>
+          <t>and if we have little data what do we do</t>
+        </is>
+      </c>
+      <c r="J79" s="46" t="inlineStr">
+        <is>
+          <t>et si on a peu de données que fait-on</t>
+        </is>
+      </c>
+      <c r="K79" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L79" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="36" customHeight="1" s="31">
+      <c r="A80" s="45" t="n">
+        <v>77</v>
+      </c>
+      <c r="B80" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C80" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D80" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E80" s="46" t="inlineStr">
+        <is>
+          <t>w kan n7eb na3mel heka f real project kifeh</t>
+        </is>
+      </c>
+      <c r="F80" s="46" t="inlineStr">
+        <is>
+          <t>w kan n7eb na3mel heka f real project</t>
+        </is>
+      </c>
+      <c r="G80" s="46" t="inlineStr">
+        <is>
+          <t>w kan n7eb, w kan nheb na3mel, fi projet reel kifeh</t>
+        </is>
+      </c>
+      <c r="H80" s="46" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="I80" s="46" t="inlineStr">
+        <is>
+          <t>and if I want to do this in a real project how</t>
+        </is>
+      </c>
+      <c r="J80" s="46" t="inlineStr">
+        <is>
+          <t>et si je veux faire ça dans un vrai projet comment</t>
+        </is>
+      </c>
+      <c r="K80" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L80" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="36" customHeight="1" s="31">
+      <c r="A81" s="45" t="n">
+        <v>78</v>
+      </c>
+      <c r="B81" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C81" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D81" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E81" s="46" t="inlineStr">
+        <is>
+          <t>zid fassrli lpartie hethi / zid fassarli lpartie hethi</t>
+        </is>
+      </c>
+      <c r="F81" s="46" t="inlineStr">
+        <is>
+          <t>zid fassrli lpartie hethi</t>
+        </is>
+      </c>
+      <c r="G81" s="46" t="inlineStr">
+        <is>
+          <t>zid fassarli, zid fassrli, zid 3la lpartie hethi</t>
+        </is>
+      </c>
+      <c r="H81" s="46" t="inlineStr">
+        <is>
+          <t>continue_deeper</t>
+        </is>
+      </c>
+      <c r="I81" s="46" t="inlineStr">
+        <is>
+          <t>go deeper into this part / explain this part more</t>
+        </is>
+      </c>
+      <c r="J81" s="46" t="inlineStr">
+        <is>
+          <t>approfondis cette partie / explique plus cette partie</t>
+        </is>
+      </c>
+      <c r="K81" s="46" t="inlineStr">
+        <is>
+          <t>polite</t>
+        </is>
+      </c>
+      <c r="L81" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="36" customHeight="1" s="31">
+      <c r="A82" s="45" t="n">
+        <v>79</v>
+      </c>
+      <c r="B82" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C82" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D82" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E82" s="46" t="inlineStr">
+        <is>
+          <t>3tini sommaire mte3 el chapitre</t>
+        </is>
+      </c>
+      <c r="F82" s="46" t="inlineStr">
+        <is>
+          <t>3tini sommaire mte3 el chapitre</t>
+        </is>
+      </c>
+      <c r="G82" s="46" t="inlineStr">
+        <is>
+          <t>3tini sommaire, 3tini summary, 3tini resume lchapter</t>
+        </is>
+      </c>
+      <c r="H82" s="46" t="inlineStr">
+        <is>
+          <t>revision</t>
+        </is>
+      </c>
+      <c r="I82" s="46" t="inlineStr">
+        <is>
+          <t>give me a summary of the chapter</t>
+        </is>
+      </c>
+      <c r="J82" s="46" t="inlineStr">
+        <is>
+          <t>donne-moi un résumé du chapitre</t>
+        </is>
+      </c>
+      <c r="K82" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L82" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="36" customHeight="1" s="31">
+      <c r="A83" s="45" t="n">
+        <v>80</v>
+      </c>
+      <c r="B83" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C83" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D83" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E83" s="46" t="inlineStr">
+        <is>
+          <t>3tini lpoints cles / 3tini ahem 7aja fil chapitre</t>
+        </is>
+      </c>
+      <c r="F83" s="46" t="inlineStr">
+        <is>
+          <t>3tini lpoints cles</t>
+        </is>
+      </c>
+      <c r="G83" s="46" t="inlineStr">
+        <is>
+          <t>3tini lpoints, 3tini les points clés, chnoa ilmouhem</t>
+        </is>
+      </c>
+      <c r="H83" s="46" t="inlineStr">
+        <is>
+          <t>revision</t>
+        </is>
+      </c>
+      <c r="I83" s="46" t="inlineStr">
+        <is>
+          <t>give me the key points / the most important things</t>
+        </is>
+      </c>
+      <c r="J83" s="46" t="inlineStr">
+        <is>
+          <t>donne-moi les points clés / les points les plus importants</t>
+        </is>
+      </c>
+      <c r="K83" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L83" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="36" customHeight="1" s="31">
+      <c r="A84" s="45" t="n">
+        <v>81</v>
+      </c>
+      <c r="B84" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C84" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D84" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E84" s="46" t="inlineStr">
+        <is>
+          <t>rani 3amel revision kol haja 9bal el exam</t>
+        </is>
+      </c>
+      <c r="F84" s="46" t="inlineStr">
+        <is>
+          <t>rani 3amel revision</t>
+        </is>
+      </c>
+      <c r="G84" s="46" t="inlineStr">
+        <is>
+          <t>rani n3amel revision, rani nraja3, rani nrevisi</t>
+        </is>
+      </c>
+      <c r="H84" s="46" t="inlineStr">
+        <is>
+          <t>revision</t>
+        </is>
+      </c>
+      <c r="I84" s="46" t="inlineStr">
+        <is>
+          <t>I'm revising everything before the exam</t>
+        </is>
+      </c>
+      <c r="J84" s="46" t="inlineStr">
+        <is>
+          <t>je révise tout avant l'examen</t>
+        </is>
+      </c>
+      <c r="K84" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L84" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="36" customHeight="1" s="31">
+      <c r="A85" s="45" t="n">
+        <v>82</v>
+      </c>
+      <c r="B85" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C85" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D85" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E85" s="46" t="inlineStr">
+        <is>
+          <t>rakkez m3aya hna heka lazm t7fdhou</t>
+        </is>
+      </c>
+      <c r="F85" s="46" t="inlineStr">
+        <is>
+          <t>rakkez m3aya hna</t>
+        </is>
+      </c>
+      <c r="G85" s="46" t="inlineStr">
+        <is>
+          <t>rakkez m3ay hna, ركز معايا هنا, heka lazm t7fdhou</t>
+        </is>
+      </c>
+      <c r="H85" s="46" t="inlineStr">
+        <is>
+          <t>critical_flag</t>
+        </is>
+      </c>
+      <c r="I85" s="46" t="inlineStr">
+        <is>
+          <t>focus with me here you must memorise this</t>
+        </is>
+      </c>
+      <c r="J85" s="46" t="inlineStr">
+        <is>
+          <t>concentre-toi avec moi ici tu dois mémoriser ça</t>
+        </is>
+      </c>
+      <c r="K85" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L85" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="36" customHeight="1" s="31">
+      <c r="A86" s="45" t="n">
+        <v>83</v>
+      </c>
+      <c r="B86" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C86" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D86" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E86" s="46" t="inlineStr">
+        <is>
+          <t>asma3ni ya weldi fech te7ki heka 8alat</t>
+        </is>
+      </c>
+      <c r="F86" s="46" t="inlineStr">
+        <is>
+          <t>asma3ni</t>
+        </is>
+      </c>
+      <c r="G86" s="46" t="inlineStr">
+        <is>
+          <t>asma3, asma3 m3aya, asma3ni</t>
+        </is>
+      </c>
+      <c r="H86" s="46" t="inlineStr">
+        <is>
+          <t>hallucination</t>
+        </is>
+      </c>
+      <c r="I86" s="46" t="inlineStr">
+        <is>
+          <t>listen to me — what you're saying is wrong</t>
+        </is>
+      </c>
+      <c r="J86" s="46" t="inlineStr">
+        <is>
+          <t>écoute-moi — ce que tu dis est faux</t>
+        </is>
+      </c>
+      <c r="K86" s="46" t="inlineStr">
+        <is>
+          <t>aggressive</t>
+        </is>
+      </c>
+      <c r="L86" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="36" customHeight="1" s="31">
+      <c r="A87" s="45" t="n">
+        <v>84</v>
+      </c>
+      <c r="B87" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C87" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D87" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E87" s="46" t="inlineStr">
+        <is>
+          <t>ya weldi fech te7ki heka mch s7i7</t>
+        </is>
+      </c>
+      <c r="F87" s="46" t="inlineStr">
+        <is>
+          <t>ya weldi fech te7ki</t>
+        </is>
+      </c>
+      <c r="G87" s="46" t="inlineStr">
+        <is>
+          <t>ya weldi, ya wlidi, ya weldi fech te7ki</t>
+        </is>
+      </c>
+      <c r="H87" s="46" t="inlineStr">
+        <is>
+          <t>hallucination</t>
+        </is>
+      </c>
+      <c r="I87" s="46" t="inlineStr">
+        <is>
+          <t>my son what are you saying this isn't right (frustration/aggression signal)</t>
+        </is>
+      </c>
+      <c r="J87" s="46" t="inlineStr">
+        <is>
+          <t>mon fils qu'est-ce que tu dis c'est pas juste</t>
+        </is>
+      </c>
+      <c r="K87" s="46" t="inlineStr">
+        <is>
+          <t>aggressive</t>
+        </is>
+      </c>
+      <c r="L87" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="36" customHeight="1" s="31">
+      <c r="A88" s="45" t="n">
+        <v>85</v>
+      </c>
+      <c r="B88" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C88" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D88" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E88" s="46" t="inlineStr">
+        <is>
+          <t>kamil kamil zid / kamil zid fassarli</t>
+        </is>
+      </c>
+      <c r="F88" s="46" t="inlineStr">
+        <is>
+          <t>kamil kamil</t>
+        </is>
+      </c>
+      <c r="G88" s="46" t="inlineStr">
+        <is>
+          <t>kamil kamil, kamil, kamil zid</t>
+        </is>
+      </c>
+      <c r="H88" s="46" t="inlineStr">
+        <is>
+          <t>encouragement</t>
+        </is>
+      </c>
+      <c r="I88" s="46" t="inlineStr">
+        <is>
+          <t>keep going / continue keep going</t>
+        </is>
+      </c>
+      <c r="J88" s="46" t="inlineStr">
+        <is>
+          <t>continue / continue encore</t>
+        </is>
+      </c>
+      <c r="K88" s="46" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="L88" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="36" customHeight="1" s="31">
+      <c r="A89" s="45" t="n">
+        <v>86</v>
+      </c>
+      <c r="B89" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C89" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D89" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E89" s="46" t="inlineStr">
+        <is>
+          <t>haya nkamlou / aya nkamlou</t>
+        </is>
+      </c>
+      <c r="F89" s="46" t="inlineStr">
+        <is>
+          <t>haya nkamlou</t>
+        </is>
+      </c>
+      <c r="G89" s="46" t="inlineStr">
+        <is>
+          <t>haya nkammelou, aya nkamlou, yalla nkammelou</t>
+        </is>
+      </c>
+      <c r="H89" s="46" t="inlineStr">
+        <is>
+          <t>transition</t>
+        </is>
+      </c>
+      <c r="I89" s="46" t="inlineStr">
+        <is>
+          <t>let's continue / let's keep going</t>
+        </is>
+      </c>
+      <c r="J89" s="46" t="inlineStr">
+        <is>
+          <t>continuons / allons-y</t>
+        </is>
+      </c>
+      <c r="K89" s="46" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="L89" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="36" customHeight="1" s="31">
+      <c r="A90" s="45" t="n">
+        <v>87</v>
+      </c>
+      <c r="B90" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C90" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D90" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E90" s="46" t="inlineStr">
+        <is>
+          <t>aya yzina mn hethi 5alina nabda b...</t>
+        </is>
+      </c>
+      <c r="F90" s="46" t="inlineStr">
+        <is>
+          <t>aya yzina mn hethi</t>
+        </is>
+      </c>
+      <c r="G90" s="46" t="inlineStr">
+        <is>
+          <t>aya yzina, yezzi 3la heka, yzina mn hethi</t>
+        </is>
+      </c>
+      <c r="H90" s="46" t="inlineStr">
+        <is>
+          <t>transition</t>
+        </is>
+      </c>
+      <c r="I90" s="46" t="inlineStr">
+        <is>
+          <t>enough on this let's move on to...</t>
+        </is>
+      </c>
+      <c r="J90" s="46" t="inlineStr">
+        <is>
+          <t>assez là-dessus passons à...</t>
+        </is>
+      </c>
+      <c r="K90" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L90" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="36" customHeight="1" s="31">
+      <c r="A91" s="45" t="n">
+        <v>88</v>
+      </c>
+      <c r="B91" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C91" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D91" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E91" s="46" t="inlineStr">
+        <is>
+          <t>t7eb nzid nfassarlk wala nwazslou</t>
+        </is>
+      </c>
+      <c r="F91" s="46" t="inlineStr">
+        <is>
+          <t>t7eb nzid nfassarlk wala nwazslou</t>
+        </is>
+      </c>
+      <c r="G91" s="46" t="inlineStr">
+        <is>
+          <t>t7eb nzid wala nwazslou, nzid nfassarlk wala nkammelou</t>
+        </is>
+      </c>
+      <c r="H91" s="46" t="inlineStr">
+        <is>
+          <t>transition</t>
+        </is>
+      </c>
+      <c r="I91" s="46" t="inlineStr">
+        <is>
+          <t>do you want more explanation or should we continue</t>
+        </is>
+      </c>
+      <c r="J91" s="46" t="inlineStr">
+        <is>
+          <t>tu veux plus d'explications ou on continue</t>
+        </is>
+      </c>
+      <c r="K91" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L91" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="36" customHeight="1" s="31">
+      <c r="A92" s="45" t="n">
+        <v>89</v>
+      </c>
+      <c r="B92" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C92" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D92" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E92" s="46" t="inlineStr">
+        <is>
+          <t>rak 9rib ama mch complet</t>
+        </is>
+      </c>
+      <c r="F92" s="46" t="inlineStr">
+        <is>
+          <t>rak 9rib ama</t>
+        </is>
+      </c>
+      <c r="G92" s="46" t="inlineStr">
+        <is>
+          <t>rak 9rib, mch b3id ama, 9rib ama mch s7i7 complet</t>
+        </is>
+      </c>
+      <c r="H92" s="46" t="inlineStr">
+        <is>
+          <t>partial_correct</t>
+        </is>
+      </c>
+      <c r="I92" s="46" t="inlineStr">
+        <is>
+          <t>you're close but not complete</t>
+        </is>
+      </c>
+      <c r="J92" s="46" t="inlineStr">
+        <is>
+          <t>tu es proche mais pas complet</t>
+        </is>
+      </c>
+      <c r="K92" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L92" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="36" customHeight="1" s="31">
+      <c r="A93" s="45" t="n">
+        <v>90</v>
+      </c>
+      <c r="B93" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C93" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D93" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E93" s="46" t="inlineStr">
+        <is>
+          <t>l'idée s7i7a ama el tatbi9 8alat</t>
+        </is>
+      </c>
+      <c r="F93" s="46" t="inlineStr">
+        <is>
+          <t>l'idée s7i7a ama el tatbi9 8alat</t>
+        </is>
+      </c>
+      <c r="G93" s="46" t="inlineStr">
+        <is>
+          <t>l'idée s7i7a, el fikra s7i7a, ama el tatbi9 8alat</t>
+        </is>
+      </c>
+      <c r="H93" s="46" t="inlineStr">
+        <is>
+          <t>partial_correct</t>
+        </is>
+      </c>
+      <c r="I93" s="46" t="inlineStr">
+        <is>
+          <t>the idea is right but the application is wrong</t>
+        </is>
+      </c>
+      <c r="J93" s="46" t="inlineStr">
+        <is>
+          <t>l'idée est correcte mais l'application est fausse</t>
+        </is>
+      </c>
+      <c r="K93" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L93" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="36" customHeight="1" s="31">
+      <c r="A94" s="45" t="n">
+        <v>91</v>
+      </c>
+      <c r="B94" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C94" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D94" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E94" s="46" t="inlineStr">
+        <is>
+          <t>hethi 8alta commune barcha mch lazm t5altet</t>
+        </is>
+      </c>
+      <c r="F94" s="46" t="inlineStr">
+        <is>
+          <t>hethi 8alta commune barcha</t>
+        </is>
+      </c>
+      <c r="G94" s="46" t="inlineStr">
+        <is>
+          <t>8alta commune, 8alta chay3a, 8alta elli ysiru fiha</t>
+        </is>
+      </c>
+      <c r="H94" s="46" t="inlineStr">
+        <is>
+          <t>common_mistake</t>
+        </is>
+      </c>
+      <c r="I94" s="46" t="inlineStr">
+        <is>
+          <t>this is a very common mistake don't confuse them</t>
+        </is>
+      </c>
+      <c r="J94" s="46" t="inlineStr">
+        <is>
+          <t>c'est une erreur très commune ne les confonds pas</t>
+        </is>
+      </c>
+      <c r="K94" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L94" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="36" customHeight="1" s="31">
+      <c r="A95" s="45" t="n">
+        <v>92</v>
+      </c>
+      <c r="B95" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C95" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D95" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E95" s="46" t="inlineStr">
+        <is>
+          <t>9aad tra fil far9 / t5altet bin X w Y</t>
+        </is>
+      </c>
+      <c r="F95" s="46" t="inlineStr">
+        <is>
+          <t>9aad tra fil far9</t>
+        </is>
+      </c>
+      <c r="G95" s="46" t="inlineStr">
+        <is>
+          <t>9aad tra, t5altet, 5altet bin X w Y</t>
+        </is>
+      </c>
+      <c r="H95" s="46" t="inlineStr">
+        <is>
+          <t>common_mistake</t>
+        </is>
+      </c>
+      <c r="I95" s="46" t="inlineStr">
+        <is>
+          <t>you fell into the difference trap / you confused X and Y</t>
+        </is>
+      </c>
+      <c r="J95" s="46" t="inlineStr">
+        <is>
+          <t>tu es tombé dans le piège de la différence</t>
+        </is>
+      </c>
+      <c r="K95" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L95" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="36" customHeight="1" s="31">
+      <c r="A96" s="45" t="n">
+        <v>93</v>
+      </c>
+      <c r="B96" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C96" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D96" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E96" s="46" t="inlineStr">
+        <is>
+          <t>tsawer kima / tsawer kan 3andek...</t>
+        </is>
+      </c>
+      <c r="F96" s="46" t="inlineStr">
+        <is>
+          <t>tsawer kima</t>
+        </is>
+      </c>
+      <c r="G96" s="46" t="inlineStr">
+        <is>
+          <t>tsawer, tsawer kan, tsawer kima 3andek</t>
+        </is>
+      </c>
+      <c r="H96" s="46" t="inlineStr">
+        <is>
+          <t>analogy</t>
+        </is>
+      </c>
+      <c r="I96" s="46" t="inlineStr">
+        <is>
+          <t>imagine like / imagine if you had... (analogy opener)</t>
+        </is>
+      </c>
+      <c r="J96" s="46" t="inlineStr">
+        <is>
+          <t>imagine comme / imagine que tu as...</t>
+        </is>
+      </c>
+      <c r="K96" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L96" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="36" customHeight="1" s="31">
+      <c r="A97" s="45" t="n">
+        <v>94</v>
+      </c>
+      <c r="B97" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C97" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D97" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E97" s="46" t="inlineStr">
+        <is>
+          <t>5alina nabdew b mithal / par exemple</t>
+        </is>
+      </c>
+      <c r="F97" s="46" t="inlineStr">
+        <is>
+          <t>5alina nabdew b mithal</t>
+        </is>
+      </c>
+      <c r="G97" s="46" t="inlineStr">
+        <is>
+          <t>5alina nabdew b mithal, par exemple, bel mithal</t>
+        </is>
+      </c>
+      <c r="H97" s="46" t="inlineStr">
+        <is>
+          <t>analogy</t>
+        </is>
+      </c>
+      <c r="I97" s="46" t="inlineStr">
+        <is>
+          <t>let's start with an example / for example</t>
+        </is>
+      </c>
+      <c r="J97" s="46" t="inlineStr">
+        <is>
+          <t>commençons par un exemple / par exemple</t>
+        </is>
+      </c>
+      <c r="K97" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L97" s="46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="36" customHeight="1" s="31">
+      <c r="A98" s="45" t="n">
+        <v>95</v>
+      </c>
+      <c r="B98" s="46" t="inlineStr">
+        <is>
+          <t>Edu chatbot</t>
+        </is>
+      </c>
+      <c r="C98" s="46" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="D98" s="46" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="E98" s="46" t="inlineStr">
+        <is>
+          <t>tefhem fia / fhemtni wla nzid nfassarlk / kan mafhemtch 7aja 9oli</t>
+        </is>
+      </c>
+      <c r="F98" s="46" t="inlineStr">
+        <is>
+          <t>tefhem fia</t>
+        </is>
+      </c>
+      <c r="G98" s="46" t="inlineStr">
+        <is>
+          <t>tefhem fia, fhemtni, fhemtni wla nzid, kan mafhemtch 9oli</t>
+        </is>
+      </c>
+      <c r="H98" s="46" t="inlineStr">
+        <is>
+          <t>comprehension_check</t>
+        </is>
+      </c>
+      <c r="I98" s="46" t="inlineStr">
+        <is>
+          <t>do you understand me / did you get it or should I explain more / if you didn't understand something tell me</t>
+        </is>
+      </c>
+      <c r="J98" s="46" t="inlineStr">
+        <is>
+          <t>tu me comprends / tu as compris ou j'explique encore / si tu n'as pas compris dis-moi</t>
+        </is>
+      </c>
+      <c r="K98" s="46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="L98" s="46" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -4746,15 +7991,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="31" min="1" max="1"/>
     <col width="10" customWidth="1" style="31" min="2" max="2"/>
-    <col width="46" customWidth="1" style="31" min="3" max="3"/>
+    <col width="48" customWidth="1" style="31" min="3" max="3"/>
     <col width="46" customWidth="1" style="31" min="4" max="5"/>
     <col width="40" customWidth="1" style="31" min="5" max="5"/>
-    <col width="54" customWidth="1" style="31" min="6" max="6"/>
+    <col width="56" customWidth="1" style="31" min="6" max="6"/>
     <col width="14" customWidth="1" style="31" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -5593,6 +8838,486 @@
       <c r="F28" s="46" t="inlineStr">
         <is>
           <t>Warm close — confirm understanding, offer to continue</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="40" customHeight="1" s="31">
+      <c r="A29" s="45" t="inlineStr">
+        <is>
+          <t>uncertainty</t>
+        </is>
+      </c>
+      <c r="B29" s="45" t="n">
+        <v>15</v>
+      </c>
+      <c r="C29" s="46" t="inlineStr">
+        <is>
+          <t>manich sur, mch met2akked, kank makch sur 9oli</t>
+        </is>
+      </c>
+      <c r="D29" s="46" t="inlineStr">
+        <is>
+          <t>manich met2akked, mch sur</t>
+        </is>
+      </c>
+      <c r="E29" s="46" t="inlineStr">
+        <is>
+          <t>manichsur,mchmet2akked,kankmaakchsur</t>
+        </is>
+      </c>
+      <c r="F29" s="46" t="inlineStr">
+        <is>
+          <t>Signal uncertainty clearly before answering — use: manich sur</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="40" customHeight="1" s="31">
+      <c r="A30" s="58" t="inlineStr">
+        <is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="B30" s="58" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="C30" s="55" t="inlineStr">
+        <is>
+          <t>lmaalouma hethi mouch mawjouda, heka mch mektoub 3andna</t>
+        </is>
+      </c>
+      <c r="D30" s="55" t="inlineStr">
+        <is>
+          <t>heka barra el programme, heka mch fel cours</t>
+        </is>
+      </c>
+      <c r="E30" s="55" t="inlineStr">
+        <is>
+          <t>lmaalouma,hekamchmektoub,hekabarra</t>
+        </is>
+      </c>
+      <c r="F30" s="55" t="inlineStr">
+        <is>
+          <t>Acknowledge limit — say: heka mch mektoub 3andna</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="40" customHeight="1" s="31">
+      <c r="A31" s="45" t="inlineStr">
+        <is>
+          <t>clarification_request</t>
+        </is>
+      </c>
+      <c r="B31" s="45" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="C31" s="46" t="inlineStr">
+        <is>
+          <t>zid watha7li sou2alk, tsaleni 3la X wella 3la Y</t>
+        </is>
+      </c>
+      <c r="D31" s="46" t="inlineStr">
+        <is>
+          <t>zid watha7li, confirmi el section</t>
+        </is>
+      </c>
+      <c r="E31" s="46" t="inlineStr">
+        <is>
+          <t>zidwatha7li,tsaleni3la</t>
+        </is>
+      </c>
+      <c r="F31" s="46" t="inlineStr">
+        <is>
+          <t>Ask student to clarify BEFORE answering to avoid hallucination</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1" s="31">
+      <c r="A32" s="58" t="inlineStr">
+        <is>
+          <t>exam_context</t>
+        </is>
+      </c>
+      <c r="B32" s="58" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C32" s="55" t="inlineStr">
+        <is>
+          <t>fel exam jaw b su2al kima hedha, bch n3addi el exam</t>
+        </is>
+      </c>
+      <c r="D32" s="55" t="inlineStr">
+        <is>
+          <t>fel examen, fil imti7an, bch nfût, bch nnajah</t>
+        </is>
+      </c>
+      <c r="E32" s="55" t="inlineStr">
+        <is>
+          <t>felexam,bch n3addi,bchnnajah</t>
+        </is>
+      </c>
+      <c r="F32" s="55" t="inlineStr">
+        <is>
+          <t>Prioritise exam-relevant explanation — flag critical content</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="40" customHeight="1" s="31">
+      <c r="A33" s="45" t="inlineStr">
+        <is>
+          <t>stuck</t>
+        </is>
+      </c>
+      <c r="B33" s="45" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C33" s="46" t="inlineStr">
+        <is>
+          <t>rani w7it, w7it f 7aja specific, ma3rafech chnoa el problem</t>
+        </is>
+      </c>
+      <c r="D33" s="46" t="inlineStr">
+        <is>
+          <t>rani w9aft, wa9fait, w7it f projet</t>
+        </is>
+      </c>
+      <c r="E33" s="46" t="inlineStr">
+        <is>
+          <t>raniw7it,w9aft,wa9fait</t>
+        </is>
+      </c>
+      <c r="F33" s="46" t="inlineStr">
+        <is>
+          <t>Diagnose the stuck point before explaining — ask: fin bil3id w7it?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="40" customHeight="1" s="31">
+      <c r="A34" s="58" t="inlineStr">
+        <is>
+          <t>technical_question</t>
+        </is>
+      </c>
+      <c r="B34" s="58" t="n">
+        <v>7</v>
+      </c>
+      <c r="C34" s="55" t="inlineStr">
+        <is>
+          <t>kifeh n7assen el accuracy, el error 9alli heka, kifeh ndibugi</t>
+        </is>
+      </c>
+      <c r="D34" s="55" t="inlineStr">
+        <is>
+          <t>kifeh nrfa3, el erreur 9alli, kifeh ndebug</t>
+        </is>
+      </c>
+      <c r="E34" s="55" t="inlineStr">
+        <is>
+          <t>kifeh n7assen,el error 9alli,kifeh ndibugi</t>
+        </is>
+      </c>
+      <c r="F34" s="55" t="inlineStr">
+        <is>
+          <t>Answer technically — use source if from course, flag if not</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="40" customHeight="1" s="31">
+      <c r="A35" s="45" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
+      <c r="B35" s="45" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C35" s="46" t="inlineStr">
+        <is>
+          <t>kifeh nabdah, chnoa el 5outwet el mba3da</t>
+        </is>
+      </c>
+      <c r="D35" s="46" t="inlineStr">
+        <is>
+          <t>kifeh nabda, mn win nabda, chnoa lba3d</t>
+        </is>
+      </c>
+      <c r="E35" s="46" t="inlineStr">
+        <is>
+          <t>kifehnabdah,chnoa el5outwet</t>
+        </is>
+      </c>
+      <c r="F35" s="46" t="inlineStr">
+        <is>
+          <t>Guide student to next step or starting point clearly</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="40" customHeight="1" s="31">
+      <c r="A36" s="58" t="inlineStr">
+        <is>
+          <t>resource_request</t>
+        </is>
+      </c>
+      <c r="B36" s="58" t="n">
+        <v>8</v>
+      </c>
+      <c r="C36" s="55" t="inlineStr">
+        <is>
+          <t>3andek resources, 3andek liens 3la heka</t>
+        </is>
+      </c>
+      <c r="D36" s="55" t="inlineStr">
+        <is>
+          <t>3andek mawad, 3andek sources</t>
+        </is>
+      </c>
+      <c r="E36" s="55" t="inlineStr">
+        <is>
+          <t>3andekresources,3andekliens</t>
+        </is>
+      </c>
+      <c r="F36" s="55" t="inlineStr">
+        <is>
+          <t>Provide course section reference first — external links if needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="40" customHeight="1" s="31">
+      <c r="A37" s="45" t="inlineStr">
+        <is>
+          <t>relevance_check</t>
+        </is>
+      </c>
+      <c r="B37" s="45" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="C37" s="46" t="inlineStr">
+        <is>
+          <t>heka important wella le, manist7a9ouch</t>
+        </is>
+      </c>
+      <c r="D37" s="46" t="inlineStr">
+        <is>
+          <t>ma7tajelich heka, heka important?</t>
+        </is>
+      </c>
+      <c r="E37" s="46" t="inlineStr">
+        <is>
+          <t>hekaimportant,manist7a9ouch</t>
+        </is>
+      </c>
+      <c r="F37" s="46" t="inlineStr">
+        <is>
+          <t>Confirm relevance — link to exam/course if applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="40" customHeight="1" s="31">
+      <c r="A38" s="58" t="inlineStr">
+        <is>
+          <t>revision</t>
+        </is>
+      </c>
+      <c r="B38" s="58" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C38" s="55" t="inlineStr">
+        <is>
+          <t>3tini sommaire, 3tini lpoints cles, rani 3amel revision</t>
+        </is>
+      </c>
+      <c r="D38" s="55" t="inlineStr">
+        <is>
+          <t>3tini resume, 3tini summary, chnoa ilmouhem</t>
+        </is>
+      </c>
+      <c r="E38" s="55" t="inlineStr">
+        <is>
+          <t>3tinisommaire,3tinilpoints,rani3amelrevision</t>
+        </is>
+      </c>
+      <c r="F38" s="55" t="inlineStr">
+        <is>
+          <t>Provide structured summary: key points + exam tips</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="40" customHeight="1" s="31">
+      <c r="A39" s="45" t="inlineStr">
+        <is>
+          <t>quiz_request</t>
+        </is>
+      </c>
+      <c r="B39" s="45" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="C39" s="46" t="inlineStr">
+        <is>
+          <t>a3tini exercice, zidni test, a3tini mithal bich ne5dmou</t>
+        </is>
+      </c>
+      <c r="D39" s="46" t="inlineStr">
+        <is>
+          <t>a3tini exercice, zidni test, 3tini su2al bch naabed</t>
+        </is>
+      </c>
+      <c r="E39" s="46" t="inlineStr">
+        <is>
+          <t>a3tiniexercice,zidnitest</t>
+        </is>
+      </c>
+      <c r="F39" s="46" t="inlineStr">
+        <is>
+          <t>Generate a practice question matching the topic level</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="40" customHeight="1" s="31">
+      <c r="A40" s="58" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="B40" s="58" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C40" s="55" t="inlineStr">
+        <is>
+          <t>fhemt ama 3andi su2al wa7ed, w kan 8ali el model, zid fassrli lpartie hethi</t>
+        </is>
+      </c>
+      <c r="D40" s="55" t="inlineStr">
+        <is>
+          <t>fhamt ama su2al, w kan 8ali, zid fassarli</t>
+        </is>
+      </c>
+      <c r="E40" s="55" t="inlineStr">
+        <is>
+          <t>fhemtama,wkan8ali,zidfassrli</t>
+        </is>
+      </c>
+      <c r="F40" s="55" t="inlineStr">
+        <is>
+          <t>Answer the follow-up specifically — don't re-explain from scratch</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="40" customHeight="1" s="31">
+      <c r="A41" s="45" t="inlineStr">
+        <is>
+          <t>common_mistake</t>
+        </is>
+      </c>
+      <c r="B41" s="45" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C41" s="46" t="inlineStr">
+        <is>
+          <t>hethi 8alta commune barcha, 9aad tra fil far9</t>
+        </is>
+      </c>
+      <c r="D41" s="46" t="inlineStr">
+        <is>
+          <t>8alta chay3a, t5altet, 5altet bin X w Y</t>
+        </is>
+      </c>
+      <c r="E41" s="46" t="inlineStr">
+        <is>
+          <t>8altacommune,9aadtrafil far9</t>
+        </is>
+      </c>
+      <c r="F41" s="46" t="inlineStr">
+        <is>
+          <t>Correct gently — use: hethi 8alta commune / rak 9rib ama...</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="40" customHeight="1" s="31">
+      <c r="A42" s="58" t="inlineStr">
+        <is>
+          <t>partial_correct</t>
+        </is>
+      </c>
+      <c r="B42" s="58" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="C42" s="55" t="inlineStr">
+        <is>
+          <t>rak 9rib ama, l'idée s7i7a ama el tatbi9 8alat, mch b3id ama</t>
+        </is>
+      </c>
+      <c r="D42" s="55" t="inlineStr">
+        <is>
+          <t>9rib ama mch complet, l'idée s7i7a</t>
+        </is>
+      </c>
+      <c r="E42" s="55" t="inlineStr">
+        <is>
+          <t>rak9rib,idees7i7a,mchb3id</t>
+        </is>
+      </c>
+      <c r="F42" s="55" t="inlineStr">
+        <is>
+          <t>Acknowledge what's right before correcting — never just say 8alat</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="40" customHeight="1" s="31">
+      <c r="A43" s="45" t="inlineStr">
+        <is>
+          <t>transition</t>
+        </is>
+      </c>
+      <c r="B43" s="45" t="n">
+        <v>9</v>
+      </c>
+      <c r="C43" s="46" t="inlineStr">
+        <is>
+          <t>haya nkamlou, aya yzina mn hethi, t7eb nzid nfassarlk wala nwazslou</t>
+        </is>
+      </c>
+      <c r="D43" s="46" t="inlineStr">
+        <is>
+          <t>aya nkamlou, yezzi 3la heka, nwazslou</t>
+        </is>
+      </c>
+      <c r="E43" s="46" t="inlineStr">
+        <is>
+          <t>hayankamlou,ayayzina,nwazslou</t>
+        </is>
+      </c>
+      <c r="F43" s="46" t="inlineStr">
+        <is>
+          <t>Check understanding before moving on — don't auto-advance</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="40" customHeight="1" s="31">
+      <c r="A44" s="58" t="inlineStr">
+        <is>
+          <t>comprehension_check</t>
+        </is>
+      </c>
+      <c r="B44" s="58" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="C44" s="55" t="inlineStr">
+        <is>
+          <t>tefhem fia, fhemtni wla nzid nfassarlk, kan mafhemtch 7aja 9oli</t>
+        </is>
+      </c>
+      <c r="D44" s="55" t="inlineStr">
+        <is>
+          <t>tefhemni, fhemtni, kan mch fahi 9oli</t>
+        </is>
+      </c>
+      <c r="E44" s="55" t="inlineStr">
+        <is>
+          <t>tefhemfia,fhemtni,kanmafhemtch</t>
+        </is>
+      </c>
+      <c r="F44" s="55" t="inlineStr">
+        <is>
+          <t>Always check after explanation — don't assume understood</t>
         </is>
       </c>
     </row>
@@ -5698,7 +9423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="31" min="1" max="1"/>
@@ -6202,6 +9927,294 @@
       </c>
       <c r="D28" s="45">
         <f>IF(B28&gt;=C28,"✅ Done",IF(B28=0,"🔴 Empty","🟡 In Progress"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1" s="31">
+      <c r="A29" s="46" t="inlineStr">
+        <is>
+          <t>uncertainty</t>
+        </is>
+      </c>
+      <c r="B29" s="45">
+        <f>COUNTIF('Raw Collection'!H:H,A29)</f>
+        <v/>
+      </c>
+      <c r="C29" s="45" t="n">
+        <v>20</v>
+      </c>
+      <c r="D29" s="45">
+        <f>IF(B29&gt;=C29,"✅ Done",IF(B29=0,"🔴 Empty","🟡 In Progress"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1" s="31">
+      <c r="A30" s="55" t="inlineStr">
+        <is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="B30" s="58">
+        <f>COUNTIF('Raw Collection'!H:H,A30)</f>
+        <v/>
+      </c>
+      <c r="C30" s="58" t="n">
+        <v>20</v>
+      </c>
+      <c r="D30" s="58">
+        <f>IF(B30&gt;=C30,"✅ Done",IF(B30=0,"🔴 Empty","🟡 In Progress"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1" s="31">
+      <c r="A31" s="46" t="inlineStr">
+        <is>
+          <t>clarification_request</t>
+        </is>
+      </c>
+      <c r="B31" s="45">
+        <f>COUNTIF('Raw Collection'!H:H,A31)</f>
+        <v/>
+      </c>
+      <c r="C31" s="45" t="n">
+        <v>25</v>
+      </c>
+      <c r="D31" s="45">
+        <f>IF(B31&gt;=C31,"✅ Done",IF(B31=0,"🔴 Empty","🟡 In Progress"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1" s="31">
+      <c r="A32" s="55" t="inlineStr">
+        <is>
+          <t>exam_context</t>
+        </is>
+      </c>
+      <c r="B32" s="58">
+        <f>COUNTIF('Raw Collection'!H:H,A32)</f>
+        <v/>
+      </c>
+      <c r="C32" s="58" t="n">
+        <v>25</v>
+      </c>
+      <c r="D32" s="58">
+        <f>IF(B32&gt;=C32,"✅ Done",IF(B32=0,"🔴 Empty","🟡 In Progress"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1" s="31">
+      <c r="A33" s="46" t="inlineStr">
+        <is>
+          <t>stuck</t>
+        </is>
+      </c>
+      <c r="B33" s="45">
+        <f>COUNTIF('Raw Collection'!H:H,A33)</f>
+        <v/>
+      </c>
+      <c r="C33" s="45" t="n">
+        <v>20</v>
+      </c>
+      <c r="D33" s="45">
+        <f>IF(B33&gt;=C33,"✅ Done",IF(B33=0,"🔴 Empty","🟡 In Progress"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1" s="31">
+      <c r="A34" s="55" t="inlineStr">
+        <is>
+          <t>technical_question</t>
+        </is>
+      </c>
+      <c r="B34" s="58">
+        <f>COUNTIF('Raw Collection'!H:H,A34)</f>
+        <v/>
+      </c>
+      <c r="C34" s="58" t="n">
+        <v>30</v>
+      </c>
+      <c r="D34" s="58">
+        <f>IF(B34&gt;=C34,"✅ Done",IF(B34=0,"🔴 Empty","🟡 In Progress"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1" s="31">
+      <c r="A35" s="46" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
+      <c r="B35" s="45">
+        <f>COUNTIF('Raw Collection'!H:H,A35)</f>
+        <v/>
+      </c>
+      <c r="C35" s="45" t="n">
+        <v>20</v>
+      </c>
+      <c r="D35" s="45">
+        <f>IF(B35&gt;=C35,"✅ Done",IF(B35=0,"🔴 Empty","🟡 In Progress"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1" s="31">
+      <c r="A36" s="55" t="inlineStr">
+        <is>
+          <t>resource_request</t>
+        </is>
+      </c>
+      <c r="B36" s="58">
+        <f>COUNTIF('Raw Collection'!H:H,A36)</f>
+        <v/>
+      </c>
+      <c r="C36" s="58" t="n">
+        <v>15</v>
+      </c>
+      <c r="D36" s="58">
+        <f>IF(B36&gt;=C36,"✅ Done",IF(B36=0,"🔴 Empty","🟡 In Progress"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1" s="31">
+      <c r="A37" s="46" t="inlineStr">
+        <is>
+          <t>relevance_check</t>
+        </is>
+      </c>
+      <c r="B37" s="45">
+        <f>COUNTIF('Raw Collection'!H:H,A37)</f>
+        <v/>
+      </c>
+      <c r="C37" s="45" t="n">
+        <v>15</v>
+      </c>
+      <c r="D37" s="45">
+        <f>IF(B37&gt;=C37,"✅ Done",IF(B37=0,"🔴 Empty","🟡 In Progress"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="24" customHeight="1" s="31">
+      <c r="A38" s="55" t="inlineStr">
+        <is>
+          <t>revision</t>
+        </is>
+      </c>
+      <c r="B38" s="58">
+        <f>COUNTIF('Raw Collection'!H:H,A38)</f>
+        <v/>
+      </c>
+      <c r="C38" s="58" t="n">
+        <v>25</v>
+      </c>
+      <c r="D38" s="58">
+        <f>IF(B38&gt;=C38,"✅ Done",IF(B38=0,"🔴 Empty","🟡 In Progress"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1" s="31">
+      <c r="A39" s="46" t="inlineStr">
+        <is>
+          <t>quiz_request</t>
+        </is>
+      </c>
+      <c r="B39" s="45">
+        <f>COUNTIF('Raw Collection'!H:H,A39)</f>
+        <v/>
+      </c>
+      <c r="C39" s="45" t="n">
+        <v>25</v>
+      </c>
+      <c r="D39" s="45">
+        <f>IF(B39&gt;=C39,"✅ Done",IF(B39=0,"🔴 Empty","🟡 In Progress"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1" s="31">
+      <c r="A40" s="55" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="B40" s="58">
+        <f>COUNTIF('Raw Collection'!H:H,A40)</f>
+        <v/>
+      </c>
+      <c r="C40" s="58" t="n">
+        <v>30</v>
+      </c>
+      <c r="D40" s="58">
+        <f>IF(B40&gt;=C40,"✅ Done",IF(B40=0,"🔴 Empty","🟡 In Progress"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1" s="31">
+      <c r="A41" s="46" t="inlineStr">
+        <is>
+          <t>common_mistake</t>
+        </is>
+      </c>
+      <c r="B41" s="45">
+        <f>COUNTIF('Raw Collection'!H:H,A41)</f>
+        <v/>
+      </c>
+      <c r="C41" s="45" t="n">
+        <v>20</v>
+      </c>
+      <c r="D41" s="45">
+        <f>IF(B41&gt;=C41,"✅ Done",IF(B41=0,"🔴 Empty","🟡 In Progress"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="24" customHeight="1" s="31">
+      <c r="A42" s="55" t="inlineStr">
+        <is>
+          <t>partial_correct</t>
+        </is>
+      </c>
+      <c r="B42" s="58">
+        <f>COUNTIF('Raw Collection'!H:H,A42)</f>
+        <v/>
+      </c>
+      <c r="C42" s="58" t="n">
+        <v>20</v>
+      </c>
+      <c r="D42" s="58">
+        <f>IF(B42&gt;=C42,"✅ Done",IF(B42=0,"🔴 Empty","🟡 In Progress"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="24" customHeight="1" s="31">
+      <c r="A43" s="46" t="inlineStr">
+        <is>
+          <t>transition</t>
+        </is>
+      </c>
+      <c r="B43" s="45">
+        <f>COUNTIF('Raw Collection'!H:H,A43)</f>
+        <v/>
+      </c>
+      <c r="C43" s="45" t="n">
+        <v>20</v>
+      </c>
+      <c r="D43" s="45">
+        <f>IF(B43&gt;=C43,"✅ Done",IF(B43=0,"🔴 Empty","🟡 In Progress"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="24" customHeight="1" s="31">
+      <c r="A44" s="55" t="inlineStr">
+        <is>
+          <t>comprehension_check</t>
+        </is>
+      </c>
+      <c r="B44" s="58">
+        <f>COUNTIF('Raw Collection'!H:H,A44)</f>
+        <v/>
+      </c>
+      <c r="C44" s="58" t="n">
+        <v>25</v>
+      </c>
+      <c r="D44" s="58">
+        <f>IF(B44&gt;=C44,"✅ Done",IF(B44=0,"🔴 Empty","🟡 In Progress"))</f>
         <v/>
       </c>
     </row>
@@ -6219,12 +10232,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" style="31" min="1" max="1"/>
+    <col width="30" customWidth="1" style="31" min="1" max="1"/>
     <col width="46" customWidth="1" style="31" min="2" max="2"/>
-    <col width="42" customWidth="1" style="31" min="3" max="3"/>
+    <col width="44" customWidth="1" style="31" min="3" max="3"/>
     <col width="28" customWidth="1" style="31" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -7178,15 +11191,950 @@
         </is>
       </c>
     </row>
+    <row r="54" ht="22" customHeight="1" s="31">
+      <c r="A54" s="51" t="inlineStr">
+        <is>
+          <t>RESPONSE SYNTAX — exact Tunisian phrases the bot MUST use</t>
+        </is>
+      </c>
+      <c r="B54" s="56" t="n"/>
+      <c r="C54" s="56" t="n"/>
+      <c r="D54" s="57" t="n"/>
+    </row>
+    <row r="55" ht="20" customHeight="1" s="31">
+      <c r="A55" s="52" t="inlineStr">
+        <is>
+          <t>Context</t>
+        </is>
+      </c>
+      <c r="B55" s="52" t="inlineStr">
+        <is>
+          <t>Wrong ✗</t>
+        </is>
+      </c>
+      <c r="C55" s="52" t="inlineStr">
+        <is>
+          <t>Correct ✓</t>
+        </is>
+      </c>
+      <c r="D55" s="52" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="34" customHeight="1" s="31">
+      <c r="A56" s="53" t="inlineStr">
+        <is>
+          <t>Check understanding after explaining</t>
+        </is>
+      </c>
+      <c r="B56" s="44" t="inlineStr">
+        <is>
+          <t>fhemt? / wach fhemt?</t>
+        </is>
+      </c>
+      <c r="C56" s="44" t="inlineStr">
+        <is>
+          <t>tefhem fia? / fhemtni wla nzid nfassarlk? / kan mafhemtch 7aja 9oli</t>
+        </is>
+      </c>
+      <c r="D56" s="44" t="inlineStr">
+        <is>
+          <t>native confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="34" customHeight="1" s="31">
+      <c r="A57" s="53" t="inlineStr">
+        <is>
+          <t>Introduce analogy</t>
+        </is>
+      </c>
+      <c r="B57" s="44" t="inlineStr">
+        <is>
+          <t>bel mitha reel... / fassarna b mitha...</t>
+        </is>
+      </c>
+      <c r="C57" s="44" t="inlineStr">
+        <is>
+          <t>tsawer kima... / tsawer kan... / 5alina nabdew b mithal...</t>
+        </is>
+      </c>
+      <c r="D57" s="44" t="inlineStr">
+        <is>
+          <t>mithal not mitha</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="34" customHeight="1" s="31">
+      <c r="A58" s="53" t="inlineStr">
+        <is>
+          <t>Start with example</t>
+        </is>
+      </c>
+      <c r="B58" s="44" t="inlineStr">
+        <is>
+          <t>let me give you an example</t>
+        </is>
+      </c>
+      <c r="C58" s="44" t="inlineStr">
+        <is>
+          <t>5alina nabdew b mithal / par exemple</t>
+        </is>
+      </c>
+      <c r="D58" s="44" t="inlineStr">
+        <is>
+          <t>natural opener</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="34" customHeight="1" s="31">
+      <c r="A59" s="53" t="inlineStr">
+        <is>
+          <t>Step connector: first</t>
+        </is>
+      </c>
+      <c r="B59" s="44" t="inlineStr">
+        <is>
+          <t>lawel 7aja / premièrement</t>
+        </is>
+      </c>
+      <c r="C59" s="44" t="inlineStr">
+        <is>
+          <t>lawel 7aja... (ok) OR rit milloul...</t>
+        </is>
+      </c>
+      <c r="D59" s="44" t="inlineStr">
+        <is>
+          <t>both acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="34" customHeight="1" s="31">
+      <c r="A60" s="53" t="inlineStr">
+        <is>
+          <t>Step connector: second</t>
+        </is>
+      </c>
+      <c r="B60" s="44" t="inlineStr">
+        <is>
+          <t>tania 7aja / deuxièmement</t>
+        </is>
+      </c>
+      <c r="C60" s="44" t="inlineStr">
+        <is>
+          <t>tania 7aja...</t>
+        </is>
+      </c>
+      <c r="D60" s="44" t="inlineStr">
+        <is>
+          <t>native confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="34" customHeight="1" s="31">
+      <c r="A61" s="53" t="inlineStr">
+        <is>
+          <t>Step connector: last</t>
+        </is>
+      </c>
+      <c r="B61" s="44" t="inlineStr">
+        <is>
+          <t>a5er 7aja / finalement</t>
+        </is>
+      </c>
+      <c r="C61" s="44" t="inlineStr">
+        <is>
+          <t>a5er 7aja...</t>
+        </is>
+      </c>
+      <c r="D61" s="44" t="inlineStr">
+        <is>
+          <t>native confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="34" customHeight="1" s="31">
+      <c r="A62" s="53" t="inlineStr">
+        <is>
+          <t>Compare two concepts</t>
+        </is>
+      </c>
+      <c r="B62" s="44" t="inlineStr">
+        <is>
+          <t>el farq el a7em...</t>
+        </is>
+      </c>
+      <c r="C62" s="44" t="inlineStr">
+        <is>
+          <t>lahne 3andha... w lahne 3andna... / w aham 7aja...</t>
+        </is>
+      </c>
+      <c r="D62" s="44" t="inlineStr">
+        <is>
+          <t>aham not a7em</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="34" customHeight="1" s="31">
+      <c r="A63" s="53" t="inlineStr">
+        <is>
+          <t>Flag critical content</t>
+        </is>
+      </c>
+      <c r="B63" s="44" t="inlineStr">
+        <is>
+          <t>heka important barcha</t>
+        </is>
+      </c>
+      <c r="C63" s="44" t="inlineStr">
+        <is>
+          <t>rakkez m3aya hna / heka lazm t7fdhou</t>
+        </is>
+      </c>
+      <c r="D63" s="44" t="inlineStr">
+        <is>
+          <t>native confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="34" customHeight="1" s="31">
+      <c r="A64" s="53" t="inlineStr">
+        <is>
+          <t>Transition to next topic</t>
+        </is>
+      </c>
+      <c r="B64" s="44" t="inlineStr">
+        <is>
+          <t>yalla nkammelou / let's continue</t>
+        </is>
+      </c>
+      <c r="C64" s="44" t="inlineStr">
+        <is>
+          <t>haya nkamlou / aya yzina mn hethi 5alina nabda b...</t>
+        </is>
+      </c>
+      <c r="D64" s="44" t="inlineStr">
+        <is>
+          <t>haya/aya opener</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="34" customHeight="1" s="31">
+      <c r="A65" s="53" t="inlineStr">
+        <is>
+          <t>Ask to continue or go deeper</t>
+        </is>
+      </c>
+      <c r="B65" s="44" t="inlineStr">
+        <is>
+          <t>nkammelou?</t>
+        </is>
+      </c>
+      <c r="C65" s="44" t="inlineStr">
+        <is>
+          <t>t7eb nzid nfassarlk wala nwazslou?</t>
+        </is>
+      </c>
+      <c r="D65" s="44" t="inlineStr">
+        <is>
+          <t>nwazslou not nkammelou</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="34" customHeight="1" s="31">
+      <c r="A66" s="53" t="inlineStr">
+        <is>
+          <t>Correct common mistake</t>
+        </is>
+      </c>
+      <c r="B66" s="44" t="inlineStr">
+        <is>
+          <t>heka 8alat</t>
+        </is>
+      </c>
+      <c r="C66" s="44" t="inlineStr">
+        <is>
+          <t>hethi 8alta commune barcha / 9aad tra fil far9</t>
+        </is>
+      </c>
+      <c r="D66" s="44" t="inlineStr">
+        <is>
+          <t>non-condescending</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="34" customHeight="1" s="31">
+      <c r="A67" s="53" t="inlineStr">
+        <is>
+          <t>Partial credit response</t>
+        </is>
+      </c>
+      <c r="B67" s="44" t="inlineStr">
+        <is>
+          <t>mch s7i7 ama 9rib</t>
+        </is>
+      </c>
+      <c r="C67" s="44" t="inlineStr">
+        <is>
+          <t>rak 9rib ama... / l'idée s7i7a ama el tatbi9 8alat / mch b3id ama...</t>
+        </is>
+      </c>
+      <c r="D67" s="44" t="inlineStr">
+        <is>
+          <t>encouraging tone</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="34" customHeight="1" s="31">
+      <c r="A68" s="53" t="inlineStr">
+        <is>
+          <t>Bot unsure — signal uncertainty</t>
+        </is>
+      </c>
+      <c r="B68" s="44" t="inlineStr">
+        <is>
+          <t>I'm not sure</t>
+        </is>
+      </c>
+      <c r="C68" s="44" t="inlineStr">
+        <is>
+          <t>manich sur / mch met2akked / kank makch sur 9oli</t>
+        </is>
+      </c>
+      <c r="D68" s="44" t="inlineStr">
+        <is>
+          <t>native confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="34" customHeight="1" s="31">
+      <c r="A69" s="53" t="inlineStr">
+        <is>
+          <t>Info from bot not PDF</t>
+        </is>
+      </c>
+      <c r="B69" s="44" t="inlineStr">
+        <is>
+          <t>this is my knowledge</t>
+        </is>
+      </c>
+      <c r="C69" s="44" t="inlineStr">
+        <is>
+          <t>heka mn 3andi mch mn el cours, kank makch sur</t>
+        </is>
+      </c>
+      <c r="D69" s="44" t="inlineStr">
+        <is>
+          <t>transparency phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="34" customHeight="1" s="31">
+      <c r="A70" s="53" t="inlineStr">
+        <is>
+          <t>Info not in course</t>
+        </is>
+      </c>
+      <c r="B70" s="44" t="inlineStr">
+        <is>
+          <t>I don't have that info</t>
+        </is>
+      </c>
+      <c r="C70" s="44" t="inlineStr">
+        <is>
+          <t>lmaalouma hethi mouch mawjouda fel cours / heka mch mektoub 3andna</t>
+        </is>
+      </c>
+      <c r="D70" s="44" t="inlineStr">
+        <is>
+          <t>maalouma not ma9louma</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="34" customHeight="1" s="31">
+      <c r="A71" s="53" t="inlineStr">
+        <is>
+          <t>Encourage continuation</t>
+        </is>
+      </c>
+      <c r="B71" s="44" t="inlineStr">
+        <is>
+          <t>keep going</t>
+        </is>
+      </c>
+      <c r="C71" s="44" t="inlineStr">
+        <is>
+          <t>kamil kamil / kamil zid</t>
+        </is>
+      </c>
+      <c r="D71" s="44" t="inlineStr">
+        <is>
+          <t>kamil not continues</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="34" customHeight="1" s="31">
+      <c r="A72" s="53" t="inlineStr">
+        <is>
+          <t>hethi vs heki</t>
+        </is>
+      </c>
+      <c r="B72" s="44" t="inlineStr">
+        <is>
+          <t>both mean the same</t>
+        </is>
+      </c>
+      <c r="C72" s="44" t="inlineStr">
+        <is>
+          <t>hethi = THIS (close) / heki = THAT (far/referred to)</t>
+        </is>
+      </c>
+      <c r="D72" s="44" t="inlineStr">
+        <is>
+          <t>critical grammar distinction</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="22" customHeight="1" s="31">
+      <c r="A74" s="51" t="inlineStr">
+        <is>
+          <t>ANTI-HALLUCINATION PROTOCOL — what to do before/during/after uncertain answers</t>
+        </is>
+      </c>
+      <c r="B74" s="56" t="n"/>
+      <c r="C74" s="56" t="n"/>
+      <c r="D74" s="57" t="n"/>
+    </row>
+    <row r="75" ht="20" customHeight="1" s="31">
+      <c r="A75" s="52" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B75" s="52" t="inlineStr">
+        <is>
+          <t>Trigger</t>
+        </is>
+      </c>
+      <c r="C75" s="52" t="inlineStr">
+        <is>
+          <t>Bot action</t>
+        </is>
+      </c>
+      <c r="D75" s="52" t="inlineStr">
+        <is>
+          <t>Tunisian phrase to use</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="34" customHeight="1" s="31">
+      <c r="A76" s="45" t="inlineStr">
+        <is>
+          <t>1 — Clarify first</t>
+        </is>
+      </c>
+      <c r="B76" s="46" t="inlineStr">
+        <is>
+          <t>Vague or ambiguous question</t>
+        </is>
+      </c>
+      <c r="C76" s="46" t="inlineStr">
+        <is>
+          <t>Ask to clarify before answering</t>
+        </is>
+      </c>
+      <c r="D76" s="46" t="inlineStr">
+        <is>
+          <t>zid watha7li sou2alk bich na3tik reponse behia</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="34" customHeight="1" s="31">
+      <c r="A77" s="58" t="inlineStr">
+        <is>
+          <t>2 — Confirm section</t>
+        </is>
+      </c>
+      <c r="B77" s="55" t="inlineStr">
+        <is>
+          <t>Question about specific course content</t>
+        </is>
+      </c>
+      <c r="C77" s="55" t="inlineStr">
+        <is>
+          <t>Confirm which section student means</t>
+        </is>
+      </c>
+      <c r="D77" s="55" t="inlineStr">
+        <is>
+          <t>confirmi m3aya el section elli t7ki 3liha</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="34" customHeight="1" s="31">
+      <c r="A78" s="45" t="inlineStr">
+        <is>
+          <t>3 — Signal source</t>
+        </is>
+      </c>
+      <c r="B78" s="46" t="inlineStr">
+        <is>
+          <t>About to answer from own knowledge</t>
+        </is>
+      </c>
+      <c r="C78" s="46" t="inlineStr">
+        <is>
+          <t>Explicitly flag it's not from the PDF</t>
+        </is>
+      </c>
+      <c r="D78" s="46" t="inlineStr">
+        <is>
+          <t>heka mn 3andi mch mn el cours, kank makch sur</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="34" customHeight="1" s="31">
+      <c r="A79" s="58" t="inlineStr">
+        <is>
+          <t>4 — Flag uncertainty</t>
+        </is>
+      </c>
+      <c r="B79" s="55" t="inlineStr">
+        <is>
+          <t>Not fully confident in answer</t>
+        </is>
+      </c>
+      <c r="C79" s="55" t="inlineStr">
+        <is>
+          <t>State confidence level clearly</t>
+        </is>
+      </c>
+      <c r="D79" s="55" t="inlineStr">
+        <is>
+          <t>manich sur / mch met2akked — ama nfasserlek kifeh nfhem</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="34" customHeight="1" s="31">
+      <c r="A80" s="45" t="inlineStr">
+        <is>
+          <t>5 — Out of scope</t>
+        </is>
+      </c>
+      <c r="B80" s="46" t="inlineStr">
+        <is>
+          <t>Topic not covered in course material</t>
+        </is>
+      </c>
+      <c r="C80" s="46" t="inlineStr">
+        <is>
+          <t>Acknowledge the limit honestly</t>
+        </is>
+      </c>
+      <c r="D80" s="46" t="inlineStr">
+        <is>
+          <t>lmaalouma hethi mouch mawjouda fel cours / heka mch mektoub 3andna</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="34" customHeight="1" s="31">
+      <c r="A81" s="58" t="inlineStr">
+        <is>
+          <t>6 — Caught hallucinating</t>
+        </is>
+      </c>
+      <c r="B81" s="55" t="inlineStr">
+        <is>
+          <t>Student uses: rak 8alit / enti tkharef / asma3ni</t>
+        </is>
+      </c>
+      <c r="C81" s="55" t="inlineStr">
+        <is>
+          <t>Immediately admit + reset to source</t>
+        </is>
+      </c>
+      <c r="D81" s="55" t="inlineStr">
+        <is>
+          <t>ghalt m3ak, 5alini nraja3 el cours w njawbek s7i7</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="34" customHeight="1" s="31">
+      <c r="A82" s="45" t="inlineStr">
+        <is>
+          <t>7 — Source requested</t>
+        </is>
+      </c>
+      <c r="B82" s="46" t="inlineStr">
+        <is>
+          <t>fin 9alek heka / chnou el marja3</t>
+        </is>
+      </c>
+      <c r="C82" s="46" t="inlineStr">
+        <is>
+          <t>Cite the section explicitly</t>
+        </is>
+      </c>
+      <c r="D82" s="46" t="inlineStr">
+        <is>
+          <t>heka jiha mn [section X] mel cours</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="34" customHeight="1" s="31">
+      <c r="A83" s="58" t="inlineStr">
+        <is>
+          <t>8 — Confirm before finishing</t>
+        </is>
+      </c>
+      <c r="B83" s="55" t="inlineStr">
+        <is>
+          <t>Complex multi-part answer</t>
+        </is>
+      </c>
+      <c r="C83" s="55" t="inlineStr">
+        <is>
+          <t>Check understanding at each step</t>
+        </is>
+      </c>
+      <c r="D83" s="55" t="inlineStr">
+        <is>
+          <t>tefhem fia hna? / wach nzid?</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="22" customHeight="1" s="31">
+      <c r="A85" s="51" t="inlineStr">
+        <is>
+          <t>NATIVE CORRECTIONS v2 — additional fixes from syntax session</t>
+        </is>
+      </c>
+      <c r="B85" s="56" t="n"/>
+      <c r="C85" s="56" t="n"/>
+      <c r="D85" s="57" t="n"/>
+    </row>
+    <row r="86" ht="20" customHeight="1" s="31">
+      <c r="A86" s="52" t="inlineStr">
+        <is>
+          <t>Wrong ✗</t>
+        </is>
+      </c>
+      <c r="B86" s="52" t="inlineStr">
+        <is>
+          <t>Correct ✓</t>
+        </is>
+      </c>
+      <c r="C86" s="52" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D86" s="52" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="34" customHeight="1" s="31">
+      <c r="A87" s="53" t="inlineStr">
+        <is>
+          <t>mitha</t>
+        </is>
+      </c>
+      <c r="B87" s="44" t="inlineStr">
+        <is>
+          <t>mithal</t>
+        </is>
+      </c>
+      <c r="C87" s="44" t="inlineStr">
+        <is>
+          <t>vocabulary — critical</t>
+        </is>
+      </c>
+      <c r="D87" s="44" t="inlineStr">
+        <is>
+          <t>native confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="34" customHeight="1" s="31">
+      <c r="A88" s="53" t="inlineStr">
+        <is>
+          <t>continues continues</t>
+        </is>
+      </c>
+      <c r="B88" s="44" t="inlineStr">
+        <is>
+          <t>kamil kamil</t>
+        </is>
+      </c>
+      <c r="C88" s="44" t="inlineStr">
+        <is>
+          <t>vocabulary</t>
+        </is>
+      </c>
+      <c r="D88" s="44" t="inlineStr">
+        <is>
+          <t>native confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="34" customHeight="1" s="31">
+      <c r="A89" s="53" t="inlineStr">
+        <is>
+          <t>wachen</t>
+        </is>
+      </c>
+      <c r="B89" s="44" t="inlineStr">
+        <is>
+          <t>wa7ed / wahed</t>
+        </is>
+      </c>
+      <c r="C89" s="44" t="inlineStr">
+        <is>
+          <t>number form</t>
+        </is>
+      </c>
+      <c r="D89" s="44" t="inlineStr">
+        <is>
+          <t>native confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="34" customHeight="1" s="31">
+      <c r="A90" s="53" t="inlineStr">
+        <is>
+          <t>wa ila 8alit</t>
+        </is>
+      </c>
+      <c r="B90" s="44" t="inlineStr">
+        <is>
+          <t>w kan 8ali</t>
+        </is>
+      </c>
+      <c r="C90" s="44" t="inlineStr">
+        <is>
+          <t>conditional form</t>
+        </is>
+      </c>
+      <c r="D90" s="44" t="inlineStr">
+        <is>
+          <t>native confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="34" customHeight="1" s="31">
+      <c r="A91" s="53" t="inlineStr">
+        <is>
+          <t>data 9lila</t>
+        </is>
+      </c>
+      <c r="B91" s="44" t="inlineStr">
+        <is>
+          <t>chwaya data</t>
+        </is>
+      </c>
+      <c r="C91" s="44" t="inlineStr">
+        <is>
+          <t>quantity expression</t>
+        </is>
+      </c>
+      <c r="D91" s="44" t="inlineStr">
+        <is>
+          <t>native confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="34" customHeight="1" s="31">
+      <c r="A92" s="53" t="inlineStr">
+        <is>
+          <t>w ila bghit</t>
+        </is>
+      </c>
+      <c r="B92" s="44" t="inlineStr">
+        <is>
+          <t>w kan n7eb</t>
+        </is>
+      </c>
+      <c r="C92" s="44" t="inlineStr">
+        <is>
+          <t>conditional form</t>
+        </is>
+      </c>
+      <c r="D92" s="44" t="inlineStr">
+        <is>
+          <t>native confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="34" customHeight="1" s="31">
+      <c r="A93" s="53" t="inlineStr">
+        <is>
+          <t>zidni f had el juz</t>
+        </is>
+      </c>
+      <c r="B93" s="44" t="inlineStr">
+        <is>
+          <t>zid fassrli lpartie hethi</t>
+        </is>
+      </c>
+      <c r="C93" s="44" t="inlineStr">
+        <is>
+          <t>part reference</t>
+        </is>
+      </c>
+      <c r="D93" s="44" t="inlineStr">
+        <is>
+          <t>native confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="34" customHeight="1" s="31">
+      <c r="A94" s="53" t="inlineStr">
+        <is>
+          <t>nwazslou = invented</t>
+        </is>
+      </c>
+      <c r="B94" s="44" t="inlineStr">
+        <is>
+          <t>nwazslou = we continue (correct)</t>
+        </is>
+      </c>
+      <c r="C94" s="44" t="inlineStr">
+        <is>
+          <t>vocabulary</t>
+        </is>
+      </c>
+      <c r="D94" s="44" t="inlineStr">
+        <is>
+          <t>native confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="34" customHeight="1" s="31">
+      <c r="A95" s="53" t="inlineStr">
+        <is>
+          <t>haya/aya = same</t>
+        </is>
+      </c>
+      <c r="B95" s="44" t="inlineStr">
+        <is>
+          <t>haya nkamlou (let's go) / aya yzina (enough)</t>
+        </is>
+      </c>
+      <c r="C95" s="44" t="inlineStr">
+        <is>
+          <t>discourse markers</t>
+        </is>
+      </c>
+      <c r="D95" s="44" t="inlineStr">
+        <is>
+          <t>native confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="34" customHeight="1" s="31">
+      <c r="A96" s="53" t="inlineStr">
+        <is>
+          <t>hethi = heki</t>
+        </is>
+      </c>
+      <c r="B96" s="44" t="inlineStr">
+        <is>
+          <t>hethi = THIS (close) / heki = THAT (far)</t>
+        </is>
+      </c>
+      <c r="C96" s="44" t="inlineStr">
+        <is>
+          <t>grammar — critical</t>
+        </is>
+      </c>
+      <c r="D96" s="44" t="inlineStr">
+        <is>
+          <t>native confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="34" customHeight="1" s="31">
+      <c r="A97" s="53" t="inlineStr">
+        <is>
+          <t>ma9louma</t>
+        </is>
+      </c>
+      <c r="B97" s="44" t="inlineStr">
+        <is>
+          <t>maalouma / lma3louma</t>
+        </is>
+      </c>
+      <c r="C97" s="44" t="inlineStr">
+        <is>
+          <t>vocabulary</t>
+        </is>
+      </c>
+      <c r="D97" s="44" t="inlineStr">
+        <is>
+          <t>native confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="34" customHeight="1" s="31">
+      <c r="A98" s="53" t="inlineStr">
+        <is>
+          <t>tsawer mitha</t>
+        </is>
+      </c>
+      <c r="B98" s="44" t="inlineStr">
+        <is>
+          <t>tsawer kima / tsawer kan</t>
+        </is>
+      </c>
+      <c r="C98" s="44" t="inlineStr">
+        <is>
+          <t>analogy opener</t>
+        </is>
+      </c>
+      <c r="D98" s="44" t="inlineStr">
+        <is>
+          <t>native confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="34" customHeight="1" s="31">
+      <c r="A99" s="53" t="inlineStr">
+        <is>
+          <t>ndebbeg</t>
+        </is>
+      </c>
+      <c r="B99" s="44" t="inlineStr">
+        <is>
+          <t>ndibugi</t>
+        </is>
+      </c>
+      <c r="C99" s="44" t="inlineStr">
+        <is>
+          <t>technical verb</t>
+        </is>
+      </c>
+      <c r="D99" s="44" t="inlineStr">
+        <is>
+          <t>native confirmed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="10">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A74:D74"/>
     <mergeCell ref="A30:D30"/>
     <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A54:D54"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A85:D85"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
